--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$105</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4031" uniqueCount="702">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4228" uniqueCount="725">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1078,6 +1078,9 @@
     <t>.role</t>
   </si>
   <si>
+    <t>1711: reference from PRESCRIPTION - DIVISION (#52-20)</t>
+  </si>
+  <si>
     <t>MedicationDispense.location</t>
   </si>
   <si>
@@ -1156,6 +1159,9 @@
   </si>
   <si>
     <t>RXD-33-Dispense Type</t>
+  </si>
+  <si>
+    <t>1708: fixed value = FF</t>
   </si>
   <si>
     <t>MedicationDispense.quantity</t>
@@ -1530,6 +1536,71 @@
   </si>
   <si>
     <t>RXD-9 Dispense Notes</t>
+  </si>
+  <si>
+    <t>MedicationDispense.note.id</t>
+  </si>
+  <si>
+    <t>MedicationDispense.note.extension</t>
+  </si>
+  <si>
+    <t>MedicationDispense.note.author[x]</t>
+  </si>
+  <si>
+    <t>Reference(Practitioner|Patient|RelatedPerson|Organization)
+string</t>
+  </si>
+  <si>
+    <t>Individual responsible for the annotation</t>
+  </si>
+  <si>
+    <t>The individual responsible for making the annotation.</t>
+  </si>
+  <si>
+    <t>Organization is used when there's no need for specific attribution as to who made the comment.</t>
+  </si>
+  <si>
+    <t>Annotation.author[x]</t>
+  </si>
+  <si>
+    <t>Act.participant[typeCode=AUT].role</t>
+  </si>
+  <si>
+    <t>MedicationDispense.note.time</t>
+  </si>
+  <si>
+    <t>When the annotation was made</t>
+  </si>
+  <si>
+    <t>Indicates when this particular annotation was made.</t>
+  </si>
+  <si>
+    <t>Annotation.time</t>
+  </si>
+  <si>
+    <t>Act.effectiveTime</t>
+  </si>
+  <si>
+    <t>MedicationDispense.note.text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">markdown
+</t>
+  </si>
+  <si>
+    <t>The annotation  - text content (as markdown)</t>
+  </si>
+  <si>
+    <t>The text of the annotation in markdown format.</t>
+  </si>
+  <si>
+    <t>Annotation.text</t>
+  </si>
+  <si>
+    <t>Act.text</t>
+  </si>
+  <si>
+    <t>1716: source value from PRESCRIPTION - REMARKS (#52-12)</t>
   </si>
   <si>
     <t>MedicationDispense.dosageInstruction</t>
@@ -2511,7 +2582,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR100"/>
+  <dimension ref="A1:AR105"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="80.94140625" customWidth="true" bestFit="true"/>
@@ -7114,7 +7185,7 @@
         <v>91</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>81</v>
@@ -7210,7 +7281,7 @@
         <v>81</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>81</v>
+        <v>340</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>81</v>
@@ -7221,10 +7292,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7247,13 +7318,13 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7304,7 +7375,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7322,7 +7393,7 @@
         <v>81</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>81</v>
@@ -7334,21 +7405,21 @@
         <v>81</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7371,16 +7442,16 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7430,7 +7501,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7445,25 +7516,25 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>81</v>
@@ -7471,10 +7542,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7488,7 +7559,7 @@
         <v>91</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>81</v>
@@ -7500,10 +7571,10 @@
         <v>185</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7533,10 +7604,10 @@
         <v>179</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>81</v>
@@ -7554,7 +7625,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7572,19 +7643,19 @@
         <v>81</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>81</v>
+        <v>367</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>81</v>
@@ -7595,10 +7666,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7621,13 +7692,13 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7678,7 +7749,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7696,16 +7767,16 @@
         <v>81</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>81</v>
@@ -7719,10 +7790,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7843,10 +7914,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7969,10 +8040,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7995,19 +8066,19 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -8056,7 +8127,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -8074,7 +8145,7 @@
         <v>81</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>81</v>
@@ -8083,24 +8154,24 @@
         <v>81</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8126,20 +8197,20 @@
         <v>111</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q45" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="R45" t="s" s="2">
         <v>81</v>
@@ -8163,10 +8234,10 @@
         <v>167</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>81</v>
@@ -8184,7 +8255,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8202,7 +8273,7 @@
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>81</v>
@@ -8211,7 +8282,7 @@
         <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>81</v>
@@ -8225,10 +8296,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8254,14 +8325,14 @@
         <v>211</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -8310,7 +8381,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8328,7 +8399,7 @@
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>81</v>
@@ -8337,7 +8408,7 @@
         <v>81</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>81</v>
@@ -8351,10 +8422,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8380,14 +8451,14 @@
         <v>105</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
@@ -8436,7 +8507,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8445,7 +8516,7 @@
         <v>91</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>103</v>
@@ -8454,7 +8525,7 @@
         <v>81</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>81</v>
@@ -8463,7 +8534,7 @@
         <v>81</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>81</v>
@@ -8477,10 +8548,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8506,16 +8577,16 @@
         <v>111</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -8564,7 +8635,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8582,7 +8653,7 @@
         <v>81</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>81</v>
@@ -8591,7 +8662,7 @@
         <v>81</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>81</v>
@@ -8605,10 +8676,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8631,13 +8702,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8688,7 +8759,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8706,7 +8777,7 @@
         <v>81</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>81</v>
@@ -8715,24 +8786,24 @@
         <v>81</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8755,13 +8826,13 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8812,7 +8883,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8830,19 +8901,19 @@
         <v>81</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>81</v>
@@ -8853,10 +8924,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8879,13 +8950,13 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8936,7 +9007,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8951,22 +9022,22 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>81</v>
@@ -8977,10 +9048,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9003,13 +9074,13 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -9060,7 +9131,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9078,16 +9149,16 @@
         <v>81</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>81</v>
@@ -9101,10 +9172,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9225,10 +9296,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9351,10 +9422,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9380,13 +9451,13 @@
         <v>211</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9436,7 +9507,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9445,7 +9516,7 @@
         <v>91</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>103</v>
@@ -9477,10 +9548,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9506,13 +9577,13 @@
         <v>105</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9538,13 +9609,13 @@
         <v>81</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>81</v>
@@ -9562,7 +9633,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9603,10 +9674,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9632,13 +9703,13 @@
         <v>149</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9688,7 +9759,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9706,7 +9777,7 @@
         <v>81</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>81</v>
@@ -9729,10 +9800,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9758,13 +9829,13 @@
         <v>211</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9814,7 +9885,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9844,21 +9915,21 @@
         <v>81</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR58" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9881,13 +9952,13 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9938,7 +10009,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9956,13 +10027,13 @@
         <v>81</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>81</v>
@@ -9979,10 +10050,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10005,13 +10076,13 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -10062,7 +10133,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10077,10 +10148,10 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>81</v>
@@ -10089,7 +10160,7 @@
         <v>81</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>81</v>
@@ -10103,10 +10174,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10117,7 +10188,7 @@
         <v>82</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>81</v>
@@ -10129,17 +10200,15 @@
         <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>487</v>
+        <v>211</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>488</v>
+        <v>212</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>490</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -10188,25 +10257,25 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>486</v>
+        <v>214</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>491</v>
+        <v>215</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>81</v>
@@ -10229,21 +10298,21 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>81</v>
@@ -10255,15 +10324,17 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>211</v>
+        <v>137</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>212</v>
+        <v>138</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>218</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>81</v>
@@ -10300,31 +10371,31 @@
         <v>81</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>81</v>
+        <v>219</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>81</v>
+        <v>220</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>81</v>
+        <v>201</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>81</v>
@@ -10353,21 +10424,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>136</v>
+        <v>81</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>81</v>
@@ -10376,19 +10447,19 @@
         <v>81</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>137</v>
+        <v>491</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>138</v>
+        <v>492</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>218</v>
+        <v>493</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>140</v>
+        <v>494</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10426,37 +10497,37 @@
         <v>81</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>219</v>
+        <v>81</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>201</v>
+        <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>221</v>
+        <v>495</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>215</v>
+        <v>496</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>81</v>
@@ -10465,7 +10536,7 @@
         <v>81</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>81</v>
+        <v>134</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>81</v>
@@ -10479,46 +10550,42 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>323</v>
+        <v>81</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J64" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>137</v>
+        <v>427</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>324</v>
+        <v>498</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>499</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>81</v>
       </c>
@@ -10566,34 +10633,34 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>326</v>
+        <v>500</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO64" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>81</v>
@@ -10607,10 +10674,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10618,13 +10685,13 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>81</v>
@@ -10633,18 +10700,16 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="N65" s="2"/>
-      <c r="O65" t="s" s="2">
-        <v>499</v>
-      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>81</v>
       </c>
@@ -10692,10 +10757,10 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AH65" t="s" s="2">
         <v>91</v>
@@ -10710,7 +10775,7 @@
         <v>81</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>81</v>
@@ -10719,10 +10784,10 @@
         <v>81</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>502</v>
+        <v>134</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>81</v>
+        <v>508</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>81</v>
@@ -10733,10 +10798,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10747,30 +10812,30 @@
         <v>82</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>211</v>
+        <v>510</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" t="s" s="2">
-        <v>506</v>
-      </c>
+        <v>512</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>81</v>
       </c>
@@ -10818,13 +10883,13 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>81</v>
@@ -10836,7 +10901,7 @@
         <v>81</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>501</v>
+        <v>514</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>81</v>
@@ -10845,24 +10910,24 @@
         <v>81</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>508</v>
+        <v>81</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>509</v>
+        <v>81</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR66" t="s" s="2">
-        <v>510</v>
+        <v>81</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10873,7 +10938,7 @@
         <v>82</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>81</v>
@@ -10882,23 +10947,19 @@
         <v>81</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>185</v>
+        <v>211</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>512</v>
+        <v>212</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>515</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>81</v>
       </c>
@@ -10922,13 +10983,13 @@
         <v>81</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>179</v>
+        <v>81</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>516</v>
+        <v>81</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>517</v>
+        <v>81</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>81</v>
@@ -10946,25 +11007,25 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>518</v>
+        <v>214</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>501</v>
+        <v>215</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>81</v>
@@ -10973,7 +11034,7 @@
         <v>81</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>519</v>
+        <v>81</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>81</v>
@@ -10987,41 +11048,43 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>211</v>
+        <v>137</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>521</v>
+        <v>138</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>218</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>81</v>
@@ -11058,37 +11121,37 @@
         <v>81</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>81</v>
+        <v>219</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>81</v>
+        <v>220</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>81</v>
+        <v>201</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>523</v>
+        <v>221</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>501</v>
+        <v>215</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>81</v>
@@ -11097,13 +11160,13 @@
         <v>81</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>519</v>
+        <v>81</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>524</v>
+        <v>81</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>525</v>
+        <v>81</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>81</v>
@@ -11111,45 +11174,45 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>81</v>
+        <v>323</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J69" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>527</v>
+        <v>137</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>528</v>
+        <v>324</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>529</v>
+        <v>325</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>530</v>
+        <v>140</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>531</v>
+        <v>146</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>81</v>
@@ -11198,25 +11261,25 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>532</v>
+        <v>326</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>533</v>
+        <v>134</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>81</v>
@@ -11239,10 +11302,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>534</v>
+        <v>518</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>534</v>
+        <v>518</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11265,18 +11328,18 @@
         <v>92</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>535</v>
+        <v>519</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>536</v>
+        <v>520</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="O70" s="2"/>
+        <v>521</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" t="s" s="2">
+        <v>522</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>81</v>
       </c>
@@ -11300,13 +11363,13 @@
         <v>81</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>179</v>
+        <v>81</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>539</v>
+        <v>81</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>540</v>
+        <v>81</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>81</v>
@@ -11324,7 +11387,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>541</v>
+        <v>523</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11342,7 +11405,7 @@
         <v>81</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>542</v>
+        <v>524</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>81</v>
@@ -11351,7 +11414,7 @@
         <v>81</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>543</v>
+        <v>525</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>81</v>
@@ -11365,10 +11428,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>544</v>
+        <v>526</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>544</v>
+        <v>526</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11382,7 +11445,7 @@
         <v>91</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>81</v>
@@ -11391,19 +11454,17 @@
         <v>92</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>185</v>
+        <v>211</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>545</v>
+        <v>527</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>547</v>
-      </c>
+        <v>528</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>548</v>
+        <v>529</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>81</v>
@@ -11428,13 +11489,13 @@
         <v>81</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>179</v>
+        <v>81</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>549</v>
+        <v>81</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>550</v>
+        <v>81</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>81</v>
@@ -11452,7 +11513,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>551</v>
+        <v>530</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11470,7 +11531,7 @@
         <v>81</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>552</v>
+        <v>524</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>81</v>
@@ -11479,24 +11540,24 @@
         <v>81</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>553</v>
+        <v>531</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>81</v>
+        <v>532</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>81</v>
+        <v>533</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>554</v>
+        <v>534</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>554</v>
+        <v>534</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11507,7 +11568,7 @@
         <v>82</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>81</v>
@@ -11522,14 +11583,16 @@
         <v>185</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>555</v>
+        <v>535</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>537</v>
+      </c>
       <c r="O72" t="s" s="2">
-        <v>557</v>
+        <v>538</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -11557,10 +11620,10 @@
         <v>179</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>558</v>
+        <v>539</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>559</v>
+        <v>540</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>81</v>
@@ -11578,13 +11641,13 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>560</v>
+        <v>541</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>81</v>
@@ -11596,7 +11659,7 @@
         <v>81</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>561</v>
+        <v>524</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>81</v>
@@ -11605,7 +11668,7 @@
         <v>81</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>562</v>
+        <v>542</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>81</v>
@@ -11619,10 +11682,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>563</v>
+        <v>543</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>563</v>
+        <v>543</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11636,7 +11699,7 @@
         <v>91</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>81</v>
@@ -11645,20 +11708,16 @@
         <v>92</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>185</v>
+        <v>211</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>564</v>
+        <v>544</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>567</v>
-      </c>
+        <v>545</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>81</v>
       </c>
@@ -11682,13 +11741,13 @@
         <v>81</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>179</v>
+        <v>81</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>568</v>
+        <v>81</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>569</v>
+        <v>81</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>81</v>
@@ -11706,7 +11765,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>570</v>
+        <v>546</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11724,7 +11783,7 @@
         <v>81</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>571</v>
+        <v>524</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>81</v>
@@ -11733,13 +11792,13 @@
         <v>81</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>572</v>
+        <v>542</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>81</v>
+        <v>547</v>
       </c>
       <c r="AQ73" t="s" s="2">
-        <v>81</v>
+        <v>548</v>
       </c>
       <c r="AR73" t="s" s="2">
         <v>81</v>
@@ -11747,10 +11806,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>573</v>
+        <v>549</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>573</v>
+        <v>549</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11761,7 +11820,7 @@
         <v>82</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>81</v>
@@ -11773,16 +11832,20 @@
         <v>92</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>574</v>
+        <v>550</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>575</v>
+        <v>551</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
+        <v>552</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>554</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
       </c>
@@ -11830,13 +11893,13 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>577</v>
+        <v>555</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>81</v>
@@ -11848,7 +11911,7 @@
         <v>81</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>81</v>
+        <v>556</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>81</v>
@@ -11857,7 +11920,7 @@
         <v>81</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>578</v>
+        <v>81</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>81</v>
@@ -11871,10 +11934,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>579</v>
+        <v>557</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>579</v>
+        <v>557</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11894,18 +11957,20 @@
         <v>81</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>211</v>
+        <v>558</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>212</v>
+        <v>559</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>560</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>561</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>81</v>
@@ -11930,13 +11995,13 @@
         <v>81</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>81</v>
+        <v>179</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>81</v>
+        <v>562</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>81</v>
+        <v>563</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>81</v>
@@ -11954,7 +12019,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>214</v>
+        <v>564</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -11966,13 +12031,13 @@
         <v>81</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>215</v>
+        <v>565</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>81</v>
@@ -11981,7 +12046,7 @@
         <v>81</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>81</v>
+        <v>566</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>81</v>
@@ -11995,21 +12060,21 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>580</v>
+        <v>567</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>580</v>
+        <v>567</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>136</v>
+        <v>81</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>81</v>
@@ -12018,21 +12083,23 @@
         <v>81</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>137</v>
+        <v>185</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>138</v>
+        <v>568</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>218</v>
+        <v>569</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O76" s="2"/>
+        <v>570</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>571</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>81</v>
       </c>
@@ -12056,49 +12123,49 @@
         <v>81</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>81</v>
+        <v>179</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>81</v>
+        <v>572</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>81</v>
+        <v>573</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>219</v>
+        <v>81</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>201</v>
+        <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>221</v>
+        <v>574</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>215</v>
+        <v>575</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>81</v>
@@ -12107,7 +12174,7 @@
         <v>81</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>81</v>
+        <v>576</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>81</v>
@@ -12121,10 +12188,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12150,14 +12217,14 @@
         <v>185</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>81</v>
@@ -12185,10 +12252,10 @@
         <v>179</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>81</v>
@@ -12206,7 +12273,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12224,7 +12291,7 @@
         <v>81</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>81</v>
+        <v>584</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>81</v>
@@ -12233,7 +12300,7 @@
         <v>81</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>81</v>
@@ -12247,10 +12314,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12273,19 +12340,19 @@
         <v>92</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="O78" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>594</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>81</v>
@@ -12310,29 +12377,31 @@
         <v>81</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>81</v>
+        <v>179</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>81</v>
+        <v>591</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>81</v>
+        <v>592</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AC78" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>201</v>
+        <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12350,7 +12419,7 @@
         <v>81</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>571</v>
+        <v>594</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>81</v>
@@ -12359,7 +12428,7 @@
         <v>81</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>81</v>
@@ -12373,14 +12442,12 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="C79" t="s" s="2">
-        <v>598</v>
-      </c>
+        <v>596</v>
+      </c>
+      <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
         <v>81</v>
       </c>
@@ -12389,7 +12456,7 @@
         <v>82</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>81</v>
@@ -12398,23 +12465,19 @@
         <v>81</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>367</v>
+        <v>597</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="M79" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>594</v>
-      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>81</v>
       </c>
@@ -12462,25 +12525,25 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>602</v>
+        <v>81</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>603</v>
+        <v>103</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>604</v>
+        <v>81</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>81</v>
@@ -12489,7 +12552,7 @@
         <v>81</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>81</v>
@@ -12503,10 +12566,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12627,10 +12690,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12753,10 +12816,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>611</v>
+        <v>604</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12770,7 +12833,7 @@
         <v>91</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>81</v>
@@ -12779,19 +12842,17 @@
         <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>376</v>
+        <v>185</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>377</v>
+        <v>605</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>379</v>
-      </c>
+        <v>606</v>
+      </c>
+      <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>380</v>
+        <v>607</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>81</v>
@@ -12816,13 +12877,13 @@
         <v>81</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>81</v>
+        <v>179</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>81</v>
+        <v>608</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>81</v>
+        <v>609</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>81</v>
@@ -12840,7 +12901,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>381</v>
+        <v>610</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -12858,7 +12919,7 @@
         <v>81</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>382</v>
+        <v>81</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>81</v>
@@ -12867,24 +12928,24 @@
         <v>81</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>383</v>
+        <v>611</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>612</v>
+        <v>81</v>
       </c>
       <c r="AQ82" t="s" s="2">
-        <v>613</v>
+        <v>81</v>
       </c>
       <c r="AR82" t="s" s="2">
-        <v>614</v>
+        <v>81</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12895,36 +12956,36 @@
         <v>82</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J83" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>111</v>
+        <v>613</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>387</v>
+        <v>614</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N83" s="2"/>
+        <v>615</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>616</v>
+      </c>
       <c r="O83" t="s" s="2">
-        <v>389</v>
+        <v>617</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q83" t="s" s="2">
-        <v>390</v>
-      </c>
+      <c r="Q83" s="2"/>
       <c r="R83" t="s" s="2">
         <v>81</v>
       </c>
@@ -12944,31 +13005,29 @@
         <v>81</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>391</v>
+        <v>81</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>392</v>
+        <v>81</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="AC83" s="2"/>
       <c r="AD83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>81</v>
+        <v>201</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>393</v>
+        <v>618</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -12986,7 +13045,7 @@
         <v>81</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>394</v>
+        <v>594</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>81</v>
@@ -12995,7 +13054,7 @@
         <v>81</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>395</v>
+        <v>619</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>81</v>
@@ -13009,12 +13068,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="C84" s="2"/>
+        <v>612</v>
+      </c>
+      <c r="C84" t="s" s="2">
+        <v>621</v>
+      </c>
       <c r="D84" t="s" s="2">
         <v>81</v>
       </c>
@@ -13026,26 +13087,28 @@
         <v>91</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>211</v>
+        <v>369</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>397</v>
+        <v>622</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N84" s="2"/>
+        <v>623</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>624</v>
+      </c>
       <c r="O84" t="s" s="2">
-        <v>399</v>
+        <v>617</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -13094,7 +13157,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>400</v>
+        <v>618</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13103,16 +13166,16 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>81</v>
+        <v>625</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>103</v>
+        <v>626</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>401</v>
+        <v>627</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>81</v>
@@ -13121,24 +13184,24 @@
         <v>81</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>402</v>
+        <v>628</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>619</v>
+        <v>81</v>
       </c>
       <c r="AQ84" t="s" s="2">
-        <v>620</v>
+        <v>81</v>
       </c>
       <c r="AR84" t="s" s="2">
-        <v>621</v>
+        <v>81</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13158,21 +13221,19 @@
         <v>81</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>105</v>
+        <v>211</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>404</v>
+        <v>212</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>405</v>
+        <v>213</v>
       </c>
       <c r="N85" s="2"/>
-      <c r="O85" t="s" s="2">
-        <v>406</v>
-      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>81</v>
       </c>
@@ -13220,7 +13281,7 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>407</v>
+        <v>214</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -13229,16 +13290,16 @@
         <v>91</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>408</v>
+        <v>81</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>409</v>
+        <v>215</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>81</v>
@@ -13247,7 +13308,7 @@
         <v>81</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>402</v>
+        <v>81</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>81</v>
@@ -13261,46 +13322,44 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>624</v>
+        <v>631</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>625</v>
+        <v>632</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>411</v>
+        <v>138</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>412</v>
+        <v>218</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>414</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>81</v>
       </c>
@@ -13336,37 +13395,37 @@
         <v>81</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>81</v>
+        <v>219</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>81</v>
+        <v>220</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>81</v>
+        <v>201</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>415</v>
+        <v>221</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>416</v>
+        <v>215</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>81</v>
@@ -13375,24 +13434,24 @@
         <v>81</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>402</v>
+        <v>81</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>626</v>
+        <v>81</v>
       </c>
       <c r="AQ86" t="s" s="2">
-        <v>620</v>
+        <v>81</v>
       </c>
       <c r="AR86" t="s" s="2">
-        <v>621</v>
+        <v>81</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>627</v>
+        <v>634</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13406,7 +13465,7 @@
         <v>91</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>81</v>
@@ -13415,19 +13474,19 @@
         <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>628</v>
+        <v>378</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>629</v>
+        <v>379</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>630</v>
+        <v>380</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>631</v>
+        <v>381</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>632</v>
+        <v>382</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>81</v>
@@ -13476,7 +13535,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>633</v>
+        <v>383</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13494,7 +13553,7 @@
         <v>81</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>634</v>
+        <v>384</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>81</v>
@@ -13503,24 +13562,24 @@
         <v>81</v>
       </c>
       <c r="AO87" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AP87" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="AP87" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AQ87" t="s" s="2">
-        <v>81</v>
+        <v>636</v>
       </c>
       <c r="AR87" t="s" s="2">
-        <v>81</v>
+        <v>637</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13531,36 +13590,36 @@
         <v>82</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J88" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>637</v>
+        <v>111</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>638</v>
+        <v>389</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>640</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>641</v>
+        <v>391</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q88" s="2"/>
+      <c r="Q88" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="R88" t="s" s="2">
         <v>81</v>
       </c>
@@ -13580,13 +13639,13 @@
         <v>81</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>81</v>
+        <v>167</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>81</v>
+        <v>393</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>81</v>
+        <v>394</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>81</v>
@@ -13604,7 +13663,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>642</v>
+        <v>395</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13622,7 +13681,7 @@
         <v>81</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>643</v>
+        <v>396</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>81</v>
@@ -13631,7 +13690,7 @@
         <v>81</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>644</v>
+        <v>397</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>81</v>
@@ -13645,10 +13704,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13662,7 +13721,7 @@
         <v>91</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>81</v>
@@ -13671,19 +13730,17 @@
         <v>92</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>367</v>
+        <v>211</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>646</v>
+        <v>399</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>648</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>649</v>
+        <v>401</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>81</v>
@@ -13732,7 +13789,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>650</v>
+        <v>402</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -13750,7 +13807,7 @@
         <v>81</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>651</v>
+        <v>403</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>81</v>
@@ -13759,24 +13816,24 @@
         <v>81</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>81</v>
+        <v>404</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>81</v>
+        <v>642</v>
       </c>
       <c r="AQ89" t="s" s="2">
-        <v>81</v>
+        <v>643</v>
       </c>
       <c r="AR89" t="s" s="2">
-        <v>81</v>
+        <v>644</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>652</v>
+        <v>645</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13799,17 +13856,17 @@
         <v>92</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>367</v>
+        <v>105</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>653</v>
+        <v>406</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>654</v>
+        <v>407</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>655</v>
+        <v>408</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>81</v>
@@ -13858,7 +13915,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>656</v>
+        <v>409</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -13867,7 +13924,7 @@
         <v>91</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>81</v>
+        <v>410</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>103</v>
@@ -13876,7 +13933,7 @@
         <v>81</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>651</v>
+        <v>411</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>81</v>
@@ -13885,7 +13942,7 @@
         <v>81</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>81</v>
+        <v>404</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>81</v>
@@ -13899,10 +13956,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>657</v>
+        <v>647</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>657</v>
+        <v>648</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13916,25 +13973,29 @@
         <v>91</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>315</v>
+        <v>111</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>658</v>
+        <v>413</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
+        <v>414</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>416</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>81</v>
       </c>
@@ -13982,7 +14043,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>657</v>
+        <v>417</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -14000,33 +14061,33 @@
         <v>81</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>660</v>
+        <v>418</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>661</v>
+        <v>81</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>81</v>
+        <v>404</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>81</v>
+        <v>649</v>
       </c>
       <c r="AQ91" t="s" s="2">
-        <v>81</v>
+        <v>643</v>
       </c>
       <c r="AR91" t="s" s="2">
-        <v>81</v>
+        <v>644</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>662</v>
+        <v>650</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>662</v>
+        <v>650</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14046,19 +14107,23 @@
         <v>81</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>211</v>
+        <v>651</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>212</v>
+        <v>652</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N92" s="2"/>
-      <c r="O92" s="2"/>
+        <v>653</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>655</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>81</v>
       </c>
@@ -14106,7 +14171,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>214</v>
+        <v>656</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14118,13 +14183,13 @@
         <v>81</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>215</v>
+        <v>657</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>81</v>
@@ -14133,7 +14198,7 @@
         <v>81</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>81</v>
+        <v>658</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>81</v>
@@ -14147,21 +14212,21 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>136</v>
+        <v>81</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>81</v>
@@ -14170,21 +14235,23 @@
         <v>81</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>137</v>
+        <v>660</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>138</v>
+        <v>661</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>218</v>
+        <v>662</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O93" s="2"/>
+        <v>663</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>664</v>
+      </c>
       <c r="P93" t="s" s="2">
         <v>81</v>
       </c>
@@ -14232,25 +14299,25 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>221</v>
+        <v>665</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>215</v>
+        <v>666</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>81</v>
@@ -14259,7 +14326,7 @@
         <v>81</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>81</v>
+        <v>667</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>81</v>
@@ -14273,45 +14340,45 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>323</v>
+        <v>81</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I94" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J94" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>137</v>
+        <v>369</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>324</v>
+        <v>669</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>325</v>
+        <v>670</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>140</v>
+        <v>671</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>146</v>
+        <v>672</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -14360,25 +14427,25 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>326</v>
+        <v>673</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>134</v>
+        <v>674</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>81</v>
@@ -14401,10 +14468,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>665</v>
+        <v>675</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>665</v>
+        <v>675</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14412,7 +14479,7 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="G95" t="s" s="2">
         <v>91</v>
@@ -14424,19 +14491,21 @@
         <v>81</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>273</v>
+        <v>369</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>666</v>
+        <v>676</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>667</v>
+        <v>677</v>
       </c>
       <c r="N95" s="2"/>
-      <c r="O95" s="2"/>
+      <c r="O95" t="s" s="2">
+        <v>678</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
       </c>
@@ -14484,10 +14553,10 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>665</v>
+        <v>679</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AH95" t="s" s="2">
         <v>91</v>
@@ -14502,7 +14571,7 @@
         <v>81</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>81</v>
@@ -14525,10 +14594,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>669</v>
+        <v>680</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>669</v>
+        <v>680</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14551,13 +14620,13 @@
         <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>185</v>
+        <v>315</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>670</v>
+        <v>681</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>671</v>
+        <v>682</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14584,13 +14653,13 @@
         <v>81</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>179</v>
+        <v>81</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>672</v>
+        <v>81</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>673</v>
+        <v>81</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>81</v>
@@ -14608,7 +14677,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>669</v>
+        <v>680</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14626,16 +14695,16 @@
         <v>81</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>363</v>
+        <v>683</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>674</v>
+        <v>684</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>675</v>
+        <v>81</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>81</v>
@@ -14649,10 +14718,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>676</v>
+        <v>685</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>676</v>
+        <v>685</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14663,7 +14732,7 @@
         <v>82</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>81</v>
@@ -14675,13 +14744,13 @@
         <v>81</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>185</v>
+        <v>211</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>677</v>
+        <v>212</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>678</v>
+        <v>213</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -14708,13 +14777,13 @@
         <v>81</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>179</v>
+        <v>81</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>679</v>
+        <v>81</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>680</v>
+        <v>81</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>81</v>
@@ -14732,31 +14801,31 @@
         <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>676</v>
+        <v>214</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>681</v>
+        <v>215</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>682</v>
+        <v>81</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>81</v>
@@ -14773,14 +14842,14 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -14799,15 +14868,17 @@
         <v>81</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>684</v>
+        <v>137</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>685</v>
+        <v>138</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>686</v>
-      </c>
-      <c r="N98" s="2"/>
+        <v>218</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>81</v>
@@ -14856,7 +14927,7 @@
         <v>81</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>683</v>
+        <v>221</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>82</v>
@@ -14868,19 +14939,19 @@
         <v>81</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>687</v>
+        <v>215</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>688</v>
+        <v>81</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>81</v>
@@ -14897,14 +14968,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>690</v>
+        <v>323</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14917,24 +14988,26 @@
         <v>81</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>691</v>
+        <v>137</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>692</v>
+        <v>324</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>693</v>
+        <v>325</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="O99" s="2"/>
+        <v>140</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>81</v>
       </c>
@@ -14982,7 +15055,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>689</v>
+        <v>326</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -14994,13 +15067,13 @@
         <v>81</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>695</v>
+        <v>134</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>81</v>
@@ -15023,10 +15096,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>696</v>
+        <v>688</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>696</v>
+        <v>688</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15034,10 +15107,10 @@
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>81</v>
@@ -15049,17 +15122,15 @@
         <v>81</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>697</v>
+        <v>273</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>698</v>
+        <v>689</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>700</v>
-      </c>
+        <v>690</v>
+      </c>
+      <c r="N100" s="2"/>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>81</v>
@@ -15108,13 +15179,13 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>696</v>
+        <v>688</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>81</v>
@@ -15126,29 +15197,653 @@
         <v>81</v>
       </c>
       <c r="AL100" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR100" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="101" hidden="true">
+      <c r="A101" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="N101" s="2"/>
+      <c r="O101" s="2"/>
+      <c r="P101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="AP101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR101" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="102" hidden="true">
+      <c r="A102" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>701</v>
       </c>
-      <c r="AM100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR100" t="s" s="2">
+      <c r="N102" s="2"/>
+      <c r="O102" s="2"/>
+      <c r="P102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="AO102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR102" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="103" hidden="true">
+      <c r="A103" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="N103" s="2"/>
+      <c r="O103" s="2"/>
+      <c r="P103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="AO103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR103" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="104" hidden="true">
+      <c r="A104" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="O104" s="2"/>
+      <c r="P104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR104" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="105" hidden="true">
+      <c r="A105" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="O105" s="2"/>
+      <c r="P105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR105" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR100">
+  <autoFilter ref="A1:AR105">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15158,7 +15853,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI99">
+  <conditionalFormatting sqref="A2:AI104">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4228" uniqueCount="725">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="726">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2032,7 +2032,10 @@
     <t>MedicationDispense.dosageInstruction.doseAndRate.dose[x].code</t>
   </si>
   <si>
-    <t>1575: source value from PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - UNITS (#52-113 &gt; 52.0113-2)</t>
+    <t>http://va.gov/fhir/ValueSet/VSVFDoseUnits</t>
+  </si>
+  <si>
+    <t>1575: terminologyMaps using VF_DoseUnits on PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - UNITS (#52-113 &gt; 52.0113-2)</t>
   </si>
   <si>
     <t>MedicationDispense.dosageInstruction.doseAndRate.rate[x]</t>
@@ -14019,13 +14022,11 @@
         <v>81</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>81</v>
+        <v>649</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -14073,7 +14074,7 @@
         <v>404</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AQ91" t="s" s="2">
         <v>643</v>
@@ -14084,10 +14085,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14110,19 +14111,19 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>81</v>
@@ -14171,7 +14172,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14189,7 +14190,7 @@
         <v>81</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>81</v>
@@ -14198,7 +14199,7 @@
         <v>81</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>81</v>
@@ -14212,10 +14213,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14238,19 +14239,19 @@
         <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -14299,7 +14300,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14317,7 +14318,7 @@
         <v>81</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>81</v>
@@ -14326,7 +14327,7 @@
         <v>81</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>81</v>
@@ -14340,10 +14341,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14369,16 +14370,16 @@
         <v>369</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -14427,7 +14428,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14445,7 +14446,7 @@
         <v>81</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>81</v>
@@ -14468,10 +14469,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14497,14 +14498,14 @@
         <v>369</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -14553,7 +14554,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14571,7 +14572,7 @@
         <v>81</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>81</v>
@@ -14594,10 +14595,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14623,10 +14624,10 @@
         <v>315</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14677,7 +14678,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14695,13 +14696,13 @@
         <v>81</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>81</v>
@@ -14718,10 +14719,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14842,10 +14843,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14968,10 +14969,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15096,10 +15097,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15125,10 +15126,10 @@
         <v>273</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -15179,7 +15180,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>91</v>
@@ -15197,7 +15198,7 @@
         <v>81</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>81</v>
@@ -15220,10 +15221,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15249,10 +15250,10 @@
         <v>185</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -15282,10 +15283,10 @@
         <v>179</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>81</v>
@@ -15303,7 +15304,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15327,10 +15328,10 @@
         <v>81</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>81</v>
@@ -15344,10 +15345,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15373,10 +15374,10 @@
         <v>185</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15406,10 +15407,10 @@
         <v>179</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>81</v>
@@ -15427,7 +15428,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15445,13 +15446,13 @@
         <v>81</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>81</v>
@@ -15468,10 +15469,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15494,13 +15495,13 @@
         <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15551,7 +15552,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15569,13 +15570,13 @@
         <v>81</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>81</v>
@@ -15592,14 +15593,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -15618,16 +15619,16 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15677,7 +15678,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -15695,7 +15696,7 @@
         <v>81</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>81</v>
@@ -15718,10 +15719,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15744,16 +15745,16 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15803,7 +15804,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -15821,7 +15822,7 @@
         <v>81</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="728">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -557,7 +557,7 @@
     <t>CombinedMedicationDispense.SupplyEvent.statusCode</t>
   </si>
   <si>
-    <t>1541: fixed value = completed when PRESCRIPTION - RELEASED DATE/TIME (#52-31) case not null</t>
+    <t>1541: fixed value = #completed when PRESCRIPTION - RELEASED DATE/TIME (#52-31) case not null</t>
   </si>
   <si>
     <t>MedicationDispense.statusReason[x]</t>
@@ -604,6 +604,13 @@
     <t>The category can be used to include where the medication is expected to be consumed or other types of dispenses.  Invariants can be used to bind to different value sets when profiling to bind.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;code value="outpatient"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>A code describing where the dispensed medication is expected to be consumed or administered.</t>
   </si>
   <si>
@@ -613,7 +620,7 @@
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication dispense"].value</t>
   </si>
   <si>
-    <t>1668: fixed value = outpatient</t>
+    <t>1668: fixed value = #outpatient</t>
   </si>
   <si>
     <t>MedicationDispense.medication[x]</t>
@@ -1149,6 +1156,13 @@
     <t>Indicates the type of dispensing event that is performed. For example, Trial Fill, Completion of Trial, Partial Fill, Emergency Fill, Samples, etc.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;code value="FF"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>http://terminology.hl7.org/ValueSet/v3-ActPharmacySupplyType</t>
   </si>
   <si>
@@ -1161,7 +1175,7 @@
     <t>RXD-33-Dispense Type</t>
   </si>
   <si>
-    <t>1708: fixed value = FF</t>
+    <t>1708: fixed value = #FF</t>
   </si>
   <si>
     <t>MedicationDispense.quantity</t>
@@ -4447,7 +4461,7 @@
         <v>81</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>81</v>
+        <v>189</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>81</v>
@@ -4465,10 +4479,10 @@
         <v>115</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>81</v>
@@ -4504,7 +4518,7 @@
         <v>81</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>81</v>
@@ -4516,7 +4530,7 @@
         <v>81</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AQ15" t="s" s="2">
         <v>81</v>
@@ -4527,10 +4541,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4553,16 +4567,16 @@
         <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4591,26 +4605,26 @@
         <v>179</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AC16" s="2"/>
       <c r="AD16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>91</v>
@@ -4625,19 +4639,19 @@
         <v>103</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>81</v>
@@ -4651,13 +4665,13 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>81</v>
@@ -4682,13 +4696,13 @@
         <v>185</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4717,10 +4731,10 @@
         <v>179</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>81</v>
@@ -4738,7 +4752,7 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>91</v>
@@ -4753,19 +4767,19 @@
         <v>103</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>81</v>
@@ -4779,10 +4793,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4805,13 +4819,13 @@
         <v>81</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4862,7 +4876,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -4880,7 +4894,7 @@
         <v>81</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>81</v>
@@ -4903,10 +4917,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4935,7 +4949,7 @@
         <v>138</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>140</v>
@@ -4976,19 +4990,19 @@
         <v>81</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -5006,7 +5020,7 @@
         <v>81</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>81</v>
@@ -5029,10 +5043,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -5055,19 +5069,19 @@
         <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>81</v>
@@ -5116,7 +5130,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -5134,7 +5148,7 @@
         <v>81</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>81</v>
@@ -5143,7 +5157,7 @@
         <v>81</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>81</v>
@@ -5157,10 +5171,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5183,13 +5197,13 @@
         <v>81</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -5240,7 +5254,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -5258,7 +5272,7 @@
         <v>81</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>81</v>
@@ -5281,10 +5295,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5313,7 +5327,7 @@
         <v>138</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>140</v>
@@ -5354,19 +5368,19 @@
         <v>81</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
@@ -5384,7 +5398,7 @@
         <v>81</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>81</v>
@@ -5407,10 +5421,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5436,16 +5450,16 @@
         <v>105</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>81</v>
@@ -5494,7 +5508,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -5512,7 +5526,7 @@
         <v>81</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>81</v>
@@ -5521,7 +5535,7 @@
         <v>81</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>81</v>
@@ -5535,10 +5549,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5561,16 +5575,16 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5620,7 +5634,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -5638,7 +5652,7 @@
         <v>81</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>81</v>
@@ -5647,7 +5661,7 @@
         <v>81</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>81</v>
@@ -5661,10 +5675,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5690,14 +5704,14 @@
         <v>111</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
@@ -5746,7 +5760,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -5764,7 +5778,7 @@
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>81</v>
@@ -5773,13 +5787,13 @@
         <v>81</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AR25" t="s" s="2">
         <v>81</v>
@@ -5787,10 +5801,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5813,17 +5827,17 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>81</v>
@@ -5872,7 +5886,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5890,7 +5904,7 @@
         <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>81</v>
@@ -5899,7 +5913,7 @@
         <v>81</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>81</v>
@@ -5913,10 +5927,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5939,19 +5953,19 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -6000,7 +6014,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -6018,7 +6032,7 @@
         <v>81</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>81</v>
@@ -6027,7 +6041,7 @@
         <v>81</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>81</v>
@@ -6041,10 +6055,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6067,19 +6081,19 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>81</v>
@@ -6128,7 +6142,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -6146,7 +6160,7 @@
         <v>81</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>81</v>
@@ -6155,13 +6169,13 @@
         <v>81</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>81</v>
@@ -6169,10 +6183,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6195,16 +6209,16 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6254,7 +6268,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -6269,22 +6283,22 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>81</v>
@@ -6295,10 +6309,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6321,13 +6335,13 @@
         <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -6378,7 +6392,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -6393,10 +6407,10 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>81</v>
@@ -6419,10 +6433,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6445,13 +6459,13 @@
         <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6502,7 +6516,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6520,10 +6534,10 @@
         <v>81</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>81</v>
@@ -6543,10 +6557,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6569,13 +6583,13 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6626,7 +6640,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6641,10 +6655,10 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>81</v>
@@ -6667,10 +6681,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6693,13 +6707,13 @@
         <v>81</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6750,7 +6764,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6768,7 +6782,7 @@
         <v>81</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>81</v>
@@ -6791,10 +6805,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6823,7 +6837,7 @@
         <v>138</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>140</v>
@@ -6876,7 +6890,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6894,7 +6908,7 @@
         <v>81</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>81</v>
@@ -6917,14 +6931,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6946,10 +6960,10 @@
         <v>137</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>140</v>
@@ -7004,7 +7018,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -7045,10 +7059,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7074,14 +7088,14 @@
         <v>185</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -7109,10 +7123,10 @@
         <v>179</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>81</v>
@@ -7130,7 +7144,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -7148,7 +7162,7 @@
         <v>81</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>81</v>
@@ -7171,10 +7185,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7197,13 +7211,13 @@
         <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7254,7 +7268,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>91</v>
@@ -7269,10 +7283,10 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>81</v>
@@ -7284,7 +7298,7 @@
         <v>81</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>81</v>
@@ -7295,10 +7309,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7321,13 +7335,13 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7378,7 +7392,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7396,7 +7410,7 @@
         <v>81</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>81</v>
@@ -7408,21 +7422,21 @@
         <v>81</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7445,16 +7459,16 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7504,7 +7518,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7519,25 +7533,25 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>81</v>
@@ -7545,10 +7559,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7574,10 +7588,10 @@
         <v>185</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7589,7 +7603,7 @@
         <v>81</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>81</v>
+        <v>364</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>81</v>
@@ -7607,10 +7621,10 @@
         <v>179</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>81</v>
@@ -7628,7 +7642,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7646,19 +7660,19 @@
         <v>81</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>81</v>
@@ -7669,10 +7683,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7695,13 +7709,13 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7752,7 +7766,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7770,16 +7784,16 @@
         <v>81</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>81</v>
@@ -7793,10 +7807,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7819,13 +7833,13 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7876,7 +7890,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7894,7 +7908,7 @@
         <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>81</v>
@@ -7917,10 +7931,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7949,7 +7963,7 @@
         <v>138</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>140</v>
@@ -7990,19 +8004,19 @@
         <v>81</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -8020,7 +8034,7 @@
         <v>81</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>81</v>
@@ -8043,10 +8057,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8069,19 +8083,19 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -8130,7 +8144,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -8148,7 +8162,7 @@
         <v>81</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>81</v>
@@ -8157,24 +8171,24 @@
         <v>81</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8200,20 +8214,20 @@
         <v>111</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q45" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="R45" t="s" s="2">
         <v>81</v>
@@ -8237,10 +8251,10 @@
         <v>167</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>81</v>
@@ -8258,7 +8272,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8276,7 +8290,7 @@
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>81</v>
@@ -8285,7 +8299,7 @@
         <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>81</v>
@@ -8299,10 +8313,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8325,17 +8339,17 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -8384,7 +8398,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8402,7 +8416,7 @@
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>81</v>
@@ -8411,7 +8425,7 @@
         <v>81</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>81</v>
@@ -8425,10 +8439,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8454,14 +8468,14 @@
         <v>105</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
@@ -8510,7 +8524,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8519,7 +8533,7 @@
         <v>91</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>103</v>
@@ -8528,7 +8542,7 @@
         <v>81</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>81</v>
@@ -8537,7 +8551,7 @@
         <v>81</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>81</v>
@@ -8551,10 +8565,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8580,16 +8594,16 @@
         <v>111</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -8638,7 +8652,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8656,7 +8670,7 @@
         <v>81</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>81</v>
@@ -8665,7 +8679,7 @@
         <v>81</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>81</v>
@@ -8679,10 +8693,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8705,13 +8719,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8762,7 +8776,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8780,7 +8794,7 @@
         <v>81</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>81</v>
@@ -8789,24 +8803,24 @@
         <v>81</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8829,13 +8843,13 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8886,7 +8900,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8904,19 +8918,19 @@
         <v>81</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>81</v>
@@ -8927,10 +8941,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8953,13 +8967,13 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -9010,7 +9024,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -9025,22 +9039,22 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>81</v>
@@ -9051,10 +9065,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9077,13 +9091,13 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -9134,7 +9148,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9152,16 +9166,16 @@
         <v>81</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>81</v>
@@ -9175,10 +9189,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9201,13 +9215,13 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -9258,7 +9272,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -9276,7 +9290,7 @@
         <v>81</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>81</v>
@@ -9299,10 +9313,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9331,7 +9345,7 @@
         <v>138</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>140</v>
@@ -9372,19 +9386,19 @@
         <v>81</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9402,7 +9416,7 @@
         <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>81</v>
@@ -9425,10 +9439,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9451,16 +9465,16 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9510,7 +9524,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9519,7 +9533,7 @@
         <v>91</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>103</v>
@@ -9551,10 +9565,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9580,13 +9594,13 @@
         <v>105</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9612,13 +9626,13 @@
         <v>81</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>81</v>
@@ -9636,7 +9650,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9677,10 +9691,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9706,13 +9720,13 @@
         <v>149</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9762,7 +9776,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9780,7 +9794,7 @@
         <v>81</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>81</v>
@@ -9803,10 +9817,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9829,16 +9843,16 @@
         <v>92</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9888,7 +9902,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9918,21 +9932,21 @@
         <v>81</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR58" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9955,13 +9969,13 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -10012,7 +10026,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10030,13 +10044,13 @@
         <v>81</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>81</v>
@@ -10053,10 +10067,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10079,13 +10093,13 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -10136,7 +10150,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10151,10 +10165,10 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>81</v>
@@ -10163,7 +10177,7 @@
         <v>81</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>81</v>
@@ -10177,10 +10191,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10203,13 +10217,13 @@
         <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -10260,7 +10274,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -10278,7 +10292,7 @@
         <v>81</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>81</v>
@@ -10301,10 +10315,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10333,7 +10347,7 @@
         <v>138</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>140</v>
@@ -10374,19 +10388,19 @@
         <v>81</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10404,7 +10418,7 @@
         <v>81</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>81</v>
@@ -10427,10 +10441,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10453,16 +10467,16 @@
         <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10512,7 +10526,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10530,7 +10544,7 @@
         <v>81</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>81</v>
@@ -10553,10 +10567,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10579,13 +10593,13 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10636,7 +10650,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10654,7 +10668,7 @@
         <v>81</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>81</v>
@@ -10677,10 +10691,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10703,13 +10717,13 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10760,7 +10774,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>91</v>
@@ -10778,7 +10792,7 @@
         <v>81</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>81</v>
@@ -10790,7 +10804,7 @@
         <v>134</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>81</v>
@@ -10801,10 +10815,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10827,16 +10841,16 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10886,7 +10900,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10904,7 +10918,7 @@
         <v>81</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>81</v>
@@ -10927,10 +10941,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10953,13 +10967,13 @@
         <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -11010,7 +11024,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -11028,7 +11042,7 @@
         <v>81</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>81</v>
@@ -11051,10 +11065,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11083,7 +11097,7 @@
         <v>138</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>140</v>
@@ -11124,19 +11138,19 @@
         <v>81</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -11154,7 +11168,7 @@
         <v>81</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>81</v>
@@ -11177,14 +11191,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -11206,10 +11220,10 @@
         <v>137</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>140</v>
@@ -11264,7 +11278,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11305,10 +11319,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11331,17 +11345,17 @@
         <v>92</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>81</v>
@@ -11390,7 +11404,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11408,7 +11422,7 @@
         <v>81</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>81</v>
@@ -11417,7 +11431,7 @@
         <v>81</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>81</v>
@@ -11431,10 +11445,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11457,17 +11471,17 @@
         <v>92</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>81</v>
@@ -11516,7 +11530,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11534,7 +11548,7 @@
         <v>81</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>81</v>
@@ -11543,24 +11557,24 @@
         <v>81</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11586,16 +11600,16 @@
         <v>185</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -11623,10 +11637,10 @@
         <v>179</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>81</v>
@@ -11644,7 +11658,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11662,7 +11676,7 @@
         <v>81</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>81</v>
@@ -11671,7 +11685,7 @@
         <v>81</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>81</v>
@@ -11685,10 +11699,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11711,13 +11725,13 @@
         <v>92</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11768,7 +11782,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11786,7 +11800,7 @@
         <v>81</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>81</v>
@@ -11795,13 +11809,13 @@
         <v>81</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AQ73" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="AR73" t="s" s="2">
         <v>81</v>
@@ -11809,10 +11823,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11835,19 +11849,19 @@
         <v>92</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
@@ -11896,7 +11910,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -11914,7 +11928,7 @@
         <v>81</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>81</v>
@@ -11937,10 +11951,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11963,16 +11977,16 @@
         <v>92</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -12001,10 +12015,10 @@
         <v>179</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>81</v>
@@ -12022,7 +12036,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12040,7 +12054,7 @@
         <v>81</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>81</v>
@@ -12049,7 +12063,7 @@
         <v>81</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>81</v>
@@ -12063,10 +12077,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12092,16 +12106,16 @@
         <v>185</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>81</v>
@@ -12129,10 +12143,10 @@
         <v>179</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>81</v>
@@ -12150,7 +12164,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12168,7 +12182,7 @@
         <v>81</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>81</v>
@@ -12177,7 +12191,7 @@
         <v>81</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>81</v>
@@ -12191,10 +12205,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12220,14 +12234,14 @@
         <v>185</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>81</v>
@@ -12255,10 +12269,10 @@
         <v>179</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>81</v>
@@ -12276,7 +12290,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12294,7 +12308,7 @@
         <v>81</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>81</v>
@@ -12303,7 +12317,7 @@
         <v>81</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>81</v>
@@ -12317,10 +12331,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12346,16 +12360,16 @@
         <v>185</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>81</v>
@@ -12383,10 +12397,10 @@
         <v>179</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>81</v>
@@ -12404,7 +12418,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12422,7 +12436,7 @@
         <v>81</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>81</v>
@@ -12431,7 +12445,7 @@
         <v>81</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>81</v>
@@ -12445,10 +12459,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12471,13 +12485,13 @@
         <v>92</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12528,7 +12542,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12555,7 +12569,7 @@
         <v>81</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>81</v>
@@ -12569,10 +12583,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12595,13 +12609,13 @@
         <v>81</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12652,7 +12666,7 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -12670,7 +12684,7 @@
         <v>81</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>81</v>
@@ -12693,10 +12707,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12725,7 +12739,7 @@
         <v>138</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>140</v>
@@ -12766,19 +12780,19 @@
         <v>81</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -12796,7 +12810,7 @@
         <v>81</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>81</v>
@@ -12819,10 +12833,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12848,14 +12862,14 @@
         <v>185</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>81</v>
@@ -12883,10 +12897,10 @@
         <v>179</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>81</v>
@@ -12904,7 +12918,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -12931,7 +12945,7 @@
         <v>81</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>81</v>
@@ -12945,10 +12959,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12971,19 +12985,19 @@
         <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>81</v>
@@ -13020,17 +13034,17 @@
         <v>81</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AC83" s="2"/>
       <c r="AD83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13048,7 +13062,7 @@
         <v>81</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>81</v>
@@ -13057,7 +13071,7 @@
         <v>81</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>81</v>
@@ -13071,13 +13085,13 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>81</v>
@@ -13099,19 +13113,19 @@
         <v>81</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -13160,7 +13174,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13169,16 +13183,16 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>81</v>
@@ -13187,7 +13201,7 @@
         <v>81</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>81</v>
@@ -13201,10 +13215,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13227,13 +13241,13 @@
         <v>81</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -13284,7 +13298,7 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -13302,7 +13316,7 @@
         <v>81</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>81</v>
@@ -13325,10 +13339,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13357,7 +13371,7 @@
         <v>138</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N86" t="s" s="2">
         <v>140</v>
@@ -13398,19 +13412,19 @@
         <v>81</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
@@ -13428,7 +13442,7 @@
         <v>81</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>81</v>
@@ -13451,10 +13465,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13477,19 +13491,19 @@
         <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>81</v>
@@ -13538,7 +13552,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13556,7 +13570,7 @@
         <v>81</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>81</v>
@@ -13565,24 +13579,24 @@
         <v>81</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="AQ87" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="AR87" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13608,20 +13622,20 @@
         <v>111</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q88" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="R88" t="s" s="2">
         <v>81</v>
@@ -13645,10 +13659,10 @@
         <v>167</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>81</v>
@@ -13666,7 +13680,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13684,7 +13698,7 @@
         <v>81</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>81</v>
@@ -13693,7 +13707,7 @@
         <v>81</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>81</v>
@@ -13707,10 +13721,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13733,17 +13747,17 @@
         <v>92</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>81</v>
@@ -13792,7 +13806,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -13810,7 +13824,7 @@
         <v>81</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>81</v>
@@ -13819,24 +13833,24 @@
         <v>81</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="AQ89" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AR89" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13862,14 +13876,14 @@
         <v>105</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>81</v>
@@ -13918,7 +13932,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -13927,7 +13941,7 @@
         <v>91</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>103</v>
@@ -13936,7 +13950,7 @@
         <v>81</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>81</v>
@@ -13945,7 +13959,7 @@
         <v>81</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>81</v>
@@ -13959,10 +13973,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13988,16 +14002,16 @@
         <v>111</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>81</v>
@@ -14026,7 +14040,7 @@
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -14044,7 +14058,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -14062,7 +14076,7 @@
         <v>81</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>81</v>
@@ -14071,24 +14085,24 @@
         <v>81</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="AQ91" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AR91" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14111,19 +14125,19 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>81</v>
@@ -14172,7 +14186,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14190,7 +14204,7 @@
         <v>81</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>81</v>
@@ -14199,7 +14213,7 @@
         <v>81</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>81</v>
@@ -14213,10 +14227,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14239,19 +14253,19 @@
         <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -14300,7 +14314,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14318,7 +14332,7 @@
         <v>81</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>81</v>
@@ -14327,7 +14341,7 @@
         <v>81</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>81</v>
@@ -14341,10 +14355,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14367,19 +14381,19 @@
         <v>92</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -14428,7 +14442,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14446,7 +14460,7 @@
         <v>81</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>81</v>
@@ -14469,10 +14483,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14495,17 +14509,17 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -14554,7 +14568,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14572,7 +14586,7 @@
         <v>81</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>81</v>
@@ -14595,10 +14609,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14621,13 +14635,13 @@
         <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14678,7 +14692,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14696,13 +14710,13 @@
         <v>81</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>81</v>
@@ -14719,10 +14733,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14745,13 +14759,13 @@
         <v>81</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -14802,7 +14816,7 @@
         <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>
@@ -14820,7 +14834,7 @@
         <v>81</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>81</v>
@@ -14843,10 +14857,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14875,7 +14889,7 @@
         <v>138</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N98" t="s" s="2">
         <v>140</v>
@@ -14928,7 +14942,7 @@
         <v>81</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>82</v>
@@ -14946,7 +14960,7 @@
         <v>81</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>81</v>
@@ -14969,14 +14983,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14998,10 +15012,10 @@
         <v>137</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>140</v>
@@ -15056,7 +15070,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -15097,10 +15111,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15123,13 +15137,13 @@
         <v>81</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -15180,7 +15194,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>91</v>
@@ -15198,7 +15212,7 @@
         <v>81</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>81</v>
@@ -15221,10 +15235,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15250,10 +15264,10 @@
         <v>185</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -15283,10 +15297,10 @@
         <v>179</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>81</v>
@@ -15304,7 +15318,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15322,16 +15336,16 @@
         <v>81</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>81</v>
@@ -15345,10 +15359,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15374,10 +15388,10 @@
         <v>185</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15407,10 +15421,10 @@
         <v>179</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>81</v>
@@ -15428,7 +15442,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15446,13 +15460,13 @@
         <v>81</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>81</v>
@@ -15469,10 +15483,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15495,13 +15509,13 @@
         <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15552,7 +15566,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15570,13 +15584,13 @@
         <v>81</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>81</v>
@@ -15593,14 +15607,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -15619,16 +15633,16 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15678,7 +15692,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -15696,7 +15710,7 @@
         <v>81</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>81</v>
@@ -15719,10 +15733,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15745,16 +15759,16 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15804,7 +15818,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -15822,7 +15836,7 @@
         <v>81</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -835,9 +835,7 @@
     <t>1545: source value from PRESCRIPTION - DRUG &gt; DRUG - PSNDF VA PRODUCT NAME ENTRY (#52-6 &gt; 50-22)</t>
   </si>
   <si>
-    <t>Dim.LocalDrug.DrugNameWithoutDoseIEN
-Dim.LocalDrug.NationalDrugIEN
-Dim.LocalDrug.NationalDrugIEN</t>
+    <t>Dim.LocalDrug.DrugNameWithoutDoseIEN,Dim.LocalDrug.NationalDrugIEN,Dim.LocalDrug.NationalDrugIEN</t>
   </si>
   <si>
     <t>MedicationDispense.medication[x]:medicationCodeableConcept.coding.display</t>
@@ -925,13 +923,7 @@
     <t>1544: source value from PRESCRIPTION - DRUG &gt; DRUG - GENERIC NAME (#52-6 &gt; 50-.01)</t>
   </si>
   <si>
-    <t>Dim.IVAdditiveIngredient.LocalDrugNameWithDose
-Dim.IVSolutionIngredient.LocalDrugNameWithDose
-Dim.LocalDrug.CorrespondingInpatientLocalDrugNameWithDose
-Dim.LocalDrug.CorrespondingOutpatientLocalDrugNameWithDose
-Dim.LocalDrug.LocalDrugNameWithDose
-Dim.LocalDrug.LocalDrugNameWithDose
-RxOut.RxOutpatFill.LocalDrugNameWithDose</t>
+    <t>Dim.IVAdditiveIngredient.LocalDrugNameWithDose,Dim.IVSolutionIngredient.LocalDrugNameWithDose,Dim.LocalDrug.CorrespondingInpatientLocalDrugNameWithDose,Dim.LocalDrug.CorrespondingOutpatientLocalDrugNameWithDose,Dim.LocalDrug.LocalDrugNameWithDose,Dim.LocalDrug.LocalDrugNameWithDose,RxOut.RxOutpatFill.LocalDrugNameWithDose</t>
   </si>
   <si>
     <t>MedicationDispense.subject</t>
@@ -2643,7 +2635,7 @@
     <col min="40" max="40" width="73.296875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="148.69921875" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="61.98046875" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="255.0" customWidth="true" bestFit="true"/>
     <col min="44" max="44" width="40.984375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,15 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
+    <t>Mapping: Virtual Patient Record (VPR)</t>
+  </si>
+  <si>
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
@@ -250,15 +259,6 @@
   </si>
   <si>
     <t>Mapping: HL7 v2 Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
-  </si>
-  <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
   </si>
   <si>
     <t/>
@@ -545,6 +545,9 @@
     <t>http://hl7.org/fhir/ValueSet/medicationdispense-status|4.0.1</t>
   </si>
   <si>
+    <t>1541: fixed value = #completed when PRESCRIPTION - RELEASED DATE/TIME (#52-31) case not null</t>
+  </si>
+  <si>
     <t>Event.status</t>
   </si>
   <si>
@@ -555,9 +558,6 @@
   </si>
   <si>
     <t>CombinedMedicationDispense.SupplyEvent.statusCode</t>
-  </si>
-  <si>
-    <t>1541: fixed value = #completed when PRESCRIPTION - RELEASED DATE/TIME (#52-31) case not null</t>
   </si>
   <si>
     <t>MedicationDispense.statusReason[x]</t>
@@ -617,10 +617,10 @@
     <t>http://hl7.org/fhir/ValueSet/medicationdispense-category</t>
   </si>
   <si>
+    <t>1668: fixed value = #outpatient</t>
+  </si>
+  <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication dispense"].value</t>
-  </si>
-  <si>
-    <t>1668: fixed value = #outpatient</t>
   </si>
   <si>
     <t>MedicationDispense.medication[x]</t>
@@ -826,16 +826,16 @@
     <t>Coding.code</t>
   </si>
   <si>
+    <t>1545: source value from PRESCRIPTION - DRUG &gt; DRUG - PSNDF VA PRODUCT NAME ENTRY (#52-6 &gt; 50-22)</t>
+  </si>
+  <si>
+    <t>Dim.LocalDrug.DrugNameWithoutDoseIEN,Dim.LocalDrug.NationalDrugIEN,Dim.LocalDrug.NationalDrugIEN</t>
+  </si>
+  <si>
     <t>./code</t>
   </si>
   <si>
     <t>C*E.1</t>
-  </si>
-  <si>
-    <t>1545: source value from PRESCRIPTION - DRUG &gt; DRUG - PSNDF VA PRODUCT NAME ENTRY (#52-6 &gt; 50-22)</t>
-  </si>
-  <si>
-    <t>Dim.LocalDrug.DrugNameWithoutDoseIEN,Dim.LocalDrug.NationalDrugIEN,Dim.LocalDrug.NationalDrugIEN</t>
   </si>
   <si>
     <t>MedicationDispense.medication[x]:medicationCodeableConcept.coding.display</t>
@@ -914,16 +914,16 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
+    <t>1544: source value from PRESCRIPTION - DRUG &gt; DRUG - GENERIC NAME (#52-6 &gt; 50-.01)</t>
+  </si>
+  <si>
+    <t>Dim.IVAdditiveIngredient.LocalDrugNameWithDose,Dim.IVSolutionIngredient.LocalDrugNameWithDose,Dim.LocalDrug.CorrespondingInpatientLocalDrugNameWithDose,Dim.LocalDrug.CorrespondingOutpatientLocalDrugNameWithDose,Dim.LocalDrug.LocalDrugNameWithDose,Dim.LocalDrug.LocalDrugNameWithDose,RxOut.RxOutpatFill.LocalDrugNameWithDose</t>
+  </si>
+  <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>1544: source value from PRESCRIPTION - DRUG &gt; DRUG - GENERIC NAME (#52-6 &gt; 50-.01)</t>
-  </si>
-  <si>
-    <t>Dim.IVAdditiveIngredient.LocalDrugNameWithDose,Dim.IVSolutionIngredient.LocalDrugNameWithDose,Dim.LocalDrug.CorrespondingInpatientLocalDrugNameWithDose,Dim.LocalDrug.CorrespondingOutpatientLocalDrugNameWithDose,Dim.LocalDrug.LocalDrugNameWithDose,Dim.LocalDrug.LocalDrugNameWithDose,RxOut.RxOutpatFill.LocalDrugNameWithDose</t>
   </si>
   <si>
     <t>MedicationDispense.subject</t>
@@ -942,6 +942,9 @@
     <t>SubstanceAdministration-&gt;subject-&gt;Patient.</t>
   </si>
   <si>
+    <t>820: reference from PRESCRIPTION - PATIENT (#52-2)</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -952,9 +955,6 @@
   </si>
   <si>
     <t>PID-3-Patient ID List</t>
-  </si>
-  <si>
-    <t>820: reference from PRESCRIPTION - PATIENT (#52-2)</t>
   </si>
   <si>
     <t>MedicationDispense.context</t>
@@ -1071,13 +1071,13 @@
     <t>The device, practitioner, etc. who performed the action.  It should be assumed that the actor is the dispenser of the medication.</t>
   </si>
   <si>
+    <t>1711: reference from PRESCRIPTION - DIVISION (#52-20)</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
     <t>.role</t>
-  </si>
-  <si>
-    <t>1711: reference from PRESCRIPTION - DIVISION (#52-20)</t>
   </si>
   <si>
     <t>MedicationDispense.location</t>
@@ -1093,16 +1093,16 @@
     <t>The principal physical location where the dispense was performed.</t>
   </si>
   <si>
+    <t>821: reference from PRESCRIPTION - CLINIC (#52-5)</t>
+  </si>
+  <si>
+    <t>RxOut.RxOutpatFill.PrescribingDivisionIEN</t>
+  </si>
+  <si>
+    <t>Pharmacy: facility</t>
+  </si>
+  <si>
     <t>.participation[typeCode=LOC].role</t>
-  </si>
-  <si>
-    <t>821: reference from PRESCRIPTION - CLINIC (#52-5)</t>
-  </si>
-  <si>
-    <t>RxOut.RxOutpatFill.PrescribingDivisionIEN</t>
-  </si>
-  <si>
-    <t>Pharmacy: facility</t>
   </si>
   <si>
     <t>MedicationDispense.authorizingPrescription</t>
@@ -1121,6 +1121,12 @@
     <t>Maps to basedOn in Event logical model.</t>
   </si>
   <si>
+    <t>822: source value from PRESCRIPTION - PLACER ORDER # (#52-39.3)</t>
+  </si>
+  <si>
+    <t>RxOut.RxOutpat.CPRSOrderEntryNumber</t>
+  </si>
+  <si>
     <t>Event.basedOn</t>
   </si>
   <si>
@@ -1131,12 +1137,6 @@
   </si>
   <si>
     <t>ORC-2 Placer Order Number</t>
-  </si>
-  <si>
-    <t>822: source value from PRESCRIPTION - PLACER ORDER # (#52-39.3)</t>
-  </si>
-  <si>
-    <t>RxOut.RxOutpat.CPRSOrderEntryNumber</t>
   </si>
   <si>
     <t>MedicationDispense.type</t>
@@ -1158,6 +1158,9 @@
     <t>http://terminology.hl7.org/ValueSet/v3-ActPharmacySupplyType</t>
   </si>
   <si>
+    <t>1708: fixed value = #FF</t>
+  </si>
+  <si>
     <t>.code</t>
   </si>
   <si>
@@ -1165,9 +1168,6 @@
   </si>
   <si>
     <t>RXD-33-Dispense Type</t>
-  </si>
-  <si>
-    <t>1708: fixed value = #FF</t>
   </si>
   <si>
     <t>MedicationDispense.quantity</t>
@@ -1220,16 +1220,16 @@
     <t>Quantity.value</t>
   </si>
   <si>
+    <t>823: source value from PRESCRIPTION - QTY (#52-7)</t>
+  </si>
+  <si>
+    <t>Pharmacy: quantity</t>
+  </si>
+  <si>
     <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
   </si>
   <si>
     <t>SN.2  / CQ - N/A</t>
-  </si>
-  <si>
-    <t>823: source value from PRESCRIPTION - QTY (#52-7)</t>
-  </si>
-  <si>
-    <t>Pharmacy: quantity</t>
   </si>
   <si>
     <t>MedicationDispense.quantity.comparator</t>
@@ -1333,6 +1333,12 @@
   </si>
   <si>
     <t>The amount of medication expressed as a timing amount.</t>
+  </si>
+  <si>
+    <t>826: source value from PRESCRIPTION - DAYS SUPPLY (#52-8)</t>
+  </si>
+  <si>
+    <t>Pharmacy: daysSupply</t>
   </si>
   <si>
     <t>effectiveUseTime</t>
@@ -1344,12 +1350,6 @@
 For backwards compatibility, ORC.7 was permitted through v2.6.  Both forms (field and segment) may be present in v2.5, v2.5.1, and v2.6</t>
   </si>
   <si>
-    <t>826: source value from PRESCRIPTION - DAYS SUPPLY (#52-8)</t>
-  </si>
-  <si>
-    <t>Pharmacy: daysSupply</t>
-  </si>
-  <si>
     <t>MedicationDispense.whenPrepared</t>
   </si>
   <si>
@@ -1363,6 +1363,9 @@
     <t>The time when the dispensed product was packaged and reviewed.</t>
   </si>
   <si>
+    <t>1548: source value from PRESCRIPTION - FILL DATE (#52-22)</t>
+  </si>
+  <si>
     <t>.effectiveTime[xmi:type=IVL_TS].low</t>
   </si>
   <si>
@@ -1372,9 +1375,6 @@
     <t>RXD-3-Date/Time Dispensed</t>
   </si>
   <si>
-    <t>1548: source value from PRESCRIPTION - FILL DATE (#52-22)</t>
-  </si>
-  <si>
     <t>MedicationDispense.whenHandedOver</t>
   </si>
   <si>
@@ -1384,13 +1384,13 @@
     <t>The time the dispensed product was provided to the patient or their representative.</t>
   </si>
   <si>
+    <t>832: source value from PRESCRIPTION - RELEASED DATE/TIME (#52-31)</t>
+  </si>
+  <si>
     <t>Event.occurrence[x]</t>
   </si>
   <si>
     <t>.effectiveTime[xmi:type=IVL_TS].high</t>
-  </si>
-  <si>
-    <t>832: source value from PRESCRIPTION - RELEASED DATE/TIME (#52-31)</t>
   </si>
   <si>
     <t>MedicationDispense.destination</t>
@@ -1603,10 +1603,10 @@
     <t>Annotation.text</t>
   </si>
   <si>
+    <t>1716: source value from PRESCRIPTION - REMARKS (#52-12)</t>
+  </si>
+  <si>
     <t>Act.text</t>
-  </si>
-  <si>
-    <t>1716: source value from PRESCRIPTION - REMARKS (#52-12)</t>
   </si>
   <si>
     <t>MedicationDispense.dosageInstruction</t>
@@ -1678,13 +1678,13 @@
     <t>Dosage.text</t>
   </si>
   <si>
+    <t>838: source value from PRESCRIPTION - SIG (#52-10)</t>
+  </si>
+  <si>
+    <t>Pharmacy: sig</t>
+  </si>
+  <si>
     <t>RXO-6; RXE-21</t>
-  </si>
-  <si>
-    <t>838: source value from PRESCRIPTION - SIG (#52-10)</t>
-  </si>
-  <si>
-    <t>Pharmacy: sig</t>
   </si>
   <si>
     <t>MedicationDispense.dosageInstruction.additionalInstruction</t>
@@ -2629,14 +2629,14 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="148.69921875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="73.296875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="148.69921875" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="73.296875" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="255.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2873,19 +2873,19 @@
         <v>87</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM2" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN2" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AO2" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="AM2" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN2" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO2" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP2" t="s" s="2">
         <v>81</v>
@@ -3504,16 +3504,16 @@
         <v>81</v>
       </c>
       <c r="AL7" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM7" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN7" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO7" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO7" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP7" t="s" s="2">
         <v>81</v>
@@ -3630,16 +3630,16 @@
         <v>81</v>
       </c>
       <c r="AL8" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM8" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN8" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO8" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AM8" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN8" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO8" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP8" t="s" s="2">
         <v>81</v>
@@ -3756,16 +3756,16 @@
         <v>81</v>
       </c>
       <c r="AL9" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM9" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN9" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO9" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AM9" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN9" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO9" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP9" t="s" s="2">
         <v>81</v>
@@ -3884,16 +3884,16 @@
         <v>81</v>
       </c>
       <c r="AL10" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM10" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN10" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO10" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AM10" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN10" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO10" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP10" t="s" s="2">
         <v>81</v>
@@ -4007,25 +4007,25 @@
         <v>103</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM11" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN11" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AO11" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AP11" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="AQ11" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ11" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR11" t="s" s="2">
         <v>81</v>
@@ -4131,19 +4131,19 @@
         <v>103</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN12" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="AL12" t="s" s="2">
+      <c r="AO12" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO12" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP12" t="s" s="2">
         <v>81</v>
@@ -4260,22 +4260,22 @@
         <v>170</v>
       </c>
       <c r="AL13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN13" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="AM13" t="s" s="2">
+      <c r="AO13" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="AN13" t="s" s="2">
+      <c r="AP13" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="AO13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP13" t="s" s="2">
+      <c r="AQ13" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="AQ13" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR13" t="s" s="2">
         <v>81</v>
@@ -4381,19 +4381,19 @@
         <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN14" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>81</v>
@@ -4507,10 +4507,10 @@
         <v>103</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>81</v>
+        <v>192</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>192</v>
+        <v>81</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>81</v>
@@ -4519,10 +4519,10 @@
         <v>81</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>81</v>
+        <v>193</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>193</v>
+        <v>81</v>
       </c>
       <c r="AQ15" t="s" s="2">
         <v>81</v>
@@ -4631,28 +4631,28 @@
         <v>103</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN16" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="AL16" t="s" s="2">
+      <c r="AO16" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AP16" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="AN16" t="s" s="2">
+      <c r="AQ16" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="AO16" t="s" s="2">
+      <c r="AR16" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR16" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="17" hidden="true">
@@ -4759,28 +4759,28 @@
         <v>103</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM17" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN17" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AO17" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AP17" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="AN17" t="s" s="2">
+      <c r="AQ17" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="AO17" t="s" s="2">
+      <c r="AR17" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR17" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="18" hidden="true">
@@ -4886,16 +4886,16 @@
         <v>81</v>
       </c>
       <c r="AL18" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM18" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN18" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO18" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>81</v>
@@ -5012,16 +5012,16 @@
         <v>81</v>
       </c>
       <c r="AL19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO19" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>81</v>
@@ -5140,25 +5140,25 @@
         <v>81</v>
       </c>
       <c r="AL20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO20" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AM20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO20" t="s" s="2">
+      <c r="AP20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR20" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR20" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="21" hidden="true">
@@ -5264,16 +5264,16 @@
         <v>81</v>
       </c>
       <c r="AL21" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN21" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>81</v>
@@ -5390,16 +5390,16 @@
         <v>81</v>
       </c>
       <c r="AL22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO22" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>81</v>
@@ -5518,25 +5518,25 @@
         <v>81</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO23" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="AM23" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO23" t="s" s="2">
+      <c r="AP23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR23" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ23" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR23" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="24" hidden="true">
@@ -5644,25 +5644,25 @@
         <v>81</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO24" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="AM24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO24" t="s" s="2">
+      <c r="AP24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR24" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR24" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="25" hidden="true">
@@ -5767,10 +5767,10 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>81</v>
+        <v>260</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>81</v>
@@ -5779,16 +5779,16 @@
         <v>81</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>262</v>
+        <v>81</v>
       </c>
       <c r="AQ25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR25" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AR25" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="26" hidden="true">
@@ -5896,25 +5896,25 @@
         <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO26" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="AM26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO26" t="s" s="2">
+      <c r="AP26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR26" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR26" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="27" hidden="true">
@@ -6024,25 +6024,25 @@
         <v>81</v>
       </c>
       <c r="AL27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO27" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AM27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO27" t="s" s="2">
+      <c r="AP27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR27" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR27" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="28" hidden="true">
@@ -6149,10 +6149,10 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>81</v>
+        <v>289</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>81</v>
@@ -6161,16 +6161,16 @@
         <v>81</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>291</v>
+        <v>81</v>
       </c>
       <c r="AQ28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR28" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="AR28" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="29" hidden="true">
@@ -6278,25 +6278,25 @@
         <v>298</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="AM29" t="s" s="2">
+      <c r="AO29" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="AN29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO29" t="s" s="2">
+      <c r="AP29" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="AP29" t="s" s="2">
+      <c r="AQ29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR29" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="AQ29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR29" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="30" hidden="true">
@@ -6399,19 +6399,19 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>81</v>
@@ -6526,19 +6526,19 @@
         <v>81</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO31" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AP31" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>81</v>
@@ -6647,19 +6647,19 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AO32" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>81</v>
@@ -6774,16 +6774,16 @@
         <v>81</v>
       </c>
       <c r="AL33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO33" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>81</v>
@@ -6900,16 +6900,16 @@
         <v>81</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO34" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>81</v>
@@ -7028,16 +7028,16 @@
         <v>81</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO35" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>81</v>
@@ -7154,16 +7154,16 @@
         <v>81</v>
       </c>
       <c r="AL36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO36" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>81</v>
@@ -7278,19 +7278,19 @@
         <v>339</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AM37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AO37" t="s" s="2">
-        <v>81</v>
+        <v>341</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>341</v>
+        <v>81</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>81</v>
@@ -7399,28 +7399,28 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>81</v>
+        <v>346</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>81</v>
+        <v>348</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>81</v>
+        <v>349</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>347</v>
+        <v>81</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>348</v>
+        <v>81</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>349</v>
+        <v>81</v>
       </c>
     </row>
     <row r="39" hidden="true">
@@ -7540,13 +7540,13 @@
         <v>358</v>
       </c>
       <c r="AP39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ39" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="AQ39" t="s" s="2">
+      <c r="AR39" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="AR39" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="40" hidden="true">
@@ -7649,28 +7649,28 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>81</v>
+        <v>366</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>366</v>
+        <v>81</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO40" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="AO40" t="s" s="2">
+      <c r="AP40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ40" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="AP40" t="s" s="2">
+      <c r="AR40" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="AQ40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR40" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="41" hidden="true">
@@ -7776,25 +7776,25 @@
         <v>81</v>
       </c>
       <c r="AL41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO41" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="AM41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN41" t="s" s="2">
+      <c r="AP41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ41" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="AO41" t="s" s="2">
+      <c r="AR41" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR41" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="42" hidden="true">
@@ -7900,16 +7900,16 @@
         <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO42" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>81</v>
@@ -8026,16 +8026,16 @@
         <v>81</v>
       </c>
       <c r="AL43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO43" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>81</v>
@@ -8151,22 +8151,22 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>81</v>
+        <v>386</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>386</v>
+        <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>81</v>
+        <v>387</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>388</v>
+        <v>81</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>81</v>
@@ -8282,25 +8282,25 @@
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO45" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="AM45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO45" t="s" s="2">
+      <c r="AP45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR45" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR45" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="46" hidden="true">
@@ -8408,25 +8408,25 @@
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO46" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="AM46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO46" t="s" s="2">
+      <c r="AP46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR46" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR46" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="47" hidden="true">
@@ -8534,25 +8534,25 @@
         <v>81</v>
       </c>
       <c r="AL47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO47" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="AM47" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO47" t="s" s="2">
+      <c r="AP47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR47" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ47" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR47" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="48" hidden="true">
@@ -8662,25 +8662,25 @@
         <v>81</v>
       </c>
       <c r="AL48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO48" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="AM48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO48" t="s" s="2">
+      <c r="AP48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR48" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR48" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="49" hidden="true">
@@ -8783,22 +8783,22 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>81</v>
+        <v>424</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>424</v>
+        <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>81</v>
+        <v>425</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>426</v>
+        <v>81</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>81</v>
@@ -8907,28 +8907,28 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>81</v>
+        <v>432</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>432</v>
+        <v>81</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO50" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="AO50" t="s" s="2">
+      <c r="AP50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ50" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="AP50" t="s" s="2">
+      <c r="AR50" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="AQ50" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR50" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="51" hidden="true">
@@ -9034,25 +9034,25 @@
         <v>439</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="AM51" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>433</v>
-      </c>
       <c r="AO51" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AP51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ51" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="AP51" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="AQ51" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AR51" t="s" s="2">
-        <v>81</v>
+        <v>435</v>
       </c>
     </row>
     <row r="52" hidden="true">
@@ -9158,25 +9158,25 @@
         <v>81</v>
       </c>
       <c r="AL52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO52" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="AM52" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN52" t="s" s="2">
+      <c r="AP52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ52" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="AO52" t="s" s="2">
+      <c r="AR52" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ52" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR52" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="53" hidden="true">
@@ -9282,16 +9282,16 @@
         <v>81</v>
       </c>
       <c r="AL53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO53" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>81</v>
@@ -9408,16 +9408,16 @@
         <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO54" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>81</v>
@@ -9534,16 +9534,16 @@
         <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO55" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>81</v>
@@ -9660,16 +9660,16 @@
         <v>81</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO56" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>81</v>
@@ -9786,16 +9786,16 @@
         <v>81</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO57" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>81</v>
@@ -9909,28 +9909,28 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>81</v>
+        <v>475</v>
       </c>
       <c r="AL58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO58" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="AM58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AP58" t="s" s="2">
-        <v>475</v>
+        <v>81</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR58" t="s" s="2">
-        <v>476</v>
+        <v>81</v>
       </c>
     </row>
     <row r="59" hidden="true">
@@ -10036,22 +10036,22 @@
         <v>81</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO59" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="AM59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN59" t="s" s="2">
+      <c r="AP59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ59" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ59" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>81</v>
@@ -10157,28 +10157,28 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="AL60" t="s" s="2">
+      <c r="AO60" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="AM60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO60" t="s" s="2">
+      <c r="AP60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR60" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR60" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="61" hidden="true">
@@ -10284,16 +10284,16 @@
         <v>81</v>
       </c>
       <c r="AL61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO61" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>81</v>
@@ -10410,16 +10410,16 @@
         <v>81</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO62" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>81</v>
@@ -10536,25 +10536,25 @@
         <v>81</v>
       </c>
       <c r="AL63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO63" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="AM63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO63" t="s" s="2">
+      <c r="AP63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR63" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR63" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="64" hidden="true">
@@ -10660,25 +10660,25 @@
         <v>81</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO64" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="AM64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO64" t="s" s="2">
+      <c r="AP64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR64" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR64" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="65" hidden="true">
@@ -10781,10 +10781,10 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>81</v>
+        <v>509</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>509</v>
+        <v>81</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>81</v>
@@ -10793,16 +10793,16 @@
         <v>81</v>
       </c>
       <c r="AO65" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR65" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="AQ65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR65" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="66" hidden="true">
@@ -10910,16 +10910,16 @@
         <v>81</v>
       </c>
       <c r="AL66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO66" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>81</v>
@@ -11034,16 +11034,16 @@
         <v>81</v>
       </c>
       <c r="AL67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO67" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>81</v>
@@ -11160,16 +11160,16 @@
         <v>81</v>
       </c>
       <c r="AL68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO68" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>81</v>
@@ -11288,16 +11288,16 @@
         <v>81</v>
       </c>
       <c r="AL69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO69" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>81</v>
@@ -11414,25 +11414,25 @@
         <v>81</v>
       </c>
       <c r="AL70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO70" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="AM70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO70" t="s" s="2">
+      <c r="AP70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR70" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="AP70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR70" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="71" hidden="true">
@@ -11537,22 +11537,22 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>81</v>
+        <v>533</v>
       </c>
       <c r="AL71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO71" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="AM71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>533</v>
-      </c>
       <c r="AP71" t="s" s="2">
-        <v>534</v>
+        <v>81</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>81</v>
@@ -11668,25 +11668,25 @@
         <v>81</v>
       </c>
       <c r="AL72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO72" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="AM72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO72" t="s" s="2">
+      <c r="AP72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR72" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR72" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="73" hidden="true">
@@ -11789,28 +11789,28 @@
         <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>81</v>
+        <v>549</v>
       </c>
       <c r="AL73" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO73" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="AM73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO73" t="s" s="2">
+      <c r="AP73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR73" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="AP73" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="AQ73" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="AR73" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="74" hidden="true">
@@ -11920,16 +11920,16 @@
         <v>81</v>
       </c>
       <c r="AL74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO74" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>81</v>
@@ -12046,25 +12046,25 @@
         <v>81</v>
       </c>
       <c r="AL75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO75" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="AM75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO75" t="s" s="2">
+      <c r="AP75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR75" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="AP75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR75" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="76" hidden="true">
@@ -12174,25 +12174,25 @@
         <v>81</v>
       </c>
       <c r="AL76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO76" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="AM76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO76" t="s" s="2">
+      <c r="AP76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR76" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR76" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="77" hidden="true">
@@ -12300,25 +12300,25 @@
         <v>81</v>
       </c>
       <c r="AL77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO77" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="AM77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO77" t="s" s="2">
+      <c r="AP77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR77" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="AP77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR77" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="78" hidden="true">
@@ -12428,25 +12428,25 @@
         <v>81</v>
       </c>
       <c r="AL78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO78" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="AM78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO78" t="s" s="2">
+      <c r="AP78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR78" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="AP78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR78" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="79" hidden="true">
@@ -12561,16 +12561,16 @@
         <v>81</v>
       </c>
       <c r="AO79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR79" t="s" s="2">
         <v>603</v>
-      </c>
-      <c r="AP79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR79" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="80" hidden="true">
@@ -12676,16 +12676,16 @@
         <v>81</v>
       </c>
       <c r="AL80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO80" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO80" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP80" t="s" s="2">
         <v>81</v>
@@ -12802,16 +12802,16 @@
         <v>81</v>
       </c>
       <c r="AL81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO81" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>81</v>
@@ -12937,16 +12937,16 @@
         <v>81</v>
       </c>
       <c r="AO82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR82" t="s" s="2">
         <v>613</v>
-      </c>
-      <c r="AP82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR82" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="83" hidden="true">
@@ -13054,25 +13054,25 @@
         <v>81</v>
       </c>
       <c r="AL83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO83" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="AM83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO83" t="s" s="2">
+      <c r="AP83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR83" t="s" s="2">
         <v>621</v>
-      </c>
-      <c r="AP83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR83" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="84" hidden="true">
@@ -13184,25 +13184,25 @@
         <v>81</v>
       </c>
       <c r="AL84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO84" t="s" s="2">
         <v>629</v>
       </c>
-      <c r="AM84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO84" t="s" s="2">
+      <c r="AP84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR84" t="s" s="2">
         <v>630</v>
-      </c>
-      <c r="AP84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR84" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="85" hidden="true">
@@ -13308,16 +13308,16 @@
         <v>81</v>
       </c>
       <c r="AL85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO85" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO85" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>81</v>
@@ -13434,16 +13434,16 @@
         <v>81</v>
       </c>
       <c r="AL86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO86" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO86" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>81</v>
@@ -13559,28 +13559,28 @@
         <v>103</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>81</v>
+        <v>637</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>386</v>
+        <v>638</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>81</v>
+        <v>639</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>637</v>
+        <v>81</v>
       </c>
       <c r="AQ87" t="s" s="2">
-        <v>638</v>
+        <v>81</v>
       </c>
       <c r="AR87" t="s" s="2">
-        <v>639</v>
+        <v>389</v>
       </c>
     </row>
     <row r="88" hidden="true">
@@ -13690,25 +13690,25 @@
         <v>81</v>
       </c>
       <c r="AL88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO88" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="AM88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO88" t="s" s="2">
+      <c r="AP88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR88" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="AP88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR88" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="89" hidden="true">
@@ -13813,28 +13813,28 @@
         <v>103</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>81</v>
+        <v>644</v>
       </c>
       <c r="AL89" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO89" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="AM89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO89" t="s" s="2">
+      <c r="AP89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR89" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AP89" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="AQ89" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="AR89" t="s" s="2">
-        <v>646</v>
       </c>
     </row>
     <row r="90" hidden="true">
@@ -13942,25 +13942,25 @@
         <v>81</v>
       </c>
       <c r="AL90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO90" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="AM90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO90" t="s" s="2">
+      <c r="AP90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR90" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AP90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR90" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="91" hidden="true">
@@ -14065,28 +14065,28 @@
         <v>103</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>81</v>
+        <v>652</v>
       </c>
       <c r="AL91" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO91" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="AM91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO91" t="s" s="2">
+      <c r="AP91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR91" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AP91" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="AQ91" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="AR91" t="s" s="2">
-        <v>646</v>
       </c>
     </row>
     <row r="92" hidden="true">
@@ -14196,25 +14196,25 @@
         <v>81</v>
       </c>
       <c r="AL92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO92" t="s" s="2">
         <v>660</v>
       </c>
-      <c r="AM92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO92" t="s" s="2">
+      <c r="AP92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR92" t="s" s="2">
         <v>661</v>
-      </c>
-      <c r="AP92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR92" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="93" hidden="true">
@@ -14324,25 +14324,25 @@
         <v>81</v>
       </c>
       <c r="AL93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO93" t="s" s="2">
         <v>669</v>
       </c>
-      <c r="AM93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO93" t="s" s="2">
+      <c r="AP93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR93" t="s" s="2">
         <v>670</v>
-      </c>
-      <c r="AP93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR93" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="94" hidden="true">
@@ -14452,16 +14452,16 @@
         <v>81</v>
       </c>
       <c r="AL94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO94" t="s" s="2">
         <v>677</v>
-      </c>
-      <c r="AM94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>81</v>
@@ -14578,16 +14578,16 @@
         <v>81</v>
       </c>
       <c r="AL95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO95" t="s" s="2">
         <v>677</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>81</v>
@@ -14702,22 +14702,22 @@
         <v>81</v>
       </c>
       <c r="AL96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO96" t="s" s="2">
         <v>686</v>
       </c>
-      <c r="AM96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN96" t="s" s="2">
+      <c r="AP96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ96" t="s" s="2">
         <v>687</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ96" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR96" t="s" s="2">
         <v>81</v>
@@ -14826,16 +14826,16 @@
         <v>81</v>
       </c>
       <c r="AL97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO97" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP97" t="s" s="2">
         <v>81</v>
@@ -14952,16 +14952,16 @@
         <v>81</v>
       </c>
       <c r="AL98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO98" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP98" t="s" s="2">
         <v>81</v>
@@ -15080,16 +15080,16 @@
         <v>81</v>
       </c>
       <c r="AL99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO99" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP99" t="s" s="2">
         <v>81</v>
@@ -15204,16 +15204,16 @@
         <v>81</v>
       </c>
       <c r="AL100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO100" t="s" s="2">
         <v>694</v>
-      </c>
-      <c r="AM100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO100" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>81</v>
@@ -15328,25 +15328,25 @@
         <v>81</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>366</v>
+        <v>81</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AP101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ101" t="s" s="2">
         <v>700</v>
       </c>
-      <c r="AO101" t="s" s="2">
+      <c r="AR101" t="s" s="2">
         <v>701</v>
-      </c>
-      <c r="AP101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR101" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="102" hidden="true">
@@ -15452,22 +15452,22 @@
         <v>81</v>
       </c>
       <c r="AL102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO102" t="s" s="2">
         <v>707</v>
       </c>
-      <c r="AM102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN102" t="s" s="2">
+      <c r="AP102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ102" t="s" s="2">
         <v>708</v>
-      </c>
-      <c r="AO102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ102" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>81</v>
@@ -15576,22 +15576,22 @@
         <v>81</v>
       </c>
       <c r="AL103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO103" t="s" s="2">
         <v>713</v>
       </c>
-      <c r="AM103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN103" t="s" s="2">
+      <c r="AP103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ103" t="s" s="2">
         <v>714</v>
-      </c>
-      <c r="AO103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ103" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>81</v>
@@ -15702,16 +15702,16 @@
         <v>81</v>
       </c>
       <c r="AL104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO104" t="s" s="2">
         <v>721</v>
-      </c>
-      <c r="AM104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO104" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>81</v>
@@ -15828,16 +15828,16 @@
         <v>81</v>
       </c>
       <c r="AL105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO105" t="s" s="2">
         <v>727</v>
-      </c>
-      <c r="AM105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO105" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file PRESCRIPTION (#52) to MedicationDispense</t>
+    <t>This StructureDefinition contains the maps for VistA file PRESCRIPTION (52) to MedicationDispense</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -545,7 +545,7 @@
     <t>http://hl7.org/fhir/ValueSet/medicationdispense-status|4.0.1</t>
   </si>
   <si>
-    <t>1541: fixed value = #completed when PRESCRIPTION - RELEASED DATE/TIME (#52-31) case not null</t>
+    <t>1541: fixed value = #completed when PRESCRIPTION - RELEASED DATE/TIME (52-31) case not null</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -826,7 +826,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>1545: source value from PRESCRIPTION - DRUG &gt; DRUG - PSNDF VA PRODUCT NAME ENTRY (#52-6 &gt; 50-22)</t>
+    <t>1545: source value from PRESCRIPTION - DRUG &gt; DRUG - PSNDF VA PRODUCT NAME ENTRY (52-6 &gt; 50-22)</t>
   </si>
   <si>
     <t>Dim.LocalDrug.DrugNameWithoutDoseIEN,Dim.LocalDrug.NationalDrugIEN,Dim.LocalDrug.NationalDrugIEN</t>
@@ -914,7 +914,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1544: source value from PRESCRIPTION - DRUG &gt; DRUG - GENERIC NAME (#52-6 &gt; 50-.01)</t>
+    <t>1544: source value from PRESCRIPTION - DRUG &gt; DRUG - GENERIC NAME (52-6 &gt; 50-.01)</t>
   </si>
   <si>
     <t>Dim.IVAdditiveIngredient.LocalDrugNameWithDose,Dim.IVSolutionIngredient.LocalDrugNameWithDose,Dim.LocalDrug.CorrespondingInpatientLocalDrugNameWithDose,Dim.LocalDrug.CorrespondingOutpatientLocalDrugNameWithDose,Dim.LocalDrug.LocalDrugNameWithDose,Dim.LocalDrug.LocalDrugNameWithDose,RxOut.RxOutpatFill.LocalDrugNameWithDose</t>
@@ -942,7 +942,7 @@
     <t>SubstanceAdministration-&gt;subject-&gt;Patient.</t>
   </si>
   <si>
-    <t>820: reference from PRESCRIPTION - PATIENT (#52-2)</t>
+    <t>820: reference from PRESCRIPTION - PATIENT (52-2)</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1071,7 +1071,7 @@
     <t>The device, practitioner, etc. who performed the action.  It should be assumed that the actor is the dispenser of the medication.</t>
   </si>
   <si>
-    <t>1711: reference from PRESCRIPTION - DIVISION (#52-20)</t>
+    <t>1711: reference from PRESCRIPTION - DIVISION (52-20)</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1093,7 +1093,7 @@
     <t>The principal physical location where the dispense was performed.</t>
   </si>
   <si>
-    <t>821: reference from PRESCRIPTION - CLINIC (#52-5)</t>
+    <t>821: reference from PRESCRIPTION - CLINIC (52-5)</t>
   </si>
   <si>
     <t>RxOut.RxOutpatFill.PrescribingDivisionIEN</t>
@@ -1121,7 +1121,7 @@
     <t>Maps to basedOn in Event logical model.</t>
   </si>
   <si>
-    <t>822: source value from PRESCRIPTION - PLACER ORDER # (#52-39.3)</t>
+    <t>822: source value from PRESCRIPTION - PLACER ORDER # (52-39.3)</t>
   </si>
   <si>
     <t>RxOut.RxOutpat.CPRSOrderEntryNumber</t>
@@ -1220,7 +1220,7 @@
     <t>Quantity.value</t>
   </si>
   <si>
-    <t>823: source value from PRESCRIPTION - QTY (#52-7)</t>
+    <t>823: source value from PRESCRIPTION - QTY (52-7)</t>
   </si>
   <si>
     <t>Pharmacy: quantity</t>
@@ -1335,7 +1335,7 @@
     <t>The amount of medication expressed as a timing amount.</t>
   </si>
   <si>
-    <t>826: source value from PRESCRIPTION - DAYS SUPPLY (#52-8)</t>
+    <t>826: source value from PRESCRIPTION - DAYS SUPPLY (52-8)</t>
   </si>
   <si>
     <t>Pharmacy: daysSupply</t>
@@ -1363,7 +1363,7 @@
     <t>The time when the dispensed product was packaged and reviewed.</t>
   </si>
   <si>
-    <t>1548: source value from PRESCRIPTION - FILL DATE (#52-22)</t>
+    <t>1548: source value from PRESCRIPTION - FILL DATE (52-22)</t>
   </si>
   <si>
     <t>.effectiveTime[xmi:type=IVL_TS].low</t>
@@ -1384,7 +1384,7 @@
     <t>The time the dispensed product was provided to the patient or their representative.</t>
   </si>
   <si>
-    <t>832: source value from PRESCRIPTION - RELEASED DATE/TIME (#52-31)</t>
+    <t>832: source value from PRESCRIPTION - RELEASED DATE/TIME (52-31)</t>
   </si>
   <si>
     <t>Event.occurrence[x]</t>
@@ -1497,7 +1497,7 @@
     <t>Reference.display</t>
   </si>
   <si>
-    <t>835: source value from PRESCRIPTION - MAIL/WINDOW (#52-11)</t>
+    <t>835: source value from PRESCRIPTION - MAIL/WINDOW (52-11)</t>
   </si>
   <si>
     <t>Pharmacy: routing</t>
@@ -1603,7 +1603,7 @@
     <t>Annotation.text</t>
   </si>
   <si>
-    <t>1716: source value from PRESCRIPTION - REMARKS (#52-12)</t>
+    <t>1716: source value from PRESCRIPTION - REMARKS (52-12)</t>
   </si>
   <si>
     <t>Act.text</t>
@@ -1678,7 +1678,7 @@
     <t>Dosage.text</t>
   </si>
   <si>
-    <t>838: source value from PRESCRIPTION - SIG (#52-10)</t>
+    <t>838: source value from PRESCRIPTION - SIG (52-10)</t>
   </si>
   <si>
     <t>Pharmacy: sig</t>
@@ -1726,7 +1726,7 @@
     <t>Dosage.patientInstruction</t>
   </si>
   <si>
-    <t>839: source value from PRESCRIPTION - PATIENT INSTRUCTIONS (#52-114)</t>
+    <t>839: source value from PRESCRIPTION - PATIENT INSTRUCTIONS (52-114)</t>
   </si>
   <si>
     <t>RxOut.RxOutpatSig.PatientInstructions</t>
@@ -1996,7 +1996,7 @@
     <t>MedicationDispense.dosageInstruction.doseAndRate.dose[x].value</t>
   </si>
   <si>
-    <t>840: source value from PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - DOSAGE ORDERED (#52-113 &gt; 52.0113-.01) case number</t>
+    <t>840: source value from PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - DOSAGE ORDERED (52-113 &gt; 52.0113-.01) case number</t>
   </si>
   <si>
     <t>RxOut.RxOutpatMedInstructions.DoseOrdered</t>
@@ -2017,7 +2017,7 @@
     <t>MedicationDispense.dosageInstruction.doseAndRate.dose[x].unit</t>
   </si>
   <si>
-    <t>842: source value from PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - UNITS (#52-113 &gt; 52.0113-2)</t>
+    <t>842: source value from PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - UNITS (52-113 &gt; 52.0113-2)</t>
   </si>
   <si>
     <t>RxOut.RxOutpatMedInstructions.Unit</t>
@@ -2041,7 +2041,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFDoseUnits</t>
   </si>
   <si>
-    <t>1575: terminologyMaps using VF_DoseUnits on PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - UNITS (#52-113 &gt; 52.0113-2)</t>
+    <t>1575: terminologyMaps using VF_DoseUnits on PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - UNITS (52-113 &gt; 52.0113-2)</t>
   </si>
   <si>
     <t>MedicationDispense.dosageInstruction.doseAndRate.rate[x]</t>
@@ -2629,7 +2629,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="148.69921875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="147.1640625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1497,7 +1497,7 @@
     <t>Reference.display</t>
   </si>
   <si>
-    <t>835: source value from PRESCRIPTION - MAIL/WINDOW (52-11)</t>
+    <t>835: source value from PRESCRIPTION - MAIL/WINDOW/PARK (52-11)</t>
   </si>
   <si>
     <t>Pharmacy: routing</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="728">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="725">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -829,7 +829,8 @@
     <t>1545: source value from PRESCRIPTION - DRUG &gt; DRUG - PSNDF VA PRODUCT NAME ENTRY (52-6 &gt; 50-22)</t>
   </si>
   <si>
-    <t>Dim.LocalDrug.DrugNameWithoutDoseIEN,Dim.LocalDrug.NationalDrugIEN,Dim.LocalDrug.NationalDrugIEN</t>
+    <t>RxOut.RxOutpat.LocalDrugIEN,RxOut.RxOutpat.NationalDrugIEN,RxOut.RxOutpatFill.LocalDrugIEN,RxOut.RxOutpatFill.NationalDrugIEN
+Dim.LocalDrug.DrugNameWithoutDoseIEN,Dim.LocalDrug.NationalDrugIEN,Dim.LocalDrug.NationalDrugIEN</t>
   </si>
   <si>
     <t>./code</t>
@@ -917,7 +918,8 @@
     <t>1544: source value from PRESCRIPTION - DRUG &gt; DRUG - GENERIC NAME (52-6 &gt; 50-.01)</t>
   </si>
   <si>
-    <t>Dim.IVAdditiveIngredient.LocalDrugNameWithDose,Dim.IVSolutionIngredient.LocalDrugNameWithDose,Dim.LocalDrug.CorrespondingInpatientLocalDrugNameWithDose,Dim.LocalDrug.CorrespondingOutpatientLocalDrugNameWithDose,Dim.LocalDrug.LocalDrugNameWithDose,Dim.LocalDrug.LocalDrugNameWithDose,RxOut.RxOutpatFill.LocalDrugNameWithDose</t>
+    <t>RxOut.RxOutpat.LocalDrugIEN,RxOut.RxOutpat.NationalDrugIEN,RxOut.RxOutpatFill.LocalDrugIEN,RxOut.RxOutpatFill.NationalDrugIEN
+Dim.LocalDrug.LocalDrugNameWithDose,Dim.LocalDrug.LocalDrugNameWithDose,RxOut.RxOutpatFill.LocalDrugNameWithDose</t>
   </si>
   <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
@@ -945,6 +947,9 @@
     <t>820: reference from PRESCRIPTION - PATIENT (52-2)</t>
   </si>
   <si>
+    <t>RxOut.ActivityLog.PatientIEN,RxOut.ActivityLogOtherComments.PatientIEN,RxOut.RxOutpat.PatientIEN,RxOut.RxOutpatExt.PatientIEN,RxOut.RxOutpatExt.PatientSID,RxOut.RxOutpatFill.PatientIEN,RxOut.RxOutpatMedInstructions.PatientIEN,RxOut.RxOutpatSig.PatientIEN</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -1071,9 +1076,6 @@
     <t>The device, practitioner, etc. who performed the action.  It should be assumed that the actor is the dispenser of the medication.</t>
   </si>
   <si>
-    <t>1711: reference from PRESCRIPTION - DIVISION (52-20)</t>
-  </si>
-  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -1093,13 +1095,7 @@
     <t>The principal physical location where the dispense was performed.</t>
   </si>
   <si>
-    <t>821: reference from PRESCRIPTION - CLINIC (52-5)</t>
-  </si>
-  <si>
-    <t>RxOut.RxOutpatFill.PrescribingDivisionIEN</t>
-  </si>
-  <si>
-    <t>Pharmacy: facility</t>
+    <t>1711: reference from PRESCRIPTION - DIVISION (52-20)</t>
   </si>
   <si>
     <t>.participation[typeCode=LOC].role</t>
@@ -1363,7 +1359,7 @@
     <t>The time when the dispensed product was packaged and reviewed.</t>
   </si>
   <si>
-    <t>1548: source value from PRESCRIPTION - FILL DATE (52-22)</t>
+    <t>832: source value from PRESCRIPTION - RELEASED DATE/TIME (52-31)</t>
   </si>
   <si>
     <t>.effectiveTime[xmi:type=IVL_TS].low</t>
@@ -1382,9 +1378,6 @@
   </si>
   <si>
     <t>The time the dispensed product was provided to the patient or their representative.</t>
-  </si>
-  <si>
-    <t>832: source value from PRESCRIPTION - RELEASED DATE/TIME (52-31)</t>
   </si>
   <si>
     <t>Event.occurrence[x]</t>
@@ -2630,7 +2623,7 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="147.1640625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="249.89453125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
@@ -6278,33 +6271,33 @@
         <v>298</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>81</v>
+        <v>299</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6327,13 +6320,13 @@
         <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -6384,7 +6377,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -6408,10 +6401,10 @@
         <v>81</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>81</v>
@@ -6425,10 +6418,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6451,13 +6444,13 @@
         <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6508,7 +6501,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6535,10 +6528,10 @@
         <v>81</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>81</v>
@@ -6549,10 +6542,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6575,13 +6568,13 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6632,7 +6625,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6656,10 +6649,10 @@
         <v>81</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>81</v>
@@ -6673,10 +6666,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6797,10 +6790,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6923,14 +6916,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6952,10 +6945,10 @@
         <v>137</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>140</v>
@@ -7010,7 +7003,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -7051,10 +7044,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7080,14 +7073,14 @@
         <v>185</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -7115,10 +7108,10 @@
         <v>179</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>81</v>
@@ -7136,7 +7129,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -7163,7 +7156,7 @@
         <v>81</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>81</v>
@@ -7177,10 +7170,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7194,7 +7187,7 @@
         <v>91</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>81</v>
@@ -7203,13 +7196,13 @@
         <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7260,7 +7253,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>91</v>
@@ -7275,7 +7268,7 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>339</v>
+        <v>81</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>81</v>
@@ -7402,16 +7395,16 @@
         <v>346</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO38" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>81</v>
@@ -7425,10 +7418,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7451,16 +7444,16 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7510,7 +7503,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7525,36 +7518,36 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AO39" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AM39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN39" t="s" s="2">
+      <c r="AP39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ39" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AO39" t="s" s="2">
+      <c r="AR39" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ39" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="AR39" t="s" s="2">
-        <v>360</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7580,10 +7573,10 @@
         <v>185</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7595,7 +7588,7 @@
         <v>81</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>81</v>
@@ -7613,11 +7606,11 @@
         <v>179</v>
       </c>
       <c r="Y40" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="Z40" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="Z40" t="s" s="2">
-        <v>365</v>
-      </c>
       <c r="AA40" t="s" s="2">
         <v>81</v>
       </c>
@@ -7634,7 +7627,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7649,36 +7642,36 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO40" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AP40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ40" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="AL40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO40" t="s" s="2">
+      <c r="AR40" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="AP40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ40" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="AR40" t="s" s="2">
-        <v>369</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7701,13 +7694,13 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7758,7 +7751,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7785,24 +7778,24 @@
         <v>81</v>
       </c>
       <c r="AO41" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AP41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ41" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AR41" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ41" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="AR41" t="s" s="2">
-        <v>376</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7923,10 +7916,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8049,10 +8042,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8075,19 +8068,19 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -8136,7 +8129,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -8151,36 +8144,36 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO44" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="AL44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM44" t="s" s="2">
+      <c r="AP44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR44" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR44" t="s" s="2">
-        <v>389</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8206,20 +8199,20 @@
         <v>111</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q45" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="R45" t="s" s="2">
         <v>81</v>
@@ -8243,28 +8236,28 @@
         <v>167</v>
       </c>
       <c r="Y45" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF45" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8291,7 +8284,7 @@
         <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>81</v>
@@ -8300,15 +8293,15 @@
         <v>81</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8334,14 +8327,14 @@
         <v>212</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -8390,7 +8383,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8417,7 +8410,7 @@
         <v>81</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>81</v>
@@ -8426,15 +8419,15 @@
         <v>81</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8460,14 +8453,14 @@
         <v>105</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
@@ -8516,7 +8509,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8525,7 +8518,7 @@
         <v>91</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>103</v>
@@ -8543,7 +8536,7 @@
         <v>81</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>81</v>
@@ -8552,15 +8545,15 @@
         <v>81</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8586,16 +8579,16 @@
         <v>111</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -8644,7 +8637,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8671,7 +8664,7 @@
         <v>81</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>81</v>
@@ -8680,15 +8673,15 @@
         <v>81</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8711,13 +8704,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8768,7 +8761,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8783,36 +8776,36 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO49" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="AL49" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM49" t="s" s="2">
+      <c r="AP49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR49" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ49" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR49" t="s" s="2">
-        <v>427</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8835,13 +8828,13 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8892,7 +8885,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8907,36 +8900,36 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO50" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AP50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ50" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="AL50" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO50" t="s" s="2">
+      <c r="AR50" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ50" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="AR50" t="s" s="2">
-        <v>435</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8950,7 +8943,7 @@
         <v>91</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>81</v>
@@ -8959,13 +8952,13 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -9016,7 +9009,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -9031,7 +9024,7 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>439</v>
+        <v>81</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>81</v>
@@ -9040,27 +9033,27 @@
         <v>81</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9086,10 +9079,10 @@
         <v>343</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -9140,7 +9133,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9167,24 +9160,24 @@
         <v>81</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9305,10 +9298,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9431,10 +9424,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9460,13 +9453,13 @@
         <v>212</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9516,7 +9509,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9525,7 +9518,7 @@
         <v>91</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>103</v>
@@ -9557,10 +9550,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9586,13 +9579,13 @@
         <v>105</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9618,31 +9611,31 @@
         <v>81</v>
       </c>
       <c r="X56" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF56" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="Z56" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9683,10 +9676,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9712,13 +9705,13 @@
         <v>149</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9768,7 +9761,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9795,7 +9788,7 @@
         <v>81</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>81</v>
@@ -9809,10 +9802,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9838,13 +9831,13 @@
         <v>212</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9894,7 +9887,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9909,13 +9902,13 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>81</v>
@@ -9935,10 +9928,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9961,13 +9954,13 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -10018,7 +10011,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10045,13 +10038,13 @@
         <v>81</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>81</v>
@@ -10059,10 +10052,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10085,13 +10078,13 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -10142,7 +10135,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10166,10 +10159,10 @@
         <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>81</v>
@@ -10178,15 +10171,15 @@
         <v>81</v>
       </c>
       <c r="AR60" t="s" s="2">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10307,10 +10300,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10433,10 +10426,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10459,16 +10452,16 @@
         <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="N63" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10518,7 +10511,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10545,7 +10538,7 @@
         <v>81</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>81</v>
@@ -10559,10 +10552,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10585,13 +10578,13 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10642,7 +10635,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10669,7 +10662,7 @@
         <v>81</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>81</v>
@@ -10683,10 +10676,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10709,13 +10702,13 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10766,7 +10759,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>91</v>
@@ -10781,7 +10774,7 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>81</v>
@@ -10793,7 +10786,7 @@
         <v>81</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>81</v>
@@ -10807,10 +10800,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10833,16 +10826,16 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="N66" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10892,7 +10885,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10919,7 +10912,7 @@
         <v>81</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>81</v>
@@ -10933,10 +10926,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11057,10 +11050,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11183,14 +11176,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -11212,10 +11205,10 @@
         <v>137</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>140</v>
@@ -11270,7 +11263,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11311,10 +11304,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11337,17 +11330,17 @@
         <v>92</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>81</v>
@@ -11396,7 +11389,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11423,7 +11416,7 @@
         <v>81</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>81</v>
@@ -11432,15 +11425,15 @@
         <v>81</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11466,14 +11459,14 @@
         <v>212</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>81</v>
@@ -11522,7 +11515,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11537,19 +11530,19 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>81</v>
@@ -11558,15 +11551,15 @@
         <v>81</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11592,16 +11585,16 @@
         <v>185</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="O72" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -11629,10 +11622,10 @@
         <v>179</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>81</v>
@@ -11650,7 +11643,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11677,7 +11670,7 @@
         <v>81</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>81</v>
@@ -11686,15 +11679,15 @@
         <v>81</v>
       </c>
       <c r="AR72" t="s" s="2">
-        <v>544</v>
+        <v>541</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11720,10 +11713,10 @@
         <v>212</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11774,7 +11767,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11789,10 +11782,10 @@
         <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>81</v>
@@ -11801,7 +11794,7 @@
         <v>81</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>81</v>
@@ -11810,15 +11803,15 @@
         <v>81</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>544</v>
+        <v>541</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11841,19 +11834,19 @@
         <v>92</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="N74" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
@@ -11902,7 +11895,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -11929,7 +11922,7 @@
         <v>81</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>81</v>
@@ -11943,10 +11936,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11969,16 +11962,16 @@
         <v>92</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -12007,10 +12000,10 @@
         <v>179</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>81</v>
@@ -12028,7 +12021,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12055,7 +12048,7 @@
         <v>81</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>81</v>
@@ -12064,15 +12057,15 @@
         <v>81</v>
       </c>
       <c r="AR75" t="s" s="2">
-        <v>568</v>
+        <v>565</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12098,16 +12091,16 @@
         <v>185</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="O76" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>573</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>81</v>
@@ -12135,10 +12128,10 @@
         <v>179</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>81</v>
@@ -12156,7 +12149,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12183,7 +12176,7 @@
         <v>81</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>81</v>
@@ -12192,15 +12185,15 @@
         <v>81</v>
       </c>
       <c r="AR76" t="s" s="2">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12226,14 +12219,14 @@
         <v>185</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>81</v>
@@ -12261,10 +12254,10 @@
         <v>179</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>81</v>
@@ -12282,7 +12275,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12309,7 +12302,7 @@
         <v>81</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>81</v>
@@ -12318,15 +12311,15 @@
         <v>81</v>
       </c>
       <c r="AR77" t="s" s="2">
-        <v>587</v>
+        <v>584</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12352,16 +12345,16 @@
         <v>185</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="O78" t="s" s="2">
         <v>589</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>81</v>
@@ -12389,10 +12382,10 @@
         <v>179</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>81</v>
@@ -12410,7 +12403,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12437,7 +12430,7 @@
         <v>81</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>81</v>
@@ -12446,15 +12439,15 @@
         <v>81</v>
       </c>
       <c r="AR78" t="s" s="2">
-        <v>597</v>
+        <v>594</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12477,13 +12470,13 @@
         <v>92</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12534,7 +12527,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12570,15 +12563,15 @@
         <v>81</v>
       </c>
       <c r="AR79" t="s" s="2">
-        <v>603</v>
+        <v>600</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12699,10 +12692,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12825,10 +12818,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12854,14 +12847,14 @@
         <v>185</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>81</v>
@@ -12889,10 +12882,10 @@
         <v>179</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>81</v>
@@ -12910,7 +12903,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -12946,15 +12939,15 @@
         <v>81</v>
       </c>
       <c r="AR82" t="s" s="2">
-        <v>613</v>
+        <v>610</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12977,19 +12970,19 @@
         <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="N83" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="O83" t="s" s="2">
         <v>616</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>619</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>81</v>
@@ -13036,7 +13029,7 @@
         <v>202</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13063,7 +13056,7 @@
         <v>81</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>81</v>
@@ -13072,18 +13065,18 @@
         <v>81</v>
       </c>
       <c r="AR83" t="s" s="2">
-        <v>621</v>
+        <v>618</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>81</v>
@@ -13105,19 +13098,19 @@
         <v>81</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -13166,7 +13159,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13175,42 +13168,42 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO84" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AP84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR84" t="s" s="2">
         <v>627</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="AP84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR84" t="s" s="2">
-        <v>630</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13331,10 +13324,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13457,10 +13450,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13483,19 +13476,19 @@
         <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="O87" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>81</v>
@@ -13544,7 +13537,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13559,19 +13552,19 @@
         <v>103</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>81</v>
@@ -13580,15 +13573,15 @@
         <v>81</v>
       </c>
       <c r="AR87" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13614,20 +13607,20 @@
         <v>111</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q88" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="R88" t="s" s="2">
         <v>81</v>
@@ -13651,28 +13644,28 @@
         <v>167</v>
       </c>
       <c r="Y88" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF88" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="Z88" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13699,7 +13692,7 @@
         <v>81</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>81</v>
@@ -13708,15 +13701,15 @@
         <v>81</v>
       </c>
       <c r="AR88" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13742,14 +13735,14 @@
         <v>212</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>81</v>
@@ -13798,7 +13791,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -13813,19 +13806,19 @@
         <v>103</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>81</v>
@@ -13834,15 +13827,15 @@
         <v>81</v>
       </c>
       <c r="AR89" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13868,14 +13861,14 @@
         <v>105</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>81</v>
@@ -13924,7 +13917,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -13933,7 +13926,7 @@
         <v>91</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>103</v>
@@ -13951,7 +13944,7 @@
         <v>81</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>81</v>
@@ -13960,15 +13953,15 @@
         <v>81</v>
       </c>
       <c r="AR90" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13994,16 +13987,16 @@
         <v>111</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="N91" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="O91" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>81</v>
@@ -14032,7 +14025,7 @@
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -14050,7 +14043,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -14065,19 +14058,19 @@
         <v>103</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>81</v>
@@ -14086,15 +14079,15 @@
         <v>81</v>
       </c>
       <c r="AR91" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14117,19 +14110,19 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="N92" t="s" s="2">
         <v>654</v>
       </c>
-      <c r="L92" t="s" s="2">
+      <c r="O92" t="s" s="2">
         <v>655</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>658</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>81</v>
@@ -14178,7 +14171,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14205,7 +14198,7 @@
         <v>81</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>81</v>
@@ -14214,15 +14207,15 @@
         <v>81</v>
       </c>
       <c r="AR92" t="s" s="2">
-        <v>661</v>
+        <v>658</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14245,19 +14238,19 @@
         <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="N93" t="s" s="2">
         <v>663</v>
       </c>
-      <c r="L93" t="s" s="2">
+      <c r="O93" t="s" s="2">
         <v>664</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>667</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -14306,7 +14299,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14333,7 +14326,7 @@
         <v>81</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>81</v>
@@ -14342,15 +14335,15 @@
         <v>81</v>
       </c>
       <c r="AR93" t="s" s="2">
-        <v>670</v>
+        <v>667</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14373,19 +14366,19 @@
         <v>92</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="O94" t="s" s="2">
         <v>672</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>675</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -14434,7 +14427,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14461,7 +14454,7 @@
         <v>81</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>81</v>
@@ -14475,10 +14468,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14501,17 +14494,17 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -14560,7 +14553,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14587,7 +14580,7 @@
         <v>81</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>81</v>
@@ -14601,10 +14594,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14627,13 +14620,13 @@
         <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14684,7 +14677,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14711,13 +14704,13 @@
         <v>81</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ96" t="s" s="2">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="AR96" t="s" s="2">
         <v>81</v>
@@ -14725,10 +14718,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14849,10 +14842,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14975,14 +14968,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -15004,10 +14997,10 @@
         <v>137</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>140</v>
@@ -15062,7 +15055,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -15103,10 +15096,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15132,10 +15125,10 @@
         <v>274</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -15186,7 +15179,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>91</v>
@@ -15213,7 +15206,7 @@
         <v>81</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>81</v>
@@ -15227,10 +15220,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15256,10 +15249,10 @@
         <v>185</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -15289,10 +15282,10 @@
         <v>179</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>81</v>
@@ -15310,7 +15303,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15337,24 +15330,24 @@
         <v>81</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ101" t="s" s="2">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>701</v>
+        <v>698</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15380,10 +15373,10 @@
         <v>185</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15413,10 +15406,10 @@
         <v>179</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>81</v>
@@ -15434,7 +15427,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15461,13 +15454,13 @@
         <v>81</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>81</v>
@@ -15475,10 +15468,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15501,13 +15494,13 @@
         <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15558,7 +15551,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15585,13 +15578,13 @@
         <v>81</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>81</v>
@@ -15599,14 +15592,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -15625,16 +15618,16 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="N104" t="s" s="2">
         <v>717</v>
-      </c>
-      <c r="L104" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>719</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>720</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15684,7 +15677,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -15711,7 +15704,7 @@
         <v>81</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>81</v>
@@ -15725,10 +15718,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15751,16 +15744,16 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="N105" t="s" s="2">
         <v>723</v>
-      </c>
-      <c r="L105" t="s" s="2">
-        <v>724</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>726</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15810,7 +15803,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -15837,7 +15830,7 @@
         <v>81</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="725">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="727">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -775,7 +775,13 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
+    <t>urn:oid:2.16.840.1.113883.6.233</t>
+  </si>
+  <si>
     <t>Coding.system</t>
+  </si>
+  <si>
+    <t>1545-1: fixed value = urn:oid:2.16.840.1.113883.6.233</t>
   </si>
   <si>
     <t>./codeSystem</t>
@@ -5423,7 +5429,7 @@
         <v>91</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>81</v>
@@ -5454,7 +5460,7 @@
         <v>81</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>81</v>
+        <v>243</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>81</v>
@@ -5493,7 +5499,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -5508,7 +5514,7 @@
         <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>81</v>
+        <v>245</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>81</v>
@@ -5520,7 +5526,7 @@
         <v>81</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>81</v>
@@ -5529,15 +5535,15 @@
         <v>81</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5563,13 +5569,13 @@
         <v>212</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5619,7 +5625,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -5646,7 +5652,7 @@
         <v>81</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>81</v>
@@ -5655,15 +5661,15 @@
         <v>81</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5689,14 +5695,14 @@
         <v>111</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
@@ -5745,7 +5751,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -5760,10 +5766,10 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>81</v>
@@ -5772,7 +5778,7 @@
         <v>81</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>81</v>
@@ -5781,15 +5787,15 @@
         <v>81</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5815,14 +5821,14 @@
         <v>212</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>81</v>
@@ -5871,7 +5877,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5898,7 +5904,7 @@
         <v>81</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>81</v>
@@ -5907,15 +5913,15 @@
         <v>81</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5938,19 +5944,19 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -5999,7 +6005,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -6026,7 +6032,7 @@
         <v>81</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>81</v>
@@ -6035,15 +6041,15 @@
         <v>81</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6069,16 +6075,16 @@
         <v>212</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>81</v>
@@ -6127,7 +6133,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -6142,10 +6148,10 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>81</v>
@@ -6154,7 +6160,7 @@
         <v>81</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>81</v>
@@ -6163,15 +6169,15 @@
         <v>81</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6194,16 +6200,16 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6253,7 +6259,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -6268,36 +6274,36 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6320,13 +6326,13 @@
         <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -6377,7 +6383,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -6401,10 +6407,10 @@
         <v>81</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>81</v>
@@ -6418,10 +6424,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6444,13 +6450,13 @@
         <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6501,7 +6507,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6528,10 +6534,10 @@
         <v>81</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>81</v>
@@ -6542,10 +6548,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6568,13 +6574,13 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6625,7 +6631,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6649,10 +6655,10 @@
         <v>81</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>81</v>
@@ -6666,10 +6672,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6790,10 +6796,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6916,14 +6922,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6945,10 +6951,10 @@
         <v>137</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>140</v>
@@ -7003,7 +7009,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -7044,10 +7050,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7073,14 +7079,14 @@
         <v>185</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -7108,10 +7114,10 @@
         <v>179</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>81</v>
@@ -7129,7 +7135,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -7156,7 +7162,7 @@
         <v>81</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>81</v>
@@ -7170,10 +7176,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7196,13 +7202,13 @@
         <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7253,7 +7259,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>91</v>
@@ -7277,10 +7283,10 @@
         <v>81</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>81</v>
@@ -7294,10 +7300,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7320,13 +7326,13 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7377,7 +7383,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7392,7 +7398,7 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>81</v>
@@ -7404,7 +7410,7 @@
         <v>81</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>81</v>
@@ -7418,10 +7424,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7444,16 +7450,16 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7503,7 +7509,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7518,36 +7524,36 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7573,10 +7579,10 @@
         <v>185</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7588,7 +7594,7 @@
         <v>81</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>81</v>
@@ -7606,28 +7612,28 @@
         <v>179</v>
       </c>
       <c r="Y40" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF40" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7642,7 +7648,7 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>81</v>
@@ -7654,24 +7660,24 @@
         <v>81</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7694,13 +7700,13 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7751,7 +7757,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7778,24 +7784,24 @@
         <v>81</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7916,10 +7922,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8042,10 +8048,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8068,19 +8074,19 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -8129,7 +8135,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -8144,19 +8150,19 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>81</v>
@@ -8165,15 +8171,15 @@
         <v>81</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8199,20 +8205,20 @@
         <v>111</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q45" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="R45" t="s" s="2">
         <v>81</v>
@@ -8236,10 +8242,10 @@
         <v>167</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>81</v>
@@ -8257,7 +8263,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8284,7 +8290,7 @@
         <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>81</v>
@@ -8293,15 +8299,15 @@
         <v>81</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8327,14 +8333,14 @@
         <v>212</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -8383,7 +8389,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8410,7 +8416,7 @@
         <v>81</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>81</v>
@@ -8419,15 +8425,15 @@
         <v>81</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8453,14 +8459,14 @@
         <v>105</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
@@ -8509,7 +8515,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8518,7 +8524,7 @@
         <v>91</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>103</v>
@@ -8536,7 +8542,7 @@
         <v>81</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>81</v>
@@ -8545,15 +8551,15 @@
         <v>81</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8579,16 +8585,16 @@
         <v>111</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -8637,7 +8643,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8664,7 +8670,7 @@
         <v>81</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>81</v>
@@ -8673,15 +8679,15 @@
         <v>81</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8704,13 +8710,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8761,7 +8767,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8776,19 +8782,19 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>81</v>
@@ -8797,15 +8803,15 @@
         <v>81</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8828,13 +8834,13 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8885,7 +8891,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8900,7 +8906,7 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>81</v>
@@ -8912,24 +8918,24 @@
         <v>81</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8952,13 +8958,13 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -9009,7 +9015,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -9033,27 +9039,27 @@
         <v>81</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9076,13 +9082,13 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -9133,7 +9139,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9160,24 +9166,24 @@
         <v>81</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9298,10 +9304,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9424,10 +9430,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9453,13 +9459,13 @@
         <v>212</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9509,7 +9515,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9518,7 +9524,7 @@
         <v>91</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>103</v>
@@ -9550,10 +9556,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9579,13 +9585,13 @@
         <v>105</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9611,13 +9617,13 @@
         <v>81</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>81</v>
@@ -9635,7 +9641,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9676,10 +9682,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9705,13 +9711,13 @@
         <v>149</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9761,7 +9767,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9788,7 +9794,7 @@
         <v>81</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>81</v>
@@ -9802,10 +9808,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9831,13 +9837,13 @@
         <v>212</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9887,7 +9893,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9902,13 +9908,13 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>81</v>
@@ -9928,10 +9934,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9954,13 +9960,13 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -10011,7 +10017,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10038,13 +10044,13 @@
         <v>81</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>81</v>
@@ -10052,10 +10058,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10078,13 +10084,13 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -10135,7 +10141,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10159,10 +10165,10 @@
         <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>81</v>
@@ -10171,15 +10177,15 @@
         <v>81</v>
       </c>
       <c r="AR60" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10300,10 +10306,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10426,10 +10432,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10452,16 +10458,16 @@
         <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10511,7 +10517,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10538,7 +10544,7 @@
         <v>81</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>81</v>
@@ -10552,10 +10558,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10578,13 +10584,13 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10635,7 +10641,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10662,7 +10668,7 @@
         <v>81</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>81</v>
@@ -10676,10 +10682,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10702,13 +10708,13 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10759,7 +10765,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>91</v>
@@ -10774,7 +10780,7 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>81</v>
@@ -10786,7 +10792,7 @@
         <v>81</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>81</v>
@@ -10800,10 +10806,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10826,16 +10832,16 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10885,7 +10891,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10912,7 +10918,7 @@
         <v>81</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>81</v>
@@ -10926,10 +10932,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11050,10 +11056,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11176,14 +11182,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -11205,10 +11211,10 @@
         <v>137</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>140</v>
@@ -11263,7 +11269,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11304,10 +11310,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11330,17 +11336,17 @@
         <v>92</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>81</v>
@@ -11389,7 +11395,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11416,7 +11422,7 @@
         <v>81</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>81</v>
@@ -11425,15 +11431,15 @@
         <v>81</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11459,14 +11465,14 @@
         <v>212</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>81</v>
@@ -11515,7 +11521,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11530,19 +11536,19 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>81</v>
@@ -11551,15 +11557,15 @@
         <v>81</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11585,16 +11591,16 @@
         <v>185</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -11622,10 +11628,10 @@
         <v>179</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>81</v>
@@ -11643,7 +11649,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11670,7 +11676,7 @@
         <v>81</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>81</v>
@@ -11679,15 +11685,15 @@
         <v>81</v>
       </c>
       <c r="AR72" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11713,10 +11719,10 @@
         <v>212</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11767,7 +11773,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11782,10 +11788,10 @@
         <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>81</v>
@@ -11794,7 +11800,7 @@
         <v>81</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>81</v>
@@ -11803,15 +11809,15 @@
         <v>81</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11834,19 +11840,19 @@
         <v>92</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
@@ -11895,7 +11901,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -11922,7 +11928,7 @@
         <v>81</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>81</v>
@@ -11936,10 +11942,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11962,16 +11968,16 @@
         <v>92</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -12000,10 +12006,10 @@
         <v>179</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>81</v>
@@ -12021,7 +12027,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12048,7 +12054,7 @@
         <v>81</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>81</v>
@@ -12057,15 +12063,15 @@
         <v>81</v>
       </c>
       <c r="AR75" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12091,16 +12097,16 @@
         <v>185</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>81</v>
@@ -12128,10 +12134,10 @@
         <v>179</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>81</v>
@@ -12149,7 +12155,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12176,7 +12182,7 @@
         <v>81</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>81</v>
@@ -12185,15 +12191,15 @@
         <v>81</v>
       </c>
       <c r="AR76" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12219,14 +12225,14 @@
         <v>185</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>81</v>
@@ -12254,10 +12260,10 @@
         <v>179</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>81</v>
@@ -12275,7 +12281,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12302,7 +12308,7 @@
         <v>81</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>81</v>
@@ -12311,15 +12317,15 @@
         <v>81</v>
       </c>
       <c r="AR77" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12345,16 +12351,16 @@
         <v>185</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>81</v>
@@ -12382,10 +12388,10 @@
         <v>179</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>81</v>
@@ -12403,7 +12409,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12430,7 +12436,7 @@
         <v>81</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>81</v>
@@ -12439,15 +12445,15 @@
         <v>81</v>
       </c>
       <c r="AR78" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12470,13 +12476,13 @@
         <v>92</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12527,7 +12533,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12563,15 +12569,15 @@
         <v>81</v>
       </c>
       <c r="AR79" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12692,10 +12698,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12818,10 +12824,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12847,14 +12853,14 @@
         <v>185</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>81</v>
@@ -12882,10 +12888,10 @@
         <v>179</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>81</v>
@@ -12903,7 +12909,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -12939,15 +12945,15 @@
         <v>81</v>
       </c>
       <c r="AR82" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12970,19 +12976,19 @@
         <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>81</v>
@@ -13029,7 +13035,7 @@
         <v>202</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13056,7 +13062,7 @@
         <v>81</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>81</v>
@@ -13065,18 +13071,18 @@
         <v>81</v>
       </c>
       <c r="AR83" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>81</v>
@@ -13098,19 +13104,19 @@
         <v>81</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -13159,7 +13165,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13168,10 +13174,10 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>81</v>
@@ -13186,7 +13192,7 @@
         <v>81</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>81</v>
@@ -13195,15 +13201,15 @@
         <v>81</v>
       </c>
       <c r="AR84" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13324,10 +13330,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13450,10 +13456,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13476,19 +13482,19 @@
         <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>81</v>
@@ -13537,7 +13543,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13552,19 +13558,19 @@
         <v>103</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>81</v>
@@ -13573,15 +13579,15 @@
         <v>81</v>
       </c>
       <c r="AR87" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13607,20 +13613,20 @@
         <v>111</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q88" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="R88" t="s" s="2">
         <v>81</v>
@@ -13644,10 +13650,10 @@
         <v>167</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>81</v>
@@ -13665,7 +13671,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13692,7 +13698,7 @@
         <v>81</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>81</v>
@@ -13701,15 +13707,15 @@
         <v>81</v>
       </c>
       <c r="AR88" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13735,14 +13741,14 @@
         <v>212</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>81</v>
@@ -13791,7 +13797,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -13806,19 +13812,19 @@
         <v>103</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>81</v>
@@ -13827,15 +13833,15 @@
         <v>81</v>
       </c>
       <c r="AR89" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13861,14 +13867,14 @@
         <v>105</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>81</v>
@@ -13917,7 +13923,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -13926,7 +13932,7 @@
         <v>91</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>103</v>
@@ -13944,7 +13950,7 @@
         <v>81</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>81</v>
@@ -13953,15 +13959,15 @@
         <v>81</v>
       </c>
       <c r="AR90" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13987,16 +13993,16 @@
         <v>111</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>81</v>
@@ -14025,7 +14031,7 @@
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -14043,7 +14049,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -14058,19 +14064,19 @@
         <v>103</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>81</v>
@@ -14079,15 +14085,15 @@
         <v>81</v>
       </c>
       <c r="AR91" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14110,19 +14116,19 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>81</v>
@@ -14171,7 +14177,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14198,7 +14204,7 @@
         <v>81</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>81</v>
@@ -14207,15 +14213,15 @@
         <v>81</v>
       </c>
       <c r="AR92" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14238,19 +14244,19 @@
         <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -14299,7 +14305,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14326,7 +14332,7 @@
         <v>81</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>81</v>
@@ -14335,15 +14341,15 @@
         <v>81</v>
       </c>
       <c r="AR93" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14366,19 +14372,19 @@
         <v>92</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -14427,7 +14433,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14454,7 +14460,7 @@
         <v>81</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>81</v>
@@ -14468,10 +14474,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14494,17 +14500,17 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -14553,7 +14559,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14580,7 +14586,7 @@
         <v>81</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>81</v>
@@ -14594,10 +14600,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14620,13 +14626,13 @@
         <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14677,7 +14683,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14704,13 +14710,13 @@
         <v>81</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ96" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="AR96" t="s" s="2">
         <v>81</v>
@@ -14718,10 +14724,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14842,10 +14848,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14968,14 +14974,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14997,10 +15003,10 @@
         <v>137</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>140</v>
@@ -15055,7 +15061,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -15096,10 +15102,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15122,13 +15128,13 @@
         <v>81</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -15179,7 +15185,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>91</v>
@@ -15206,7 +15212,7 @@
         <v>81</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>81</v>
@@ -15220,10 +15226,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15249,10 +15255,10 @@
         <v>185</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -15282,10 +15288,10 @@
         <v>179</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>81</v>
@@ -15303,7 +15309,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15330,24 +15336,24 @@
         <v>81</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ101" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15373,10 +15379,10 @@
         <v>185</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15406,10 +15412,10 @@
         <v>179</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>81</v>
@@ -15427,7 +15433,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15454,13 +15460,13 @@
         <v>81</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>81</v>
@@ -15468,10 +15474,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15494,13 +15500,13 @@
         <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15551,7 +15557,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15578,13 +15584,13 @@
         <v>81</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>81</v>
@@ -15592,14 +15598,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -15618,16 +15624,16 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15677,7 +15683,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -15704,7 +15710,7 @@
         <v>81</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>81</v>
@@ -15718,10 +15724,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15744,16 +15750,16 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15803,7 +15809,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -15830,7 +15836,7 @@
         <v>81</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="728">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="724">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -839,6 +839,11 @@
 Dim.LocalDrug.DrugNameWithoutDoseIEN,Dim.LocalDrug.NationalDrugIEN,Dim.LocalDrug.NationalDrugIEN</t>
   </si>
   <si>
+    <t>Dim.LocalDrug.DrugNameWithoutDoseIEN
+Dim.LocalDrug.NationalDrugIEN
+Dim.LocalDrug.NationalDrugIEN</t>
+  </si>
+  <si>
     <t>./code</t>
   </si>
   <si>
@@ -928,6 +933,11 @@
 Dim.LocalDrug.LocalDrugNameWithDose,Dim.LocalDrug.LocalDrugNameWithDose,RxOut.RxOutpatFill.LocalDrugNameWithDose</t>
   </si>
   <si>
+    <t>Dim.LocalDrug.LocalDrugNameWithDose
+Dim.LocalDrug.LocalDrugNameWithDose
+RxOut.RxOutpatFill.LocalDrugNameWithDose</t>
+  </si>
+  <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
@@ -1113,7 +1123,7 @@
     <t>MedicationDispense.authorizingPrescription</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/MedicationRequestOutpatient)
 </t>
   </si>
   <si>
@@ -1126,7 +1136,7 @@
     <t>Maps to basedOn in Event logical model.</t>
   </si>
   <si>
-    <t>822: source value from PRESCRIPTION - PLACER ORDER # (52-39.3)</t>
+    <t>822: reference from PRESCRIPTION - PLACER ORDER # (52-39.3)</t>
   </si>
   <si>
     <t>RxOut.RxOutpat.CPRSOrderEntryNumber</t>
@@ -1228,9 +1238,6 @@
     <t>823: source value from PRESCRIPTION - QTY (52-7)</t>
   </si>
   <si>
-    <t>Pharmacy: quantity</t>
-  </si>
-  <si>
     <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
   </si>
   <si>
@@ -1341,9 +1348,6 @@
   </si>
   <si>
     <t>826: source value from PRESCRIPTION - DAYS SUPPLY (52-8)</t>
-  </si>
-  <si>
-    <t>Pharmacy: daysSupply</t>
   </si>
   <si>
     <t>effectiveUseTime</t>
@@ -1502,9 +1506,6 @@
     <t>835: source value from PRESCRIPTION - MAIL/WINDOW/PARK (52-11)</t>
   </si>
   <si>
-    <t>Pharmacy: routing</t>
-  </si>
-  <si>
     <t>MedicationDispense.receiver</t>
   </si>
   <si>
@@ -1683,9 +1684,6 @@
     <t>838: source value from PRESCRIPTION - SIG (52-10)</t>
   </si>
   <si>
-    <t>Pharmacy: sig</t>
-  </si>
-  <si>
     <t>RXO-6; RXE-21</t>
   </si>
   <si>
@@ -2004,9 +2002,6 @@
     <t>RxOut.RxOutpatMedInstructions.DoseOrdered</t>
   </si>
   <si>
-    <t>Pharmacy: dose.dose</t>
-  </si>
-  <si>
     <t>MedicationDispense.dosageInstruction.doseAndRate.dose[x]:doseQuantity.comparator</t>
   </si>
   <si>
@@ -2023,9 +2018,6 @@
   </si>
   <si>
     <t>RxOut.RxOutpatMedInstructions.Unit</t>
-  </si>
-  <si>
-    <t>Pharmacy: dose.units</t>
   </si>
   <si>
     <t>MedicationDispense.dosageInstruction.doseAndRate.dose[x]:doseQuantity.system</t>
@@ -2633,7 +2625,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="147.1640625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="249.89453125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="43.37109375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>
@@ -5775,13 +5767,13 @@
         <v>263</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>81</v>
+        <v>264</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>81</v>
@@ -5790,15 +5782,15 @@
         <v>81</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5824,14 +5816,14 @@
         <v>212</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>81</v>
@@ -5880,7 +5872,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5907,7 +5899,7 @@
         <v>81</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>81</v>
@@ -5916,15 +5908,15 @@
         <v>81</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5947,19 +5939,19 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -6008,7 +6000,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -6035,7 +6027,7 @@
         <v>81</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>81</v>
@@ -6044,15 +6036,15 @@
         <v>81</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6078,16 +6070,16 @@
         <v>212</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>81</v>
@@ -6136,7 +6128,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -6151,19 +6143,19 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>81</v>
+        <v>294</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>81</v>
@@ -6172,15 +6164,15 @@
         <v>81</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6203,16 +6195,16 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6262,7 +6254,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -6277,36 +6269,36 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6329,13 +6321,13 @@
         <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -6386,7 +6378,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -6410,10 +6402,10 @@
         <v>81</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>81</v>
@@ -6427,10 +6419,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6453,13 +6445,13 @@
         <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6510,7 +6502,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6537,10 +6529,10 @@
         <v>81</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>81</v>
@@ -6551,10 +6543,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6577,13 +6569,13 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6634,7 +6626,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6649,7 +6641,7 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>81</v>
@@ -6658,10 +6650,10 @@
         <v>81</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>81</v>
@@ -6675,10 +6667,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6799,10 +6791,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6925,14 +6917,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6954,10 +6946,10 @@
         <v>137</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>140</v>
@@ -7012,7 +7004,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -7053,10 +7045,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7082,14 +7074,14 @@
         <v>185</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -7117,10 +7109,10 @@
         <v>179</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>81</v>
@@ -7138,7 +7130,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -7165,7 +7157,7 @@
         <v>81</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>81</v>
@@ -7179,10 +7171,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7205,13 +7197,13 @@
         <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7262,7 +7254,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>91</v>
@@ -7286,10 +7278,10 @@
         <v>81</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>81</v>
@@ -7303,10 +7295,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7329,13 +7321,13 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7386,7 +7378,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7401,7 +7393,7 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>81</v>
@@ -7413,7 +7405,7 @@
         <v>81</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>81</v>
@@ -7427,10 +7419,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7453,16 +7445,16 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7512,7 +7504,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7527,36 +7519,36 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7582,10 +7574,10 @@
         <v>185</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7597,7 +7589,7 @@
         <v>81</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>81</v>
@@ -7615,28 +7607,28 @@
         <v>179</v>
       </c>
       <c r="Y40" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF40" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7651,7 +7643,7 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>81</v>
@@ -7663,24 +7655,24 @@
         <v>81</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7703,13 +7695,13 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7760,7 +7752,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7787,24 +7779,24 @@
         <v>81</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7925,10 +7917,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8051,10 +8043,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8077,19 +8069,19 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -8138,7 +8130,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -8153,19 +8145,19 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>388</v>
+        <v>81</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>81</v>
@@ -8174,15 +8166,15 @@
         <v>81</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8208,20 +8200,20 @@
         <v>111</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q45" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="R45" t="s" s="2">
         <v>81</v>
@@ -8245,10 +8237,10 @@
         <v>167</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>81</v>
@@ -8266,7 +8258,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8293,7 +8285,7 @@
         <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>81</v>
@@ -8302,15 +8294,15 @@
         <v>81</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8336,14 +8328,14 @@
         <v>212</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -8392,7 +8384,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8419,7 +8411,7 @@
         <v>81</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>81</v>
@@ -8428,15 +8420,15 @@
         <v>81</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8462,14 +8454,14 @@
         <v>105</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
@@ -8518,7 +8510,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8527,7 +8519,7 @@
         <v>91</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>103</v>
@@ -8545,7 +8537,7 @@
         <v>81</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>81</v>
@@ -8554,15 +8546,15 @@
         <v>81</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8588,16 +8580,16 @@
         <v>111</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -8646,7 +8638,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8673,7 +8665,7 @@
         <v>81</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>81</v>
@@ -8682,15 +8674,15 @@
         <v>81</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8713,13 +8705,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8770,7 +8762,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8785,13 +8777,13 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>426</v>
+        <v>81</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>81</v>
@@ -9085,7 +9077,7 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L52" t="s" s="2">
         <v>443</v>
@@ -9917,7 +9909,7 @@
         <v>81</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>476</v>
+        <v>81</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>81</v>
@@ -9937,10 +9929,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9963,13 +9955,13 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -10020,7 +10012,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10047,13 +10039,13 @@
         <v>81</v>
       </c>
       <c r="AO59" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AP59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ59" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ59" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>81</v>
@@ -10061,10 +10053,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10087,13 +10079,13 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -10144,7 +10136,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10168,27 +10160,27 @@
         <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AO60" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="AO60" t="s" s="2">
+      <c r="AP60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR60" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR60" t="s" s="2">
-        <v>489</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10309,10 +10301,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10435,10 +10427,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10461,16 +10453,16 @@
         <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10520,7 +10512,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10547,7 +10539,7 @@
         <v>81</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>81</v>
@@ -10561,10 +10553,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10590,10 +10582,10 @@
         <v>430</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10644,7 +10636,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10671,7 +10663,7 @@
         <v>81</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>81</v>
@@ -10685,10 +10677,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10711,13 +10703,13 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10768,7 +10760,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>91</v>
@@ -10783,19 +10775,19 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO65" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>81</v>
@@ -10809,10 +10801,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10835,16 +10827,16 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10894,7 +10886,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10921,7 +10913,7 @@
         <v>81</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>81</v>
@@ -10935,10 +10927,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11059,10 +11051,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11185,14 +11177,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -11214,10 +11206,10 @@
         <v>137</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>140</v>
@@ -11272,7 +11264,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11313,10 +11305,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11339,17 +11331,17 @@
         <v>92</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>81</v>
@@ -11398,7 +11390,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11425,24 +11417,24 @@
         <v>81</v>
       </c>
       <c r="AO70" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR70" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="AP70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR70" t="s" s="2">
-        <v>527</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11468,14 +11460,14 @@
         <v>212</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>81</v>
@@ -11524,7 +11516,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11539,36 +11531,36 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR71" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="AP71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR71" t="s" s="2">
-        <v>535</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11594,16 +11586,16 @@
         <v>185</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="N72" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="O72" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -11631,28 +11623,28 @@
         <v>179</v>
       </c>
       <c r="Y72" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF72" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11679,7 +11671,7 @@
         <v>81</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>81</v>
@@ -11688,15 +11680,15 @@
         <v>81</v>
       </c>
       <c r="AR72" t="s" s="2">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11722,10 +11714,10 @@
         <v>212</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11776,7 +11768,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11791,10 +11783,10 @@
         <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>81</v>
@@ -11803,7 +11795,7 @@
         <v>81</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>81</v>
@@ -11812,15 +11804,15 @@
         <v>81</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11843,19 +11835,19 @@
         <v>92</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
@@ -11904,7 +11896,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -11931,7 +11923,7 @@
         <v>81</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>81</v>
@@ -11945,10 +11937,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11971,16 +11963,16 @@
         <v>92</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>561</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -12009,28 +12001,28 @@
         <v>179</v>
       </c>
       <c r="Y75" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF75" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12057,7 +12049,7 @@
         <v>81</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>81</v>
@@ -12066,15 +12058,15 @@
         <v>81</v>
       </c>
       <c r="AR75" t="s" s="2">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12100,16 +12092,16 @@
         <v>185</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="N76" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>573</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>81</v>
@@ -12137,28 +12129,28 @@
         <v>179</v>
       </c>
       <c r="Y76" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF76" t="s" s="2">
         <v>574</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12185,7 +12177,7 @@
         <v>81</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>81</v>
@@ -12194,15 +12186,15 @@
         <v>81</v>
       </c>
       <c r="AR76" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12228,14 +12220,14 @@
         <v>185</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>81</v>
@@ -12263,28 +12255,28 @@
         <v>179</v>
       </c>
       <c r="Y77" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF77" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12311,7 +12303,7 @@
         <v>81</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>81</v>
@@ -12320,15 +12312,15 @@
         <v>81</v>
       </c>
       <c r="AR77" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12354,16 +12346,16 @@
         <v>185</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="N78" t="s" s="2">
         <v>589</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>81</v>
@@ -12391,28 +12383,28 @@
         <v>179</v>
       </c>
       <c r="Y78" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF78" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12439,7 +12431,7 @@
         <v>81</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>81</v>
@@ -12448,15 +12440,15 @@
         <v>81</v>
       </c>
       <c r="AR78" t="s" s="2">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12479,13 +12471,13 @@
         <v>92</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>599</v>
-      </c>
-      <c r="L79" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>601</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12536,7 +12528,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12572,15 +12564,15 @@
         <v>81</v>
       </c>
       <c r="AR79" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12701,10 +12693,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12827,10 +12819,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12856,14 +12848,14 @@
         <v>185</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>81</v>
@@ -12891,28 +12883,28 @@
         <v>179</v>
       </c>
       <c r="Y82" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF82" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -12948,15 +12940,15 @@
         <v>81</v>
       </c>
       <c r="AR82" t="s" s="2">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12979,19 +12971,19 @@
         <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>616</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="O83" t="s" s="2">
         <v>617</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>619</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>81</v>
@@ -13038,7 +13030,7 @@
         <v>202</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13065,7 +13057,7 @@
         <v>81</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>81</v>
@@ -13074,18 +13066,18 @@
         <v>81</v>
       </c>
       <c r="AR83" t="s" s="2">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>81</v>
@@ -13107,19 +13099,19 @@
         <v>81</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="N84" t="s" s="2">
         <v>624</v>
       </c>
-      <c r="M84" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>626</v>
-      </c>
       <c r="O84" t="s" s="2">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -13168,7 +13160,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13177,42 +13169,42 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO84" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="AJ84" t="s" s="2">
+      <c r="AP84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR84" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="AP84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR84" t="s" s="2">
-        <v>630</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13333,10 +13325,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13459,10 +13451,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13485,19 +13477,19 @@
         <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>81</v>
@@ -13546,7 +13538,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13561,19 +13553,19 @@
         <v>103</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>81</v>
@@ -13582,15 +13574,15 @@
         <v>81</v>
       </c>
       <c r="AR87" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13616,20 +13608,20 @@
         <v>111</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q88" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="R88" t="s" s="2">
         <v>81</v>
@@ -13653,10 +13645,10 @@
         <v>167</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>81</v>
@@ -13674,7 +13666,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13701,7 +13693,7 @@
         <v>81</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>81</v>
@@ -13710,15 +13702,15 @@
         <v>81</v>
       </c>
       <c r="AR88" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13744,14 +13736,14 @@
         <v>212</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>81</v>
@@ -13800,7 +13792,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -13815,19 +13807,19 @@
         <v>103</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>81</v>
@@ -13836,15 +13828,15 @@
         <v>81</v>
       </c>
       <c r="AR89" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13870,14 +13862,14 @@
         <v>105</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>81</v>
@@ -13926,7 +13918,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -13935,7 +13927,7 @@
         <v>91</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>103</v>
@@ -13953,7 +13945,7 @@
         <v>81</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>81</v>
@@ -13962,15 +13954,15 @@
         <v>81</v>
       </c>
       <c r="AR90" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13996,16 +13988,16 @@
         <v>111</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>81</v>
@@ -14034,7 +14026,7 @@
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -14052,7 +14044,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -14067,19 +14059,19 @@
         <v>103</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>81</v>
@@ -14088,15 +14080,15 @@
         <v>81</v>
       </c>
       <c r="AR91" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14119,19 +14111,19 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="O92" t="s" s="2">
         <v>654</v>
-      </c>
-      <c r="L92" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>658</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>81</v>
@@ -14180,7 +14172,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14207,7 +14199,7 @@
         <v>81</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>81</v>
@@ -14216,15 +14208,15 @@
         <v>81</v>
       </c>
       <c r="AR92" t="s" s="2">
-        <v>661</v>
+        <v>657</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14247,19 +14239,19 @@
         <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="O93" t="s" s="2">
         <v>663</v>
-      </c>
-      <c r="L93" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>667</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -14308,7 +14300,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14335,7 +14327,7 @@
         <v>81</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>81</v>
@@ -14344,15 +14336,15 @@
         <v>81</v>
       </c>
       <c r="AR93" t="s" s="2">
-        <v>670</v>
+        <v>666</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14375,19 +14367,19 @@
         <v>92</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -14436,7 +14428,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14463,7 +14455,7 @@
         <v>81</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>81</v>
@@ -14477,10 +14469,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14503,17 +14495,17 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -14562,7 +14554,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14589,7 +14581,7 @@
         <v>81</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>81</v>
@@ -14603,10 +14595,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14629,13 +14621,13 @@
         <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14686,7 +14678,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14713,13 +14705,13 @@
         <v>81</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ96" t="s" s="2">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="AR96" t="s" s="2">
         <v>81</v>
@@ -14727,10 +14719,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14851,10 +14843,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14977,14 +14969,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -15006,10 +14998,10 @@
         <v>137</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>140</v>
@@ -15064,7 +15056,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -15105,10 +15097,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15131,13 +15123,13 @@
         <v>81</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -15188,7 +15180,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>91</v>
@@ -15215,7 +15207,7 @@
         <v>81</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>81</v>
@@ -15229,10 +15221,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15258,10 +15250,10 @@
         <v>185</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -15291,10 +15283,10 @@
         <v>179</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>81</v>
@@ -15312,7 +15304,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15339,24 +15331,24 @@
         <v>81</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ101" t="s" s="2">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>701</v>
+        <v>697</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15382,10 +15374,10 @@
         <v>185</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15415,10 +15407,10 @@
         <v>179</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>81</v>
@@ -15436,7 +15428,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15463,13 +15455,13 @@
         <v>81</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>81</v>
@@ -15477,10 +15469,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15503,13 +15495,13 @@
         <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15560,7 +15552,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15587,13 +15579,13 @@
         <v>81</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>81</v>
@@ -15601,14 +15593,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -15627,16 +15619,16 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15686,7 +15678,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -15713,7 +15705,7 @@
         <v>81</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>81</v>
@@ -15727,10 +15719,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15753,16 +15745,16 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15812,7 +15804,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -15839,7 +15831,7 @@
         <v>81</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="724">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="728">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -839,11 +839,6 @@
 Dim.LocalDrug.DrugNameWithoutDoseIEN,Dim.LocalDrug.NationalDrugIEN,Dim.LocalDrug.NationalDrugIEN</t>
   </si>
   <si>
-    <t>Dim.LocalDrug.DrugNameWithoutDoseIEN
-Dim.LocalDrug.NationalDrugIEN
-Dim.LocalDrug.NationalDrugIEN</t>
-  </si>
-  <si>
     <t>./code</t>
   </si>
   <si>
@@ -933,11 +928,6 @@
 Dim.LocalDrug.LocalDrugNameWithDose,Dim.LocalDrug.LocalDrugNameWithDose,RxOut.RxOutpatFill.LocalDrugNameWithDose</t>
   </si>
   <si>
-    <t>Dim.LocalDrug.LocalDrugNameWithDose
-Dim.LocalDrug.LocalDrugNameWithDose
-RxOut.RxOutpatFill.LocalDrugNameWithDose</t>
-  </si>
-  <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
@@ -947,7 +937,7 @@
     <t>MedicationDispense.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>
@@ -1238,6 +1228,9 @@
     <t>823: source value from PRESCRIPTION - QTY (52-7)</t>
   </si>
   <si>
+    <t>Pharmacy: quantity</t>
+  </si>
+  <si>
     <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
   </si>
   <si>
@@ -1348,6 +1341,9 @@
   </si>
   <si>
     <t>826: source value from PRESCRIPTION - DAYS SUPPLY (52-8)</t>
+  </si>
+  <si>
+    <t>Pharmacy: daysSupply</t>
   </si>
   <si>
     <t>effectiveUseTime</t>
@@ -1506,6 +1502,9 @@
     <t>835: source value from PRESCRIPTION - MAIL/WINDOW/PARK (52-11)</t>
   </si>
   <si>
+    <t>Pharmacy: routing</t>
+  </si>
+  <si>
     <t>MedicationDispense.receiver</t>
   </si>
   <si>
@@ -1684,6 +1683,9 @@
     <t>838: source value from PRESCRIPTION - SIG (52-10)</t>
   </si>
   <si>
+    <t>Pharmacy: sig</t>
+  </si>
+  <si>
     <t>RXO-6; RXE-21</t>
   </si>
   <si>
@@ -2002,6 +2004,9 @@
     <t>RxOut.RxOutpatMedInstructions.DoseOrdered</t>
   </si>
   <si>
+    <t>Pharmacy: dose.dose</t>
+  </si>
+  <si>
     <t>MedicationDispense.dosageInstruction.doseAndRate.dose[x]:doseQuantity.comparator</t>
   </si>
   <si>
@@ -2018,6 +2023,9 @@
   </si>
   <si>
     <t>RxOut.RxOutpatMedInstructions.Unit</t>
+  </si>
+  <si>
+    <t>Pharmacy: dose.units</t>
   </si>
   <si>
     <t>MedicationDispense.dosageInstruction.doseAndRate.dose[x]:doseQuantity.system</t>
@@ -2625,7 +2633,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="147.1640625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="249.89453125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="43.37109375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>
@@ -5767,30 +5775,30 @@
         <v>263</v>
       </c>
       <c r="AM25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO25" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="AN25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO25" t="s" s="2">
+      <c r="AP25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR25" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR25" t="s" s="2">
-        <v>266</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5816,14 +5824,14 @@
         <v>212</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>81</v>
@@ -5872,7 +5880,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5899,24 +5907,24 @@
         <v>81</v>
       </c>
       <c r="AO26" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AP26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR26" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR26" t="s" s="2">
-        <v>274</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5939,19 +5947,19 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -6000,7 +6008,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -6027,24 +6035,24 @@
         <v>81</v>
       </c>
       <c r="AO27" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AP27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR27" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR27" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6070,16 +6078,16 @@
         <v>212</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="N28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>81</v>
@@ -6128,7 +6136,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -6143,36 +6151,36 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AM28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO28" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AP28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR28" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR28" t="s" s="2">
-        <v>296</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6195,16 +6203,16 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6254,7 +6262,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -6269,36 +6277,36 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="AL29" t="s" s="2">
+      <c r="AO29" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AM29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN29" t="s" s="2">
+      <c r="AP29" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AO29" t="s" s="2">
+      <c r="AQ29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR29" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="AQ29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR29" t="s" s="2">
-        <v>307</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6321,13 +6329,13 @@
         <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -6378,7 +6386,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -6402,10 +6410,10 @@
         <v>81</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>81</v>
@@ -6419,10 +6427,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6445,13 +6453,13 @@
         <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6502,7 +6510,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6529,10 +6537,10 @@
         <v>81</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>81</v>
@@ -6543,10 +6551,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6569,13 +6577,13 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6626,7 +6634,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6641,19 +6649,19 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AO32" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>81</v>
@@ -6667,10 +6675,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6791,10 +6799,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6917,14 +6925,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6946,10 +6954,10 @@
         <v>137</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>140</v>
@@ -7004,7 +7012,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -7045,10 +7053,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7074,14 +7082,14 @@
         <v>185</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -7109,10 +7117,10 @@
         <v>179</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>81</v>
@@ -7130,7 +7138,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -7157,7 +7165,7 @@
         <v>81</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>81</v>
@@ -7171,10 +7179,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7197,13 +7205,13 @@
         <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="L37" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7254,7 +7262,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>91</v>
@@ -7278,10 +7286,10 @@
         <v>81</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>81</v>
@@ -7295,10 +7303,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7321,13 +7329,13 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="L38" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7378,7 +7386,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7393,7 +7401,7 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>81</v>
@@ -7405,7 +7413,7 @@
         <v>81</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>81</v>
@@ -7419,10 +7427,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7445,16 +7453,16 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7504,7 +7512,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7519,36 +7527,36 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AO39" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="AM39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN39" t="s" s="2">
+      <c r="AP39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ39" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="AO39" t="s" s="2">
+      <c r="AR39" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ39" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="AR39" t="s" s="2">
-        <v>363</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7574,10 +7582,10 @@
         <v>185</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7589,7 +7597,7 @@
         <v>81</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>81</v>
@@ -7607,11 +7615,11 @@
         <v>179</v>
       </c>
       <c r="Y40" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="Z40" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="Z40" t="s" s="2">
-        <v>368</v>
-      </c>
       <c r="AA40" t="s" s="2">
         <v>81</v>
       </c>
@@ -7628,7 +7636,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7643,36 +7651,36 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO40" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AP40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ40" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="AL40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO40" t="s" s="2">
+      <c r="AR40" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AP40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ40" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="AR40" t="s" s="2">
-        <v>372</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7695,13 +7703,13 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7752,7 +7760,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7779,24 +7787,24 @@
         <v>81</v>
       </c>
       <c r="AO41" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AP41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ41" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AR41" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ41" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="AR41" t="s" s="2">
-        <v>379</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7917,10 +7925,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8043,10 +8051,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8069,19 +8077,19 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -8130,7 +8138,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -8145,36 +8153,36 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO44" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="AL44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO44" t="s" s="2">
+      <c r="AP44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR44" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR44" t="s" s="2">
-        <v>391</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8200,20 +8208,20 @@
         <v>111</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="P45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q45" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="P45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q45" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="R45" t="s" s="2">
         <v>81</v>
@@ -8237,28 +8245,28 @@
         <v>167</v>
       </c>
       <c r="Y45" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="Z45" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="Z45" t="s" s="2">
+      <c r="AA45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF45" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8285,24 +8293,24 @@
         <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AP45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR45" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR45" t="s" s="2">
-        <v>401</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8328,14 +8336,14 @@
         <v>212</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -8384,7 +8392,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8411,24 +8419,24 @@
         <v>81</v>
       </c>
       <c r="AO46" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AP46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR46" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR46" t="s" s="2">
-        <v>408</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8454,14 +8462,14 @@
         <v>105</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
@@ -8510,7 +8518,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8519,7 +8527,7 @@
         <v>91</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>103</v>
@@ -8537,7 +8545,7 @@
         <v>81</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>81</v>
@@ -8546,15 +8554,15 @@
         <v>81</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8580,16 +8588,16 @@
         <v>111</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -8638,7 +8646,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8665,7 +8673,7 @@
         <v>81</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>81</v>
@@ -8674,15 +8682,15 @@
         <v>81</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8705,13 +8713,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8762,7 +8770,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8777,13 +8785,13 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>81</v>
@@ -9077,7 +9085,7 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="L52" t="s" s="2">
         <v>443</v>
@@ -9909,7 +9917,7 @@
         <v>81</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>81</v>
+        <v>476</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>81</v>
@@ -9929,10 +9937,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9955,13 +9963,13 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -10012,7 +10020,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10039,13 +10047,13 @@
         <v>81</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>81</v>
@@ -10053,10 +10061,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10079,13 +10087,13 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -10136,7 +10144,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10160,10 +10168,10 @@
         <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>81</v>
@@ -10172,15 +10180,15 @@
         <v>81</v>
       </c>
       <c r="AR60" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10301,10 +10309,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10427,10 +10435,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10453,16 +10461,16 @@
         <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10512,7 +10520,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10539,7 +10547,7 @@
         <v>81</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>81</v>
@@ -10553,10 +10561,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10582,10 +10590,10 @@
         <v>430</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10636,7 +10644,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10663,7 +10671,7 @@
         <v>81</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>81</v>
@@ -10677,10 +10685,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10703,13 +10711,13 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10760,7 +10768,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>91</v>
@@ -10775,7 +10783,7 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>81</v>
@@ -10787,7 +10795,7 @@
         <v>81</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>81</v>
@@ -10801,10 +10809,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10827,16 +10835,16 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10886,7 +10894,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10913,7 +10921,7 @@
         <v>81</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>81</v>
@@ -10927,10 +10935,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11051,10 +11059,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11177,14 +11185,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -11206,10 +11214,10 @@
         <v>137</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>140</v>
@@ -11264,7 +11272,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11305,10 +11313,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11331,17 +11339,17 @@
         <v>92</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>81</v>
@@ -11390,7 +11398,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11417,7 +11425,7 @@
         <v>81</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>81</v>
@@ -11426,15 +11434,15 @@
         <v>81</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11460,14 +11468,14 @@
         <v>212</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>81</v>
@@ -11516,7 +11524,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11531,19 +11539,19 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>81</v>
+        <v>534</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>81</v>
@@ -11552,15 +11560,15 @@
         <v>81</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11586,16 +11594,16 @@
         <v>185</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -11623,10 +11631,10 @@
         <v>179</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>81</v>
@@ -11644,7 +11652,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11671,7 +11679,7 @@
         <v>81</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>81</v>
@@ -11680,15 +11688,15 @@
         <v>81</v>
       </c>
       <c r="AR72" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11714,10 +11722,10 @@
         <v>212</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11768,7 +11776,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11783,10 +11791,10 @@
         <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>81</v>
@@ -11795,7 +11803,7 @@
         <v>81</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>81</v>
@@ -11804,15 +11812,15 @@
         <v>81</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11835,19 +11843,19 @@
         <v>92</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
@@ -11896,7 +11904,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -11923,7 +11931,7 @@
         <v>81</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>81</v>
@@ -11937,10 +11945,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11963,16 +11971,16 @@
         <v>92</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -12001,10 +12009,10 @@
         <v>179</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>81</v>
@@ -12022,7 +12030,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12049,7 +12057,7 @@
         <v>81</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>81</v>
@@ -12058,15 +12066,15 @@
         <v>81</v>
       </c>
       <c r="AR75" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12092,16 +12100,16 @@
         <v>185</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>81</v>
@@ -12129,10 +12137,10 @@
         <v>179</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>81</v>
@@ -12150,7 +12158,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12177,7 +12185,7 @@
         <v>81</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>81</v>
@@ -12186,15 +12194,15 @@
         <v>81</v>
       </c>
       <c r="AR76" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12220,14 +12228,14 @@
         <v>185</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>81</v>
@@ -12255,10 +12263,10 @@
         <v>179</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>81</v>
@@ -12276,7 +12284,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12303,7 +12311,7 @@
         <v>81</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>81</v>
@@ -12312,15 +12320,15 @@
         <v>81</v>
       </c>
       <c r="AR77" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12346,16 +12354,16 @@
         <v>185</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>81</v>
@@ -12383,10 +12391,10 @@
         <v>179</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>81</v>
@@ -12404,7 +12412,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12431,7 +12439,7 @@
         <v>81</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>81</v>
@@ -12440,15 +12448,15 @@
         <v>81</v>
       </c>
       <c r="AR78" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12471,13 +12479,13 @@
         <v>92</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12528,7 +12536,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12564,15 +12572,15 @@
         <v>81</v>
       </c>
       <c r="AR79" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12693,10 +12701,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12819,10 +12827,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12848,14 +12856,14 @@
         <v>185</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>81</v>
@@ -12883,10 +12891,10 @@
         <v>179</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>81</v>
@@ -12904,7 +12912,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -12940,15 +12948,15 @@
         <v>81</v>
       </c>
       <c r="AR82" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12971,19 +12979,19 @@
         <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>81</v>
@@ -13030,7 +13038,7 @@
         <v>202</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13057,7 +13065,7 @@
         <v>81</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>81</v>
@@ -13066,18 +13074,18 @@
         <v>81</v>
       </c>
       <c r="AR83" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>81</v>
@@ -13099,19 +13107,19 @@
         <v>81</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -13160,7 +13168,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13169,10 +13177,10 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>81</v>
@@ -13187,7 +13195,7 @@
         <v>81</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>81</v>
@@ -13196,15 +13204,15 @@
         <v>81</v>
       </c>
       <c r="AR84" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13325,10 +13333,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13451,10 +13459,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13477,19 +13485,19 @@
         <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="O87" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>81</v>
@@ -13538,7 +13546,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13553,36 +13561,36 @@
         <v>103</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO87" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AP87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR87" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="AP87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR87" t="s" s="2">
-        <v>391</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13608,20 +13616,20 @@
         <v>111</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="P88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q88" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="P88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q88" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="R88" t="s" s="2">
         <v>81</v>
@@ -13645,28 +13653,28 @@
         <v>167</v>
       </c>
       <c r="Y88" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="Z88" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="Z88" t="s" s="2">
+      <c r="AA88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF88" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13693,24 +13701,24 @@
         <v>81</v>
       </c>
       <c r="AO88" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AP88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR88" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="AP88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR88" t="s" s="2">
-        <v>401</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13736,14 +13744,14 @@
         <v>212</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>81</v>
@@ -13792,7 +13800,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -13807,36 +13815,36 @@
         <v>103</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO89" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AP89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR89" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="AP89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR89" t="s" s="2">
-        <v>408</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13862,14 +13870,14 @@
         <v>105</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>81</v>
@@ -13918,7 +13926,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -13927,7 +13935,7 @@
         <v>91</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>103</v>
@@ -13945,7 +13953,7 @@
         <v>81</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>81</v>
@@ -13954,15 +13962,15 @@
         <v>81</v>
       </c>
       <c r="AR90" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13988,16 +13996,16 @@
         <v>111</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="N91" t="s" s="2">
+      <c r="O91" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>81</v>
@@ -14026,7 +14034,7 @@
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -14044,7 +14052,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -14059,19 +14067,19 @@
         <v>103</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>81</v>
@@ -14080,15 +14088,15 @@
         <v>81</v>
       </c>
       <c r="AR91" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14111,19 +14119,19 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>81</v>
@@ -14172,7 +14180,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14199,7 +14207,7 @@
         <v>81</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>81</v>
@@ -14208,15 +14216,15 @@
         <v>81</v>
       </c>
       <c r="AR92" t="s" s="2">
-        <v>657</v>
+        <v>661</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14239,19 +14247,19 @@
         <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -14300,7 +14308,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14327,7 +14335,7 @@
         <v>81</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>81</v>
@@ -14336,15 +14344,15 @@
         <v>81</v>
       </c>
       <c r="AR93" t="s" s="2">
-        <v>666</v>
+        <v>670</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14367,19 +14375,19 @@
         <v>92</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -14428,7 +14436,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14455,7 +14463,7 @@
         <v>81</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>81</v>
@@ -14469,10 +14477,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14495,17 +14503,17 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -14554,7 +14562,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14581,7 +14589,7 @@
         <v>81</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>81</v>
@@ -14595,10 +14603,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14621,13 +14629,13 @@
         <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14678,7 +14686,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14705,13 +14713,13 @@
         <v>81</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ96" t="s" s="2">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="AR96" t="s" s="2">
         <v>81</v>
@@ -14719,10 +14727,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14843,10 +14851,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14969,14 +14977,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14998,10 +15006,10 @@
         <v>137</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>140</v>
@@ -15056,7 +15064,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -15097,10 +15105,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15123,13 +15131,13 @@
         <v>81</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -15180,7 +15188,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>91</v>
@@ -15207,7 +15215,7 @@
         <v>81</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>81</v>
@@ -15221,10 +15229,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15250,10 +15258,10 @@
         <v>185</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -15283,28 +15291,28 @@
         <v>179</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="Z101" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF101" t="s" s="2">
         <v>695</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>691</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15331,24 +15339,24 @@
         <v>81</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ101" t="s" s="2">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>697</v>
+        <v>701</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15374,10 +15382,10 @@
         <v>185</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15407,28 +15415,28 @@
         <v>179</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="Z102" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF102" t="s" s="2">
         <v>702</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>698</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15455,13 +15463,13 @@
         <v>81</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>81</v>
@@ -15469,10 +15477,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15495,13 +15503,13 @@
         <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15552,7 +15560,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15579,13 +15587,13 @@
         <v>81</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>81</v>
@@ -15593,14 +15601,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -15619,16 +15627,16 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15678,7 +15686,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -15705,7 +15713,7 @@
         <v>81</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>81</v>
@@ -15719,10 +15727,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15745,16 +15753,16 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15804,7 +15812,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -15831,7 +15839,7 @@
         <v>81</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="728">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="729">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1019,9 +1019,6 @@
     <t>Indicates who or what performed the event.</t>
   </si>
   <si>
-    <t>1727: reference from PRESCRIPTION - PHARMACIST (52-23)</t>
-  </si>
-  <si>
     <t>Event.performer</t>
   </si>
   <si>
@@ -1075,7 +1072,7 @@
     <t>MedicationDispense.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|Patient|Device|RelatedPerson)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Practitioner)
 </t>
   </si>
   <si>
@@ -1085,6 +1082,9 @@
     <t>The device, practitioner, etc. who performed the action.  It should be assumed that the actor is the dispenser of the medication.</t>
   </si>
   <si>
+    <t>1727: reference from PRESCRIPTION - PHARMACIST (52-23)</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -1094,7 +1094,7 @@
     <t>MedicationDispense.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Location)
 </t>
   </si>
   <si>
@@ -1104,7 +1104,7 @@
     <t>The principal physical location where the dispense was performed.</t>
   </si>
   <si>
-    <t>1711: reference from PRESCRIPTION - DIVISION (52-20)</t>
+    <t>1711: reference from PRESCRIPTION - DIVISION &gt; OUTPATIENT SITE - DEFAULT ERX CLINIC (52-20 &gt; 59-10)</t>
   </si>
   <si>
     <t>.participation[typeCode=LOC].role</t>
@@ -1396,6 +1396,10 @@
   </si>
   <si>
     <t>MedicationDispense.destination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Location)
+</t>
   </si>
   <si>
     <t>Where the medication was sent</t>
@@ -2606,7 +2610,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="77.93359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="73.37890625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -6568,7 +6572,7 @@
         <v>83</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>81</v>
@@ -6649,19 +6653,19 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="AL32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN32" t="s" s="2">
+      <c r="AO32" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>81</v>
@@ -6675,10 +6679,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6799,10 +6803,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6925,14 +6929,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6954,10 +6958,10 @@
         <v>137</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>140</v>
@@ -7012,7 +7016,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -7053,10 +7057,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7082,14 +7086,14 @@
         <v>185</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -7117,11 +7121,11 @@
         <v>179</v>
       </c>
       <c r="Y36" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="Z36" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="Z36" t="s" s="2">
-        <v>337</v>
-      </c>
       <c r="AA36" t="s" s="2">
         <v>81</v>
       </c>
@@ -7138,7 +7142,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -7165,7 +7169,7 @@
         <v>81</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>81</v>
@@ -7179,10 +7183,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7196,7 +7200,7 @@
         <v>91</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>81</v>
@@ -7205,13 +7209,13 @@
         <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7262,7 +7266,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>91</v>
@@ -7277,7 +7281,7 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>81</v>
+        <v>342</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>81</v>
@@ -9085,13 +9089,13 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>346</v>
+        <v>443</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -9169,24 +9173,24 @@
         <v>81</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9307,10 +9311,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9433,10 +9437,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9462,13 +9466,13 @@
         <v>212</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9518,7 +9522,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9527,7 +9531,7 @@
         <v>91</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>103</v>
@@ -9559,10 +9563,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9588,13 +9592,13 @@
         <v>105</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9620,13 +9624,13 @@
         <v>81</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>81</v>
@@ -9644,7 +9648,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9685,10 +9689,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9714,13 +9718,13 @@
         <v>149</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9770,7 +9774,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9797,7 +9801,7 @@
         <v>81</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>81</v>
@@ -9811,10 +9815,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9840,13 +9844,13 @@
         <v>212</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9896,7 +9900,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9911,13 +9915,13 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>81</v>
@@ -9937,10 +9941,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9963,13 +9967,13 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -10020,7 +10024,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10047,13 +10051,13 @@
         <v>81</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>81</v>
@@ -10061,10 +10065,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10087,13 +10091,13 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -10144,7 +10148,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10168,10 +10172,10 @@
         <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>81</v>
@@ -10180,15 +10184,15 @@
         <v>81</v>
       </c>
       <c r="AR60" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10309,10 +10313,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10435,10 +10439,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10461,16 +10465,16 @@
         <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10520,7 +10524,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10547,7 +10551,7 @@
         <v>81</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>81</v>
@@ -10561,10 +10565,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10590,10 +10594,10 @@
         <v>430</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10644,7 +10648,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10671,7 +10675,7 @@
         <v>81</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>81</v>
@@ -10685,10 +10689,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10711,13 +10715,13 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10768,7 +10772,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>91</v>
@@ -10783,7 +10787,7 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>81</v>
@@ -10795,7 +10799,7 @@
         <v>81</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>81</v>
@@ -10809,10 +10813,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10835,16 +10839,16 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10894,7 +10898,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10921,7 +10925,7 @@
         <v>81</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>81</v>
@@ -10935,10 +10939,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11059,10 +11063,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11185,14 +11189,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -11214,10 +11218,10 @@
         <v>137</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>140</v>
@@ -11272,7 +11276,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11313,10 +11317,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11339,17 +11343,17 @@
         <v>92</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>81</v>
@@ -11398,7 +11402,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11425,7 +11429,7 @@
         <v>81</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>81</v>
@@ -11434,15 +11438,15 @@
         <v>81</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11468,14 +11472,14 @@
         <v>212</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>81</v>
@@ -11524,7 +11528,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11539,19 +11543,19 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>81</v>
@@ -11560,15 +11564,15 @@
         <v>81</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11594,16 +11598,16 @@
         <v>185</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -11631,10 +11635,10 @@
         <v>179</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>81</v>
@@ -11652,7 +11656,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11679,7 +11683,7 @@
         <v>81</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>81</v>
@@ -11688,15 +11692,15 @@
         <v>81</v>
       </c>
       <c r="AR72" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11722,10 +11726,10 @@
         <v>212</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11776,7 +11780,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11791,10 +11795,10 @@
         <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>81</v>
@@ -11803,7 +11807,7 @@
         <v>81</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>81</v>
@@ -11812,15 +11816,15 @@
         <v>81</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11843,19 +11847,19 @@
         <v>92</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
@@ -11904,7 +11908,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -11931,7 +11935,7 @@
         <v>81</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>81</v>
@@ -11945,10 +11949,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11971,16 +11975,16 @@
         <v>92</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -12009,10 +12013,10 @@
         <v>179</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>81</v>
@@ -12030,7 +12034,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12057,7 +12061,7 @@
         <v>81</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>81</v>
@@ -12066,15 +12070,15 @@
         <v>81</v>
       </c>
       <c r="AR75" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12100,16 +12104,16 @@
         <v>185</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>81</v>
@@ -12137,10 +12141,10 @@
         <v>179</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>81</v>
@@ -12158,7 +12162,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12185,7 +12189,7 @@
         <v>81</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>81</v>
@@ -12194,15 +12198,15 @@
         <v>81</v>
       </c>
       <c r="AR76" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12228,14 +12232,14 @@
         <v>185</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>81</v>
@@ -12263,10 +12267,10 @@
         <v>179</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>81</v>
@@ -12284,7 +12288,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12311,7 +12315,7 @@
         <v>81</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>81</v>
@@ -12320,15 +12324,15 @@
         <v>81</v>
       </c>
       <c r="AR77" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12354,16 +12358,16 @@
         <v>185</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>81</v>
@@ -12391,10 +12395,10 @@
         <v>179</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>81</v>
@@ -12412,7 +12416,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12439,7 +12443,7 @@
         <v>81</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>81</v>
@@ -12448,15 +12452,15 @@
         <v>81</v>
       </c>
       <c r="AR78" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12479,13 +12483,13 @@
         <v>92</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12536,7 +12540,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12572,15 +12576,15 @@
         <v>81</v>
       </c>
       <c r="AR79" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12701,10 +12705,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12827,10 +12831,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12856,14 +12860,14 @@
         <v>185</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>81</v>
@@ -12891,10 +12895,10 @@
         <v>179</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>81</v>
@@ -12912,7 +12916,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -12948,15 +12952,15 @@
         <v>81</v>
       </c>
       <c r="AR82" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12979,19 +12983,19 @@
         <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>81</v>
@@ -13038,7 +13042,7 @@
         <v>202</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13065,7 +13069,7 @@
         <v>81</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>81</v>
@@ -13074,18 +13078,18 @@
         <v>81</v>
       </c>
       <c r="AR83" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>81</v>
@@ -13110,16 +13114,16 @@
         <v>372</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -13168,7 +13172,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13177,10 +13181,10 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>81</v>
@@ -13195,7 +13199,7 @@
         <v>81</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>81</v>
@@ -13204,15 +13208,15 @@
         <v>81</v>
       </c>
       <c r="AR84" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13333,10 +13337,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13459,10 +13463,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13561,13 +13565,13 @@
         <v>103</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>81</v>
@@ -13587,10 +13591,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13715,10 +13719,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13815,13 +13819,13 @@
         <v>103</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>81</v>
@@ -13841,10 +13845,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13967,10 +13971,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14034,7 +14038,7 @@
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -14067,13 +14071,13 @@
         <v>103</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>81</v>
@@ -14093,10 +14097,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14119,19 +14123,19 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>81</v>
@@ -14180,7 +14184,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14207,7 +14211,7 @@
         <v>81</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>81</v>
@@ -14216,15 +14220,15 @@
         <v>81</v>
       </c>
       <c r="AR92" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14247,19 +14251,19 @@
         <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -14308,7 +14312,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14335,7 +14339,7 @@
         <v>81</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>81</v>
@@ -14344,15 +14348,15 @@
         <v>81</v>
       </c>
       <c r="AR93" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14378,16 +14382,16 @@
         <v>372</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -14436,7 +14440,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14463,7 +14467,7 @@
         <v>81</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>81</v>
@@ -14477,10 +14481,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14506,14 +14510,14 @@
         <v>372</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -14562,7 +14566,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14589,7 +14593,7 @@
         <v>81</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>81</v>
@@ -14603,10 +14607,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14632,10 +14636,10 @@
         <v>319</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14686,7 +14690,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14713,13 +14717,13 @@
         <v>81</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ96" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AR96" t="s" s="2">
         <v>81</v>
@@ -14727,10 +14731,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14851,10 +14855,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14977,14 +14981,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -15006,10 +15010,10 @@
         <v>137</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>140</v>
@@ -15064,7 +15068,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -15105,10 +15109,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15134,10 +15138,10 @@
         <v>276</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -15188,7 +15192,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>91</v>
@@ -15215,7 +15219,7 @@
         <v>81</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>81</v>
@@ -15229,10 +15233,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15258,10 +15262,10 @@
         <v>185</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -15291,10 +15295,10 @@
         <v>179</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>81</v>
@@ -15312,7 +15316,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15345,18 +15349,18 @@
         <v>81</v>
       </c>
       <c r="AQ101" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15382,10 +15386,10 @@
         <v>185</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15415,10 +15419,10 @@
         <v>179</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>81</v>
@@ -15436,7 +15440,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15463,13 +15467,13 @@
         <v>81</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>81</v>
@@ -15477,10 +15481,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15503,13 +15507,13 @@
         <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15560,7 +15564,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15587,13 +15591,13 @@
         <v>81</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>81</v>
@@ -15601,14 +15605,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -15627,16 +15631,16 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15686,7 +15690,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -15713,7 +15717,7 @@
         <v>81</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>81</v>
@@ -15727,10 +15731,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15753,16 +15757,16 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15812,7 +15816,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -15839,7 +15843,7 @@
         <v>81</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1155,6 +1155,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
+    &lt;system value="http://terminology.hl7.org/CodeSystem/v3-ActCode"/&gt;
     &lt;code value="FF"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1163,7 +1164,7 @@
     <t>http://terminology.hl7.org/ValueSet/v3-ActPharmacySupplyType</t>
   </si>
   <si>
-    <t>1708: fixed value = #FF</t>
+    <t>1708: fixed value = http://terminology.hl7.org/CodeSystem/v3-ActCode#FF</t>
   </si>
   <si>
     <t>.code</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -606,6 +606,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
+    &lt;system value="http://terminology.hl7.org/fhir/CodeSystem/medicationdispense-category"/&gt;
     &lt;code value="outpatient"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -617,7 +618,7 @@
     <t>http://hl7.org/fhir/ValueSet/medicationdispense-category</t>
   </si>
   <si>
-    <t>1668: fixed value = #outpatient</t>
+    <t>1668: fixed value = http://terminology.hl7.org/fhir/CodeSystem/medicationdispense-category#outpatient</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication dispense"].value</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2046,7 +2046,7 @@
     <t>MedicationDispense.dosageInstruction.doseAndRate.dose[x].code</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFDoseUnits</t>
+    <t>http://va.gov/fhir/ValueSet/DoseUnits</t>
   </si>
   <si>
     <t>1575: terminologyMaps using VF_DoseUnits on PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - UNITS (52-113 &gt; 52.0113-2)</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="729">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="730">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -543,6 +543,10 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/medicationdispense-status|4.0.1</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+MedicationDispenseOriginal-1541:if not null then fixed value #completed {null}</t>
   </si>
   <si>
     <t>1541: fixed value = #completed when PRESCRIPTION - RELEASED DATE/TIME (52-31) case not null</t>
@@ -4262,10 +4266,10 @@
         <v>81</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>103</v>
+        <v>170</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>81</v>
@@ -4274,16 +4278,16 @@
         <v>81</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AP13" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AQ13" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AR13" t="s" s="2">
         <v>81</v>
@@ -4291,10 +4295,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4317,13 +4321,13 @@
         <v>81</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -4350,13 +4354,13 @@
         <v>81</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>81</v>
@@ -4374,7 +4378,7 @@
         <v>81</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>82</v>
@@ -4398,10 +4402,10 @@
         <v>81</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>81</v>
@@ -4415,10 +4419,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4441,16 +4445,16 @@
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4461,7 +4465,7 @@
         <v>81</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>81</v>
@@ -4479,10 +4483,10 @@
         <v>115</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>81</v>
@@ -4500,7 +4504,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>82</v>
@@ -4515,7 +4519,7 @@
         <v>103</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>81</v>
@@ -4527,7 +4531,7 @@
         <v>81</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>81</v>
@@ -4541,10 +4545,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4567,16 +4571,16 @@
         <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4602,29 +4606,29 @@
         <v>81</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AC16" s="2"/>
       <c r="AD16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>91</v>
@@ -4648,30 +4652,30 @@
         <v>81</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AQ16" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AR16" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>81</v>
@@ -4693,16 +4697,16 @@
         <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4728,13 +4732,13 @@
         <v>81</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>81</v>
@@ -4752,7 +4756,7 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>91</v>
@@ -4776,27 +4780,27 @@
         <v>81</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AR17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4819,13 +4823,13 @@
         <v>81</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4876,7 +4880,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -4903,7 +4907,7 @@
         <v>81</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>81</v>
@@ -4917,10 +4921,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4949,7 +4953,7 @@
         <v>138</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>140</v>
@@ -4990,19 +4994,19 @@
         <v>81</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -5029,7 +5033,7 @@
         <v>81</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>81</v>
@@ -5043,10 +5047,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -5069,19 +5073,19 @@
         <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>81</v>
@@ -5130,7 +5134,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -5157,7 +5161,7 @@
         <v>81</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>81</v>
@@ -5166,15 +5170,15 @@
         <v>81</v>
       </c>
       <c r="AR20" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5197,13 +5201,13 @@
         <v>81</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -5254,7 +5258,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -5281,7 +5285,7 @@
         <v>81</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>81</v>
@@ -5295,10 +5299,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5327,7 +5331,7 @@
         <v>138</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>140</v>
@@ -5368,19 +5372,19 @@
         <v>81</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
@@ -5407,7 +5411,7 @@
         <v>81</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>81</v>
@@ -5421,10 +5425,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5450,16 +5454,16 @@
         <v>105</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>81</v>
@@ -5469,7 +5473,7 @@
         <v>81</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>81</v>
@@ -5508,7 +5512,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -5523,7 +5527,7 @@
         <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>81</v>
@@ -5535,7 +5539,7 @@
         <v>81</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>81</v>
@@ -5544,15 +5548,15 @@
         <v>81</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5575,16 +5579,16 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5634,7 +5638,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -5661,7 +5665,7 @@
         <v>81</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>81</v>
@@ -5670,15 +5674,15 @@
         <v>81</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5704,14 +5708,14 @@
         <v>111</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
@@ -5760,7 +5764,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -5775,10 +5779,10 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>81</v>
@@ -5787,7 +5791,7 @@
         <v>81</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>81</v>
@@ -5796,15 +5800,15 @@
         <v>81</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5827,17 +5831,17 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>81</v>
@@ -5886,7 +5890,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5913,7 +5917,7 @@
         <v>81</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>81</v>
@@ -5922,15 +5926,15 @@
         <v>81</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5953,19 +5957,19 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -6014,7 +6018,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -6041,7 +6045,7 @@
         <v>81</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>81</v>
@@ -6050,15 +6054,15 @@
         <v>81</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6081,19 +6085,19 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>81</v>
@@ -6142,7 +6146,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -6157,10 +6161,10 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>81</v>
@@ -6169,7 +6173,7 @@
         <v>81</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>81</v>
@@ -6178,15 +6182,15 @@
         <v>81</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6209,16 +6213,16 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6268,7 +6272,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -6283,36 +6287,36 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6335,13 +6339,13 @@
         <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -6392,7 +6396,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -6416,10 +6420,10 @@
         <v>81</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>81</v>
@@ -6433,10 +6437,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6459,13 +6463,13 @@
         <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6516,7 +6520,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6543,10 +6547,10 @@
         <v>81</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>81</v>
@@ -6557,10 +6561,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6583,13 +6587,13 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6640,7 +6644,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6664,10 +6668,10 @@
         <v>81</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>81</v>
@@ -6681,10 +6685,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6707,13 +6711,13 @@
         <v>81</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6764,7 +6768,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6791,7 +6795,7 @@
         <v>81</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>81</v>
@@ -6805,10 +6809,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6837,7 +6841,7 @@
         <v>138</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>140</v>
@@ -6890,7 +6894,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6917,7 +6921,7 @@
         <v>81</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>81</v>
@@ -6931,14 +6935,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6960,10 +6964,10 @@
         <v>137</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>140</v>
@@ -7018,7 +7022,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -7059,10 +7063,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7085,17 +7089,17 @@
         <v>81</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -7120,13 +7124,13 @@
         <v>81</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>81</v>
@@ -7144,7 +7148,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -7171,7 +7175,7 @@
         <v>81</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>81</v>
@@ -7185,10 +7189,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7211,13 +7215,13 @@
         <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7268,7 +7272,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>91</v>
@@ -7283,7 +7287,7 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>81</v>
@@ -7292,10 +7296,10 @@
         <v>81</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>81</v>
@@ -7309,10 +7313,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7335,13 +7339,13 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7392,7 +7396,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7407,7 +7411,7 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>81</v>
@@ -7419,7 +7423,7 @@
         <v>81</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>81</v>
@@ -7433,10 +7437,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7459,16 +7463,16 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7518,7 +7522,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7533,36 +7537,36 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7585,13 +7589,13 @@
         <v>81</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7603,28 +7607,28 @@
         <v>81</v>
       </c>
       <c r="S40" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="Y40" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="T40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X40" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>364</v>
-      </c>
       <c r="Z40" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>81</v>
@@ -7642,7 +7646,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7657,7 +7661,7 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>81</v>
@@ -7669,24 +7673,24 @@
         <v>81</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7709,13 +7713,13 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7766,7 +7770,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7793,24 +7797,24 @@
         <v>81</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7833,13 +7837,13 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7890,7 +7894,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7917,7 +7921,7 @@
         <v>81</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>81</v>
@@ -7931,10 +7935,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7963,7 +7967,7 @@
         <v>138</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>140</v>
@@ -8004,19 +8008,19 @@
         <v>81</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -8043,7 +8047,7 @@
         <v>81</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>81</v>
@@ -8057,10 +8061,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8083,19 +8087,19 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -8144,7 +8148,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -8159,19 +8163,19 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>81</v>
@@ -8180,15 +8184,15 @@
         <v>81</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8214,20 +8218,20 @@
         <v>111</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q45" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="R45" t="s" s="2">
         <v>81</v>
@@ -8251,10 +8255,10 @@
         <v>167</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>81</v>
@@ -8272,7 +8276,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8299,7 +8303,7 @@
         <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>81</v>
@@ -8308,15 +8312,15 @@
         <v>81</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8339,17 +8343,17 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -8398,7 +8402,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8425,7 +8429,7 @@
         <v>81</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>81</v>
@@ -8434,15 +8438,15 @@
         <v>81</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8468,14 +8472,14 @@
         <v>105</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
@@ -8524,7 +8528,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8533,7 +8537,7 @@
         <v>91</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>103</v>
@@ -8551,7 +8555,7 @@
         <v>81</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>81</v>
@@ -8560,15 +8564,15 @@
         <v>81</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8594,16 +8598,16 @@
         <v>111</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -8652,7 +8656,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8679,7 +8683,7 @@
         <v>81</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>81</v>
@@ -8688,15 +8692,15 @@
         <v>81</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8719,13 +8723,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8776,7 +8780,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8791,19 +8795,19 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>81</v>
@@ -8812,15 +8816,15 @@
         <v>81</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8843,13 +8847,13 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8900,7 +8904,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8915,7 +8919,7 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>81</v>
@@ -8927,24 +8931,24 @@
         <v>81</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8967,13 +8971,13 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -9024,7 +9028,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -9048,27 +9052,27 @@
         <v>81</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9091,13 +9095,13 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -9148,7 +9152,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9175,24 +9179,24 @@
         <v>81</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9215,13 +9219,13 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -9272,7 +9276,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -9299,7 +9303,7 @@
         <v>81</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>81</v>
@@ -9313,10 +9317,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9345,7 +9349,7 @@
         <v>138</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>140</v>
@@ -9386,19 +9390,19 @@
         <v>81</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9425,7 +9429,7 @@
         <v>81</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>81</v>
@@ -9439,10 +9443,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9465,16 +9469,16 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9524,7 +9528,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9533,7 +9537,7 @@
         <v>91</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>103</v>
@@ -9565,10 +9569,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9594,13 +9598,13 @@
         <v>105</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9626,13 +9630,13 @@
         <v>81</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>81</v>
@@ -9650,7 +9654,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9691,10 +9695,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9720,13 +9724,13 @@
         <v>149</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9776,7 +9780,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9803,7 +9807,7 @@
         <v>81</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>81</v>
@@ -9817,10 +9821,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9843,16 +9847,16 @@
         <v>92</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9902,7 +9906,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9917,13 +9921,13 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>81</v>
@@ -9943,10 +9947,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9969,13 +9973,13 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -10026,7 +10030,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10053,13 +10057,13 @@
         <v>81</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>81</v>
@@ -10067,10 +10071,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10093,13 +10097,13 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -10150,7 +10154,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10174,10 +10178,10 @@
         <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>81</v>
@@ -10186,15 +10190,15 @@
         <v>81</v>
       </c>
       <c r="AR60" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10217,13 +10221,13 @@
         <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -10274,7 +10278,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -10301,7 +10305,7 @@
         <v>81</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>81</v>
@@ -10315,10 +10319,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10347,7 +10351,7 @@
         <v>138</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>140</v>
@@ -10388,19 +10392,19 @@
         <v>81</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10427,7 +10431,7 @@
         <v>81</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>81</v>
@@ -10441,10 +10445,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10467,16 +10471,16 @@
         <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10526,7 +10530,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10553,7 +10557,7 @@
         <v>81</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>81</v>
@@ -10567,10 +10571,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10593,13 +10597,13 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10650,7 +10654,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10677,7 +10681,7 @@
         <v>81</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>81</v>
@@ -10691,10 +10695,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10717,13 +10721,13 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10774,7 +10778,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>91</v>
@@ -10789,7 +10793,7 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>81</v>
@@ -10801,7 +10805,7 @@
         <v>81</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>81</v>
@@ -10815,10 +10819,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10841,16 +10845,16 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10900,7 +10904,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10927,7 +10931,7 @@
         <v>81</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>81</v>
@@ -10941,10 +10945,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10967,13 +10971,13 @@
         <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -11024,7 +11028,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -11051,7 +11055,7 @@
         <v>81</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>81</v>
@@ -11065,10 +11069,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11097,7 +11101,7 @@
         <v>138</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>140</v>
@@ -11138,19 +11142,19 @@
         <v>81</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -11177,7 +11181,7 @@
         <v>81</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>81</v>
@@ -11191,14 +11195,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -11220,10 +11224,10 @@
         <v>137</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>140</v>
@@ -11278,7 +11282,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11319,10 +11323,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11345,17 +11349,17 @@
         <v>92</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>81</v>
@@ -11404,7 +11408,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11431,7 +11435,7 @@
         <v>81</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>81</v>
@@ -11440,15 +11444,15 @@
         <v>81</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11471,17 +11475,17 @@
         <v>92</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>81</v>
@@ -11530,7 +11534,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11545,19 +11549,19 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>81</v>
@@ -11566,15 +11570,15 @@
         <v>81</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11597,19 +11601,19 @@
         <v>92</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -11634,13 +11638,13 @@
         <v>81</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>81</v>
@@ -11658,7 +11662,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11685,7 +11689,7 @@
         <v>81</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>81</v>
@@ -11694,15 +11698,15 @@
         <v>81</v>
       </c>
       <c r="AR72" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11725,13 +11729,13 @@
         <v>92</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11782,7 +11786,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11797,10 +11801,10 @@
         <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>81</v>
@@ -11809,7 +11813,7 @@
         <v>81</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>81</v>
@@ -11818,15 +11822,15 @@
         <v>81</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11849,19 +11853,19 @@
         <v>92</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
@@ -11910,7 +11914,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -11937,7 +11941,7 @@
         <v>81</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>81</v>
@@ -11951,10 +11955,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11977,16 +11981,16 @@
         <v>92</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -12012,13 +12016,13 @@
         <v>81</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>81</v>
@@ -12036,7 +12040,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12063,7 +12067,7 @@
         <v>81</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>81</v>
@@ -12072,15 +12076,15 @@
         <v>81</v>
       </c>
       <c r="AR75" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12103,19 +12107,19 @@
         <v>92</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>81</v>
@@ -12140,13 +12144,13 @@
         <v>81</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>81</v>
@@ -12164,7 +12168,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12191,7 +12195,7 @@
         <v>81</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>81</v>
@@ -12200,15 +12204,15 @@
         <v>81</v>
       </c>
       <c r="AR76" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12231,17 +12235,17 @@
         <v>92</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>81</v>
@@ -12266,13 +12270,13 @@
         <v>81</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>81</v>
@@ -12290,7 +12294,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12317,7 +12321,7 @@
         <v>81</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>81</v>
@@ -12326,15 +12330,15 @@
         <v>81</v>
       </c>
       <c r="AR77" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12357,19 +12361,19 @@
         <v>92</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>81</v>
@@ -12394,13 +12398,13 @@
         <v>81</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>81</v>
@@ -12418,7 +12422,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12445,7 +12449,7 @@
         <v>81</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>81</v>
@@ -12454,15 +12458,15 @@
         <v>81</v>
       </c>
       <c r="AR78" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12485,13 +12489,13 @@
         <v>92</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12542,7 +12546,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12578,15 +12582,15 @@
         <v>81</v>
       </c>
       <c r="AR79" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12609,13 +12613,13 @@
         <v>81</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12666,7 +12670,7 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -12693,7 +12697,7 @@
         <v>81</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AP80" t="s" s="2">
         <v>81</v>
@@ -12707,10 +12711,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12739,7 +12743,7 @@
         <v>138</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>140</v>
@@ -12780,19 +12784,19 @@
         <v>81</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -12819,7 +12823,7 @@
         <v>81</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>81</v>
@@ -12833,10 +12837,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12859,17 +12863,17 @@
         <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>81</v>
@@ -12894,13 +12898,13 @@
         <v>81</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>81</v>
@@ -12918,7 +12922,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -12954,15 +12958,15 @@
         <v>81</v>
       </c>
       <c r="AR82" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12985,19 +12989,19 @@
         <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>81</v>
@@ -13034,17 +13038,17 @@
         <v>81</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AC83" s="2"/>
       <c r="AD83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13071,7 +13075,7 @@
         <v>81</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>81</v>
@@ -13080,18 +13084,18 @@
         <v>81</v>
       </c>
       <c r="AR83" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>81</v>
@@ -13113,19 +13117,19 @@
         <v>81</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -13174,7 +13178,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13183,10 +13187,10 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>81</v>
@@ -13201,7 +13205,7 @@
         <v>81</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>81</v>
@@ -13210,15 +13214,15 @@
         <v>81</v>
       </c>
       <c r="AR84" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13241,13 +13245,13 @@
         <v>81</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -13298,7 +13302,7 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -13325,7 +13329,7 @@
         <v>81</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>81</v>
@@ -13339,10 +13343,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13371,7 +13375,7 @@
         <v>138</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N86" t="s" s="2">
         <v>140</v>
@@ -13412,19 +13416,19 @@
         <v>81</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
@@ -13451,7 +13455,7 @@
         <v>81</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>81</v>
@@ -13465,10 +13469,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13491,19 +13495,19 @@
         <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>81</v>
@@ -13552,7 +13556,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13567,19 +13571,19 @@
         <v>103</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>81</v>
@@ -13588,15 +13592,15 @@
         <v>81</v>
       </c>
       <c r="AR87" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13622,20 +13626,20 @@
         <v>111</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q88" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="R88" t="s" s="2">
         <v>81</v>
@@ -13659,10 +13663,10 @@
         <v>167</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>81</v>
@@ -13680,7 +13684,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13707,7 +13711,7 @@
         <v>81</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>81</v>
@@ -13716,15 +13720,15 @@
         <v>81</v>
       </c>
       <c r="AR88" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13747,17 +13751,17 @@
         <v>92</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>81</v>
@@ -13806,7 +13810,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -13821,19 +13825,19 @@
         <v>103</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>81</v>
@@ -13842,15 +13846,15 @@
         <v>81</v>
       </c>
       <c r="AR89" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13876,14 +13880,14 @@
         <v>105</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>81</v>
@@ -13932,7 +13936,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -13941,7 +13945,7 @@
         <v>91</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>103</v>
@@ -13959,7 +13963,7 @@
         <v>81</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>81</v>
@@ -13968,15 +13972,15 @@
         <v>81</v>
       </c>
       <c r="AR90" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14002,16 +14006,16 @@
         <v>111</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>81</v>
@@ -14040,7 +14044,7 @@
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -14058,7 +14062,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -14073,19 +14077,19 @@
         <v>103</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>81</v>
@@ -14094,15 +14098,15 @@
         <v>81</v>
       </c>
       <c r="AR91" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14125,19 +14129,19 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>81</v>
@@ -14186,7 +14190,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14213,7 +14217,7 @@
         <v>81</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>81</v>
@@ -14222,15 +14226,15 @@
         <v>81</v>
       </c>
       <c r="AR92" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14253,19 +14257,19 @@
         <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -14314,7 +14318,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14341,7 +14345,7 @@
         <v>81</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>81</v>
@@ -14350,15 +14354,15 @@
         <v>81</v>
       </c>
       <c r="AR93" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14381,19 +14385,19 @@
         <v>92</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -14442,7 +14446,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14469,7 +14473,7 @@
         <v>81</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>81</v>
@@ -14483,10 +14487,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14509,17 +14513,17 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -14568,7 +14572,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14595,7 +14599,7 @@
         <v>81</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>81</v>
@@ -14609,10 +14613,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14635,13 +14639,13 @@
         <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14692,7 +14696,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14719,13 +14723,13 @@
         <v>81</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ96" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AR96" t="s" s="2">
         <v>81</v>
@@ -14733,10 +14737,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14759,13 +14763,13 @@
         <v>81</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -14816,7 +14820,7 @@
         <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>
@@ -14843,7 +14847,7 @@
         <v>81</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AP97" t="s" s="2">
         <v>81</v>
@@ -14857,10 +14861,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14889,7 +14893,7 @@
         <v>138</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N98" t="s" s="2">
         <v>140</v>
@@ -14942,7 +14946,7 @@
         <v>81</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>82</v>
@@ -14969,7 +14973,7 @@
         <v>81</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AP98" t="s" s="2">
         <v>81</v>
@@ -14983,14 +14987,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -15012,10 +15016,10 @@
         <v>137</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>140</v>
@@ -15070,7 +15074,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -15111,10 +15115,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15137,13 +15141,13 @@
         <v>81</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -15194,7 +15198,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>91</v>
@@ -15221,7 +15225,7 @@
         <v>81</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>81</v>
@@ -15235,10 +15239,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15261,13 +15265,13 @@
         <v>81</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -15294,13 +15298,13 @@
         <v>81</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>81</v>
@@ -15318,7 +15322,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15345,24 +15349,24 @@
         <v>81</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ101" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15385,13 +15389,13 @@
         <v>81</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15418,13 +15422,13 @@
         <v>81</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>81</v>
@@ -15442,7 +15446,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15469,13 +15473,13 @@
         <v>81</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>81</v>
@@ -15483,10 +15487,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15509,13 +15513,13 @@
         <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15566,7 +15570,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15593,13 +15597,13 @@
         <v>81</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>81</v>
@@ -15607,14 +15611,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -15633,16 +15637,16 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15692,7 +15696,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -15719,7 +15723,7 @@
         <v>81</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>81</v>
@@ -15733,10 +15737,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15759,16 +15763,16 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15818,7 +15822,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -15845,7 +15849,7 @@
         <v>81</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -546,7 +546,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-MedicationDispenseOriginal-1541:if not null then fixed value #completed {null}</t>
+mdo-26-1541:52-31: if not null then #completed {null}</t>
   </si>
   <si>
     <t>1541: fixed value = #completed when PRESCRIPTION - RELEASED DATE/TIME (52-31) case not null</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="730">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="731">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -844,6 +844,9 @@
 Dim.LocalDrug.DrugNameWithoutDoseIEN,Dim.LocalDrug.NationalDrugIEN,Dim.LocalDrug.NationalDrugIEN</t>
   </si>
   <si>
+    <t>pharmacy.product [m]</t>
+  </si>
+  <si>
     <t>./code</t>
   </si>
   <si>
@@ -1135,6 +1138,9 @@
   </si>
   <si>
     <t>RxOut.RxOutpat.CPRSOrderEntryNumber</t>
+  </si>
+  <si>
+    <t>pharmacy.id,pharmacy.orderID,pharmacy.parent</t>
   </si>
   <si>
     <t>Event.basedOn</t>
@@ -1234,7 +1240,7 @@
     <t>823: source value from PRESCRIPTION - QTY (52-7)</t>
   </si>
   <si>
-    <t>Pharmacy: quantity</t>
+    <t>pharmacy.quantity</t>
   </si>
   <si>
     <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
@@ -1349,7 +1355,7 @@
     <t>826: source value from PRESCRIPTION - DAYS SUPPLY (52-8)</t>
   </si>
   <si>
-    <t>Pharmacy: daysSupply</t>
+    <t>pharmacy.daysSupply</t>
   </si>
   <si>
     <t>effectiveUseTime</t>
@@ -1512,7 +1518,7 @@
     <t>835: source value from PRESCRIPTION - MAIL/WINDOW/PARK (52-11)</t>
   </si>
   <si>
-    <t>Pharmacy: routing</t>
+    <t>pharmacy.routing</t>
   </si>
   <si>
     <t>MedicationDispense.receiver</t>
@@ -1693,9 +1699,6 @@
     <t>838: source value from PRESCRIPTION - SIG (52-10)</t>
   </si>
   <si>
-    <t>Pharmacy: sig</t>
-  </si>
-  <si>
     <t>RXO-6; RXE-21</t>
   </si>
   <si>
@@ -1742,6 +1745,9 @@
   </si>
   <si>
     <t>RxOut.RxOutpatSig.PatientInstructions</t>
+  </si>
+  <si>
+    <t>pharmacy.ptInstructions</t>
   </si>
   <si>
     <t>MedicationDispense.dosageInstruction.timing</t>
@@ -2014,7 +2020,7 @@
     <t>RxOut.RxOutpatMedInstructions.DoseOrdered</t>
   </si>
   <si>
-    <t>Pharmacy: dose.dose</t>
+    <t>pharmacy.dose [m]</t>
   </si>
   <si>
     <t>MedicationDispense.dosageInstruction.doseAndRate.dose[x]:doseQuantity.comparator</t>
@@ -2033,9 +2039,6 @@
   </si>
   <si>
     <t>RxOut.RxOutpatMedInstructions.Unit</t>
-  </si>
-  <si>
-    <t>Pharmacy: dose.units</t>
   </si>
   <si>
     <t>MedicationDispense.dosageInstruction.doseAndRate.dose[x]:doseQuantity.system</t>
@@ -2643,7 +2646,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="147.1640625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="249.89453125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="46.16796875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>
@@ -5785,13 +5788,13 @@
         <v>264</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>81</v>
+        <v>265</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>81</v>
@@ -5800,15 +5803,15 @@
         <v>81</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5834,14 +5837,14 @@
         <v>213</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>81</v>
@@ -5890,7 +5893,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5917,7 +5920,7 @@
         <v>81</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>81</v>
@@ -5926,15 +5929,15 @@
         <v>81</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5957,19 +5960,19 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -6018,7 +6021,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -6045,7 +6048,7 @@
         <v>81</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>81</v>
@@ -6054,15 +6057,15 @@
         <v>81</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6088,16 +6091,16 @@
         <v>213</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>81</v>
@@ -6146,7 +6149,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -6161,19 +6164,19 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>81</v>
+        <v>265</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>81</v>
@@ -6182,15 +6185,15 @@
         <v>81</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6213,16 +6216,16 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6272,7 +6275,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -6287,36 +6290,36 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6339,13 +6342,13 @@
         <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -6396,7 +6399,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -6420,10 +6423,10 @@
         <v>81</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>81</v>
@@ -6437,10 +6440,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6463,13 +6466,13 @@
         <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6520,7 +6523,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6547,10 +6550,10 @@
         <v>81</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>81</v>
@@ -6561,10 +6564,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6587,13 +6590,13 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6644,7 +6647,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6668,10 +6671,10 @@
         <v>81</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>81</v>
@@ -6685,10 +6688,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6809,10 +6812,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6935,14 +6938,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6964,10 +6967,10 @@
         <v>137</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>140</v>
@@ -7022,7 +7025,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -7063,10 +7066,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7092,14 +7095,14 @@
         <v>186</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -7127,10 +7130,10 @@
         <v>180</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>81</v>
@@ -7148,7 +7151,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -7175,7 +7178,7 @@
         <v>81</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>81</v>
@@ -7189,10 +7192,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7215,13 +7218,13 @@
         <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7272,7 +7275,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>91</v>
@@ -7287,7 +7290,7 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>81</v>
@@ -7296,10 +7299,10 @@
         <v>81</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>81</v>
@@ -7313,10 +7316,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7339,13 +7342,13 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7396,7 +7399,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7411,7 +7414,7 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>81</v>
@@ -7423,7 +7426,7 @@
         <v>81</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>81</v>
@@ -7437,10 +7440,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7463,16 +7466,16 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7522,7 +7525,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7537,36 +7540,36 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>81</v>
+        <v>360</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7592,10 +7595,10 @@
         <v>186</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7607,7 +7610,7 @@
         <v>81</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>81</v>
@@ -7625,28 +7628,28 @@
         <v>180</v>
       </c>
       <c r="Y40" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF40" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7661,7 +7664,7 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>81</v>
@@ -7673,24 +7676,24 @@
         <v>81</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7713,13 +7716,13 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7770,7 +7773,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7797,24 +7800,24 @@
         <v>81</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7935,10 +7938,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8061,10 +8064,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8087,19 +8090,19 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -8148,7 +8151,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -8163,19 +8166,19 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>81</v>
@@ -8184,15 +8187,15 @@
         <v>81</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8218,20 +8221,20 @@
         <v>111</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q45" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="R45" t="s" s="2">
         <v>81</v>
@@ -8255,10 +8258,10 @@
         <v>167</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>81</v>
@@ -8276,7 +8279,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8303,7 +8306,7 @@
         <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>81</v>
@@ -8312,15 +8315,15 @@
         <v>81</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8346,14 +8349,14 @@
         <v>213</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -8402,7 +8405,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8429,7 +8432,7 @@
         <v>81</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>81</v>
@@ -8438,15 +8441,15 @@
         <v>81</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8472,14 +8475,14 @@
         <v>105</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
@@ -8528,7 +8531,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8537,7 +8540,7 @@
         <v>91</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>103</v>
@@ -8555,7 +8558,7 @@
         <v>81</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>81</v>
@@ -8564,15 +8567,15 @@
         <v>81</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8598,16 +8601,16 @@
         <v>111</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -8656,7 +8659,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8683,7 +8686,7 @@
         <v>81</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>81</v>
@@ -8692,15 +8695,15 @@
         <v>81</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8723,13 +8726,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8780,7 +8783,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8795,19 +8798,19 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>81</v>
@@ -8816,15 +8819,15 @@
         <v>81</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8847,13 +8850,13 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8904,7 +8907,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8919,7 +8922,7 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>81</v>
@@ -8931,24 +8934,24 @@
         <v>81</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8971,13 +8974,13 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -9028,7 +9031,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -9052,27 +9055,27 @@
         <v>81</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9095,13 +9098,13 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -9152,7 +9155,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9179,24 +9182,24 @@
         <v>81</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9317,10 +9320,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9443,10 +9446,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9472,13 +9475,13 @@
         <v>213</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9528,7 +9531,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9537,7 +9540,7 @@
         <v>91</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>103</v>
@@ -9569,10 +9572,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9598,13 +9601,13 @@
         <v>105</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9630,13 +9633,13 @@
         <v>81</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>81</v>
@@ -9654,7 +9657,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9695,10 +9698,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9724,13 +9727,13 @@
         <v>149</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9780,7 +9783,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9807,7 +9810,7 @@
         <v>81</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>81</v>
@@ -9821,10 +9824,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9850,13 +9853,13 @@
         <v>213</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9906,7 +9909,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9921,13 +9924,13 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>81</v>
@@ -9947,10 +9950,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9973,13 +9976,13 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -10030,7 +10033,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10057,13 +10060,13 @@
         <v>81</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>81</v>
@@ -10071,10 +10074,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10097,13 +10100,13 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -10154,7 +10157,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10178,10 +10181,10 @@
         <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>81</v>
@@ -10190,15 +10193,15 @@
         <v>81</v>
       </c>
       <c r="AR60" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10319,10 +10322,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10445,10 +10448,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10471,16 +10474,16 @@
         <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10530,7 +10533,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10557,7 +10560,7 @@
         <v>81</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>81</v>
@@ -10571,10 +10574,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10597,13 +10600,13 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10654,7 +10657,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10681,7 +10684,7 @@
         <v>81</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>81</v>
@@ -10695,10 +10698,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10721,13 +10724,13 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10778,7 +10781,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>91</v>
@@ -10793,7 +10796,7 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>81</v>
@@ -10805,7 +10808,7 @@
         <v>81</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>81</v>
@@ -10819,10 +10822,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10845,16 +10848,16 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10904,7 +10907,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10931,7 +10934,7 @@
         <v>81</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>81</v>
@@ -10945,10 +10948,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11069,10 +11072,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11195,14 +11198,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -11224,10 +11227,10 @@
         <v>137</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>140</v>
@@ -11282,7 +11285,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11323,10 +11326,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11349,17 +11352,17 @@
         <v>92</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>81</v>
@@ -11408,7 +11411,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11435,7 +11438,7 @@
         <v>81</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>81</v>
@@ -11444,15 +11447,15 @@
         <v>81</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11478,14 +11481,14 @@
         <v>213</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>81</v>
@@ -11534,7 +11537,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11549,19 +11552,19 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>536</v>
+        <v>81</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>81</v>
@@ -11570,15 +11573,15 @@
         <v>81</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11604,16 +11607,16 @@
         <v>186</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -11641,10 +11644,10 @@
         <v>180</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>81</v>
@@ -11662,7 +11665,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11689,7 +11692,7 @@
         <v>81</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>81</v>
@@ -11698,15 +11701,15 @@
         <v>81</v>
       </c>
       <c r="AR72" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11732,10 +11735,10 @@
         <v>213</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11786,7 +11789,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11801,19 +11804,19 @@
         <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>81</v>
+        <v>554</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>81</v>
@@ -11822,15 +11825,15 @@
         <v>81</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11853,19 +11856,19 @@
         <v>92</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
@@ -11914,7 +11917,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -11941,7 +11944,7 @@
         <v>81</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>81</v>
@@ -11955,10 +11958,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11981,16 +11984,16 @@
         <v>92</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -12019,10 +12022,10 @@
         <v>180</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>81</v>
@@ -12040,7 +12043,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12067,7 +12070,7 @@
         <v>81</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>81</v>
@@ -12076,15 +12079,15 @@
         <v>81</v>
       </c>
       <c r="AR75" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12110,16 +12113,16 @@
         <v>186</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>81</v>
@@ -12147,10 +12150,10 @@
         <v>180</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>81</v>
@@ -12168,7 +12171,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12195,7 +12198,7 @@
         <v>81</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>81</v>
@@ -12204,15 +12207,15 @@
         <v>81</v>
       </c>
       <c r="AR76" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12238,14 +12241,14 @@
         <v>186</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>81</v>
@@ -12273,10 +12276,10 @@
         <v>180</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>81</v>
@@ -12294,7 +12297,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12321,7 +12324,7 @@
         <v>81</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>81</v>
@@ -12330,15 +12333,15 @@
         <v>81</v>
       </c>
       <c r="AR77" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12364,16 +12367,16 @@
         <v>186</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>81</v>
@@ -12401,10 +12404,10 @@
         <v>180</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>81</v>
@@ -12422,7 +12425,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12449,7 +12452,7 @@
         <v>81</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>81</v>
@@ -12458,15 +12461,15 @@
         <v>81</v>
       </c>
       <c r="AR78" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12489,13 +12492,13 @@
         <v>92</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12546,7 +12549,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12582,15 +12585,15 @@
         <v>81</v>
       </c>
       <c r="AR79" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12711,10 +12714,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12837,10 +12840,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12866,14 +12869,14 @@
         <v>186</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>81</v>
@@ -12901,10 +12904,10 @@
         <v>180</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>81</v>
@@ -12922,7 +12925,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -12958,15 +12961,15 @@
         <v>81</v>
       </c>
       <c r="AR82" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12989,19 +12992,19 @@
         <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>81</v>
@@ -13048,7 +13051,7 @@
         <v>203</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13075,7 +13078,7 @@
         <v>81</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>81</v>
@@ -13084,18 +13087,18 @@
         <v>81</v>
       </c>
       <c r="AR83" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>81</v>
@@ -13117,19 +13120,19 @@
         <v>81</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -13178,7 +13181,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13187,10 +13190,10 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>81</v>
@@ -13205,7 +13208,7 @@
         <v>81</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>81</v>
@@ -13214,15 +13217,15 @@
         <v>81</v>
       </c>
       <c r="AR84" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13343,10 +13346,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13469,10 +13472,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13495,19 +13498,19 @@
         <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>81</v>
@@ -13556,7 +13559,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13571,19 +13574,19 @@
         <v>103</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>81</v>
@@ -13592,15 +13595,15 @@
         <v>81</v>
       </c>
       <c r="AR87" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13626,20 +13629,20 @@
         <v>111</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q88" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="R88" t="s" s="2">
         <v>81</v>
@@ -13663,10 +13666,10 @@
         <v>167</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>81</v>
@@ -13684,7 +13687,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13711,7 +13714,7 @@
         <v>81</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>81</v>
@@ -13720,15 +13723,15 @@
         <v>81</v>
       </c>
       <c r="AR88" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13754,14 +13757,14 @@
         <v>213</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>81</v>
@@ -13810,7 +13813,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -13825,19 +13828,19 @@
         <v>103</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>81</v>
@@ -13846,15 +13849,15 @@
         <v>81</v>
       </c>
       <c r="AR89" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13880,14 +13883,14 @@
         <v>105</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>81</v>
@@ -13936,7 +13939,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -13945,7 +13948,7 @@
         <v>91</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>103</v>
@@ -13963,7 +13966,7 @@
         <v>81</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>81</v>
@@ -13972,15 +13975,15 @@
         <v>81</v>
       </c>
       <c r="AR90" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14006,16 +14009,16 @@
         <v>111</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>81</v>
@@ -14044,7 +14047,7 @@
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -14062,7 +14065,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -14077,19 +14080,19 @@
         <v>103</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>81</v>
@@ -14098,15 +14101,15 @@
         <v>81</v>
       </c>
       <c r="AR91" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14129,19 +14132,19 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>81</v>
@@ -14190,7 +14193,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14217,7 +14220,7 @@
         <v>81</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>81</v>
@@ -14226,15 +14229,15 @@
         <v>81</v>
       </c>
       <c r="AR92" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14257,19 +14260,19 @@
         <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -14318,7 +14321,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14345,7 +14348,7 @@
         <v>81</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>81</v>
@@ -14354,15 +14357,15 @@
         <v>81</v>
       </c>
       <c r="AR93" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14385,19 +14388,19 @@
         <v>92</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -14446,7 +14449,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14473,7 +14476,7 @@
         <v>81</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>81</v>
@@ -14487,10 +14490,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14513,17 +14516,17 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -14572,7 +14575,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14599,7 +14602,7 @@
         <v>81</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>81</v>
@@ -14613,10 +14616,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14639,13 +14642,13 @@
         <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14696,7 +14699,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14723,13 +14726,13 @@
         <v>81</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ96" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="AR96" t="s" s="2">
         <v>81</v>
@@ -14737,10 +14740,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14861,10 +14864,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14987,14 +14990,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -15016,10 +15019,10 @@
         <v>137</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>140</v>
@@ -15074,7 +15077,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -15115,10 +15118,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15141,13 +15144,13 @@
         <v>81</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -15198,7 +15201,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>91</v>
@@ -15225,7 +15228,7 @@
         <v>81</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>81</v>
@@ -15239,10 +15242,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15268,10 +15271,10 @@
         <v>186</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -15301,10 +15304,10 @@
         <v>180</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>81</v>
@@ -15322,7 +15325,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15349,24 +15352,24 @@
         <v>81</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ101" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15392,10 +15395,10 @@
         <v>186</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15425,10 +15428,10 @@
         <v>180</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>81</v>
@@ -15446,7 +15449,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15473,13 +15476,13 @@
         <v>81</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>81</v>
@@ -15487,10 +15490,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15513,13 +15516,13 @@
         <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15570,7 +15573,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15597,13 +15600,13 @@
         <v>81</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>81</v>
@@ -15611,14 +15614,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -15637,16 +15640,16 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15696,7 +15699,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -15723,7 +15726,7 @@
         <v>81</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>81</v>
@@ -15737,10 +15740,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15763,16 +15766,16 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15822,7 +15825,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -15849,7 +15852,7 @@
         <v>81</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="729">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -844,7 +844,7 @@
 Dim.LocalDrug.DrugNameWithoutDoseIEN,Dim.LocalDrug.NationalDrugIEN,Dim.LocalDrug.NationalDrugIEN</t>
   </si>
   <si>
-    <t>pharmacy.product [m]</t>
+    <t>pharmacy (med).route,med.route</t>
   </si>
   <si>
     <t>./code</t>
@@ -964,6 +964,9 @@
     <t>RxOut.ActivityLog.PatientIEN,RxOut.ActivityLogOtherComments.PatientIEN,RxOut.RxOutpat.PatientIEN,RxOut.RxOutpatExt.PatientIEN,RxOut.RxOutpatExt.PatientSID,RxOut.RxOutpatFill.PatientIEN,RxOut.RxOutpatMedInstructions.PatientIEN,RxOut.RxOutpatSig.PatientIEN</t>
   </si>
   <si>
+    <t>pharmacy (med).units,med.units</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -1138,9 +1141,6 @@
   </si>
   <si>
     <t>RxOut.RxOutpat.CPRSOrderEntryNumber</t>
-  </si>
-  <si>
-    <t>pharmacy.id,pharmacy.orderID,pharmacy.parent</t>
   </si>
   <si>
     <t>Event.basedOn</t>
@@ -1240,7 +1240,7 @@
     <t>823: source value from PRESCRIPTION - QTY (52-7)</t>
   </si>
   <si>
-    <t>pharmacy.quantity</t>
+    <t>pharmacy (med).schedule,med.schedule</t>
   </si>
   <si>
     <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
@@ -1355,7 +1355,7 @@
     <t>826: source value from PRESCRIPTION - DAYS SUPPLY (52-8)</t>
   </si>
   <si>
-    <t>pharmacy.daysSupply</t>
+    <t>pharmacy (med).daysSupply,med.daysSupply</t>
   </si>
   <si>
     <t>effectiveUseTime</t>
@@ -1518,9 +1518,6 @@
     <t>835: source value from PRESCRIPTION - MAIL/WINDOW/PARK (52-11)</t>
   </si>
   <si>
-    <t>pharmacy.routing</t>
-  </si>
-  <si>
     <t>MedicationDispense.receiver</t>
   </si>
   <si>
@@ -1747,9 +1744,6 @@
     <t>RxOut.RxOutpatSig.PatientInstructions</t>
   </si>
   <si>
-    <t>pharmacy.ptInstructions</t>
-  </si>
-  <si>
     <t>MedicationDispense.dosageInstruction.timing</t>
   </si>
   <si>
@@ -2020,7 +2014,7 @@
     <t>RxOut.RxOutpatMedInstructions.DoseOrdered</t>
   </si>
   <si>
-    <t>pharmacy.dose [m]</t>
+    <t>pharmacy (med).dose [m],med.dose [m]</t>
   </si>
   <si>
     <t>MedicationDispense.dosageInstruction.doseAndRate.dose[x]:doseQuantity.comparator</t>
@@ -2646,7 +2640,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="147.1640625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="249.89453125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="46.16796875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="43.31640625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>
@@ -6296,30 +6290,30 @@
         <v>303</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>81</v>
+        <v>304</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6342,13 +6336,13 @@
         <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -6399,7 +6393,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -6423,10 +6417,10 @@
         <v>81</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>81</v>
@@ -6440,10 +6434,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6466,13 +6460,13 @@
         <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6523,7 +6517,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6550,10 +6544,10 @@
         <v>81</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>81</v>
@@ -6564,10 +6558,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6590,13 +6584,13 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6647,7 +6641,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6671,10 +6665,10 @@
         <v>81</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>81</v>
@@ -6688,10 +6682,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6812,10 +6806,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6938,14 +6932,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6967,10 +6961,10 @@
         <v>137</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>140</v>
@@ -7025,7 +7019,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -7066,10 +7060,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7095,14 +7089,14 @@
         <v>186</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -7130,10 +7124,10 @@
         <v>180</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>81</v>
@@ -7151,7 +7145,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -7178,7 +7172,7 @@
         <v>81</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>81</v>
@@ -7192,10 +7186,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7218,13 +7212,13 @@
         <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7275,7 +7269,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>91</v>
@@ -7290,7 +7284,7 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>81</v>
@@ -7299,10 +7293,10 @@
         <v>81</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>81</v>
@@ -7316,10 +7310,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7342,13 +7336,13 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7399,7 +7393,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7414,7 +7408,7 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>81</v>
@@ -7426,7 +7420,7 @@
         <v>81</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>81</v>
@@ -7440,10 +7434,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7466,16 +7460,16 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7525,7 +7519,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7540,13 +7534,13 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>360</v>
+        <v>81</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>361</v>
@@ -9930,7 +9924,7 @@
         <v>81</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>480</v>
+        <v>81</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>81</v>
@@ -9950,10 +9944,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9976,13 +9970,13 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>484</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -10033,7 +10027,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10060,13 +10054,13 @@
         <v>81</v>
       </c>
       <c r="AO59" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AP59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ59" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ59" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>81</v>
@@ -10074,10 +10068,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10100,13 +10094,13 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -10157,7 +10151,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10181,27 +10175,27 @@
         <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AO60" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="AO60" t="s" s="2">
+      <c r="AP60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR60" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR60" t="s" s="2">
-        <v>493</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10322,10 +10316,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10448,10 +10442,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10474,16 +10468,16 @@
         <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10533,7 +10527,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10560,7 +10554,7 @@
         <v>81</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>81</v>
@@ -10574,10 +10568,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10603,10 +10597,10 @@
         <v>433</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10657,7 +10651,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10684,7 +10678,7 @@
         <v>81</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>81</v>
@@ -10698,10 +10692,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10724,13 +10718,13 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10781,7 +10775,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>91</v>
@@ -10796,19 +10790,19 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO65" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>81</v>
@@ -10822,10 +10816,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10848,16 +10842,16 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10907,7 +10901,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10934,7 +10928,7 @@
         <v>81</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>81</v>
@@ -10948,10 +10942,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11072,10 +11066,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11198,14 +11192,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -11227,10 +11221,10 @@
         <v>137</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>140</v>
@@ -11285,7 +11279,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11326,10 +11320,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11352,17 +11346,17 @@
         <v>92</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>527</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>81</v>
@@ -11411,7 +11405,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11438,24 +11432,24 @@
         <v>81</v>
       </c>
       <c r="AO70" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR70" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="AP70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR70" t="s" s="2">
-        <v>531</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11481,14 +11475,14 @@
         <v>213</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>81</v>
@@ -11537,7 +11531,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11552,36 +11546,36 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR71" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="AP71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR71" t="s" s="2">
-        <v>538</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11607,16 +11601,16 @@
         <v>186</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="N72" t="s" s="2">
+      <c r="O72" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -11644,28 +11638,28 @@
         <v>180</v>
       </c>
       <c r="Y72" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="Z72" t="s" s="2">
         <v>544</v>
       </c>
-      <c r="Z72" t="s" s="2">
+      <c r="AA72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF72" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11692,7 +11686,7 @@
         <v>81</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>81</v>
@@ -11701,15 +11695,15 @@
         <v>81</v>
       </c>
       <c r="AR72" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11735,10 +11729,10 @@
         <v>213</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>550</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11789,7 +11783,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11804,19 +11798,19 @@
         <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="AL73" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="AL73" t="s" s="2">
-        <v>553</v>
-      </c>
       <c r="AM73" t="s" s="2">
-        <v>554</v>
+        <v>81</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>81</v>
@@ -11825,15 +11819,15 @@
         <v>81</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11856,19 +11850,19 @@
         <v>92</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
@@ -11917,7 +11911,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -11944,7 +11938,7 @@
         <v>81</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>81</v>
@@ -11958,10 +11952,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11984,16 +11978,16 @@
         <v>92</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>567</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -12022,28 +12016,28 @@
         <v>180</v>
       </c>
       <c r="Y75" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF75" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>570</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12070,7 +12064,7 @@
         <v>81</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>81</v>
@@ -12079,15 +12073,15 @@
         <v>81</v>
       </c>
       <c r="AR75" t="s" s="2">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12113,16 +12107,16 @@
         <v>186</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="N76" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>577</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>81</v>
@@ -12150,28 +12144,28 @@
         <v>180</v>
       </c>
       <c r="Y76" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF76" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12198,7 +12192,7 @@
         <v>81</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>81</v>
@@ -12207,15 +12201,15 @@
         <v>81</v>
       </c>
       <c r="AR76" t="s" s="2">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12241,14 +12235,14 @@
         <v>186</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>81</v>
@@ -12276,28 +12270,28 @@
         <v>180</v>
       </c>
       <c r="Y77" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF77" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12324,7 +12318,7 @@
         <v>81</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>81</v>
@@ -12333,15 +12327,15 @@
         <v>81</v>
       </c>
       <c r="AR77" t="s" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12367,16 +12361,16 @@
         <v>186</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="N78" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>596</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>81</v>
@@ -12404,28 +12398,28 @@
         <v>180</v>
       </c>
       <c r="Y78" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF78" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12452,7 +12446,7 @@
         <v>81</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>81</v>
@@ -12461,15 +12455,15 @@
         <v>81</v>
       </c>
       <c r="AR78" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12492,13 +12486,13 @@
         <v>92</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>603</v>
-      </c>
-      <c r="L79" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>605</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12549,7 +12543,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12585,15 +12579,15 @@
         <v>81</v>
       </c>
       <c r="AR79" t="s" s="2">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12714,10 +12708,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12840,10 +12834,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12869,14 +12863,14 @@
         <v>186</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>81</v>
@@ -12904,28 +12898,28 @@
         <v>180</v>
       </c>
       <c r="Y82" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF82" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>616</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -12961,15 +12955,15 @@
         <v>81</v>
       </c>
       <c r="AR82" t="s" s="2">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12992,19 +12986,19 @@
         <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>619</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>620</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="O83" t="s" s="2">
         <v>621</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>623</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>81</v>
@@ -13051,7 +13045,7 @@
         <v>203</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13078,7 +13072,7 @@
         <v>81</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>81</v>
@@ -13087,18 +13081,18 @@
         <v>81</v>
       </c>
       <c r="AR83" t="s" s="2">
-        <v>625</v>
+        <v>623</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>81</v>
@@ -13123,16 +13117,16 @@
         <v>375</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="N84" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="M84" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>630</v>
-      </c>
       <c r="O84" t="s" s="2">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -13181,7 +13175,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13190,42 +13184,42 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO84" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="AJ84" t="s" s="2">
+      <c r="AP84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR84" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="AP84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR84" t="s" s="2">
-        <v>634</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13346,10 +13340,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13472,10 +13466,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13574,13 +13568,13 @@
         <v>103</v>
       </c>
       <c r="AK87" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="AM87" t="s" s="2">
         <v>641</v>
-      </c>
-      <c r="AL87" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>643</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>81</v>
@@ -13600,10 +13594,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13728,10 +13722,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13828,13 +13822,13 @@
         <v>103</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>81</v>
@@ -13854,10 +13848,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13980,10 +13974,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14047,7 +14041,7 @@
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -14080,13 +14074,13 @@
         <v>103</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>81</v>
@@ -14106,10 +14100,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14132,19 +14126,19 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>657</v>
       </c>
-      <c r="L92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>658</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="O92" t="s" s="2">
         <v>659</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>661</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>81</v>
@@ -14193,7 +14187,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14220,7 +14214,7 @@
         <v>81</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>81</v>
@@ -14229,15 +14223,15 @@
         <v>81</v>
       </c>
       <c r="AR92" t="s" s="2">
-        <v>664</v>
+        <v>662</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14260,19 +14254,19 @@
         <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>666</v>
       </c>
-      <c r="L93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>667</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="O93" t="s" s="2">
         <v>668</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>670</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -14321,7 +14315,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14348,7 +14342,7 @@
         <v>81</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>81</v>
@@ -14357,15 +14351,15 @@
         <v>81</v>
       </c>
       <c r="AR93" t="s" s="2">
-        <v>673</v>
+        <v>671</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14391,16 +14385,16 @@
         <v>375</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="N94" t="s" s="2">
         <v>675</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="O94" t="s" s="2">
         <v>676</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>678</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -14449,7 +14443,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14476,7 +14470,7 @@
         <v>81</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>81</v>
@@ -14490,10 +14484,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14519,14 +14513,14 @@
         <v>375</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -14575,7 +14569,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14602,7 +14596,7 @@
         <v>81</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>81</v>
@@ -14616,10 +14610,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14642,13 +14636,13 @@
         <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14699,7 +14693,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14726,13 +14720,13 @@
         <v>81</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ96" t="s" s="2">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="AR96" t="s" s="2">
         <v>81</v>
@@ -14740,10 +14734,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14864,10 +14858,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14990,14 +14984,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -15019,10 +15013,10 @@
         <v>137</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>140</v>
@@ -15077,7 +15071,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -15118,10 +15112,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15147,10 +15141,10 @@
         <v>278</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -15201,7 +15195,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>91</v>
@@ -15228,7 +15222,7 @@
         <v>81</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>81</v>
@@ -15242,10 +15236,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15271,10 +15265,10 @@
         <v>186</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -15304,10 +15298,10 @@
         <v>180</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>81</v>
@@ -15325,7 +15319,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15358,18 +15352,18 @@
         <v>81</v>
       </c>
       <c r="AQ101" t="s" s="2">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15395,10 +15389,10 @@
         <v>186</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15428,10 +15422,10 @@
         <v>180</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>81</v>
@@ -15449,7 +15443,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15476,13 +15470,13 @@
         <v>81</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>81</v>
@@ -15490,10 +15484,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15516,13 +15510,13 @@
         <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>713</v>
-      </c>
-      <c r="L103" t="s" s="2">
-        <v>714</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>715</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15573,7 +15567,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15600,13 +15594,13 @@
         <v>81</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>81</v>
@@ -15614,14 +15608,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -15640,16 +15634,16 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>720</v>
       </c>
-      <c r="L104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>721</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>723</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15699,7 +15693,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -15726,7 +15720,7 @@
         <v>81</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>81</v>
@@ -15740,10 +15734,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15766,16 +15760,16 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>726</v>
       </c>
-      <c r="L105" t="s" s="2">
+      <c r="N105" t="s" s="2">
         <v>727</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>728</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>729</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15825,7 +15819,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -15852,7 +15846,7 @@
         <v>81</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -243,7 +243,7 @@
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
+    <t>Mapping: Summary Document Architecure (SDA)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>
@@ -2640,7 +2640,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="147.1640625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="249.89453125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="43.31640625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="729">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="733">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -844,7 +844,8 @@
 Dim.LocalDrug.DrugNameWithoutDoseIEN,Dim.LocalDrug.NationalDrugIEN,Dim.LocalDrug.NationalDrugIEN</t>
   </si>
   <si>
-    <t>pharmacy (med).route,med.route</t>
+    <t>Medication.DrugProduct,Medication.CMOP
+Medication.DrugProduct.Identifier2,Medication.DrugProduct.ProductName,Medication.DrugProductExtension.FederalSchedule</t>
   </si>
   <si>
     <t>./code</t>
@@ -936,6 +937,10 @@
 Dim.LocalDrug.LocalDrugNameWithDose,Dim.LocalDrug.LocalDrugNameWithDose,RxOut.RxOutpatFill.LocalDrugNameWithDose</t>
   </si>
   <si>
+    <t>Medication.DrugProduct,Medication.CMOP
+Medication.DrugProduct.Description,Medication.DrugProduct.OriginalText,Medication.DrugProduct.Description,Medication.DrugProduct.OriginalText,Medication.ATCCode.Code,Medication.Generic.Description,Medication.Route.Description,Medication.OrderCategory.Description,Medication.OriginalText,Medication.OriginalText</t>
+  </si>
+  <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
@@ -964,9 +969,6 @@
     <t>RxOut.ActivityLog.PatientIEN,RxOut.ActivityLogOtherComments.PatientIEN,RxOut.RxOutpat.PatientIEN,RxOut.RxOutpatExt.PatientIEN,RxOut.RxOutpatExt.PatientSID,RxOut.RxOutpatFill.PatientIEN,RxOut.RxOutpatMedInstructions.PatientIEN,RxOut.RxOutpatSig.PatientIEN</t>
   </si>
   <si>
-    <t>pharmacy (med).units,med.units</t>
-  </si>
-  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -1118,6 +1120,9 @@
     <t>1711: reference from PRESCRIPTION - DIVISION &gt; OUTPATIENT SITE - DEFAULT ERX CLINIC (52-20 &gt; 59-10)</t>
   </si>
   <si>
+    <t>Medication.OutpatientSite</t>
+  </si>
+  <si>
     <t>.participation[typeCode=LOC].role</t>
   </si>
   <si>
@@ -1141,6 +1146,9 @@
   </si>
   <si>
     <t>RxOut.RxOutpat.CPRSOrderEntryNumber</t>
+  </si>
+  <si>
+    <t>Medication.ExternalId,Medication.PlacerId</t>
   </si>
   <si>
     <t>Event.basedOn</t>
@@ -1240,7 +1248,7 @@
     <t>823: source value from PRESCRIPTION - QTY (52-7)</t>
   </si>
   <si>
-    <t>pharmacy (med).schedule,med.schedule</t>
+    <t>Medication.OrderQuantity</t>
   </si>
   <si>
     <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
@@ -1355,7 +1363,7 @@
     <t>826: source value from PRESCRIPTION - DAYS SUPPLY (52-8)</t>
   </si>
   <si>
-    <t>pharmacy (med).daysSupply,med.daysSupply</t>
+    <t>Medication.DaysSupply</t>
   </si>
   <si>
     <t>effectiveUseTime</t>
@@ -1621,6 +1629,9 @@
     <t>1716: source value from PRESCRIPTION - REMARKS (52-12)</t>
   </si>
   <si>
+    <t>Medication.Remarks</t>
+  </si>
+  <si>
     <t>Act.text</t>
   </si>
   <si>
@@ -1744,6 +1755,9 @@
     <t>RxOut.RxOutpatSig.PatientInstructions</t>
   </si>
   <si>
+    <t>Medication.TextInstruction</t>
+  </si>
+  <si>
     <t>MedicationDispense.dosageInstruction.timing</t>
   </si>
   <si>
@@ -2014,7 +2028,7 @@
     <t>RxOut.RxOutpatMedInstructions.DoseOrdered</t>
   </si>
   <si>
-    <t>pharmacy (med).dose [m],med.dose [m]</t>
+    <t>Medication.DosageSteps,Medication.Route,Medication.DoseQuantity,Medication.DoseUoM,Medication.Duration,Medication.Frequency,Medication.TextInstruction,Medication.Conjunction,Medication.Noun,Medication.UnitsPerDose,Medication.Verb</t>
   </si>
   <si>
     <t>MedicationDispense.dosageInstruction.doseAndRate.dose[x]:doseQuantity.comparator</t>
@@ -2640,7 +2654,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="147.1640625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="249.89453125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>
@@ -6164,13 +6178,13 @@
         <v>294</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>265</v>
+        <v>295</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>81</v>
@@ -6179,15 +6193,15 @@
         <v>81</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6210,16 +6224,16 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6269,7 +6283,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -6284,13 +6298,13 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>304</v>
+        <v>81</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>305</v>
@@ -7414,13 +7428,13 @@
         <v>81</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>81</v>
+        <v>353</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>81</v>
@@ -7434,10 +7448,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7460,16 +7474,16 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7519,7 +7533,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7534,36 +7548,36 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>81</v>
+        <v>362</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7589,10 +7603,10 @@
         <v>186</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7604,7 +7618,7 @@
         <v>81</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>81</v>
@@ -7622,28 +7636,28 @@
         <v>180</v>
       </c>
       <c r="Y40" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF40" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7658,7 +7672,7 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>81</v>
@@ -7670,24 +7684,24 @@
         <v>81</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7710,13 +7724,13 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7767,7 +7781,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7794,24 +7808,24 @@
         <v>81</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7932,10 +7946,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8058,10 +8072,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8084,19 +8098,19 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -8145,7 +8159,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -8160,19 +8174,19 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>81</v>
@@ -8181,15 +8195,15 @@
         <v>81</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8215,20 +8229,20 @@
         <v>111</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q45" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="R45" t="s" s="2">
         <v>81</v>
@@ -8252,10 +8266,10 @@
         <v>167</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>81</v>
@@ -8273,7 +8287,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8300,7 +8314,7 @@
         <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>81</v>
@@ -8309,15 +8323,15 @@
         <v>81</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8343,14 +8357,14 @@
         <v>213</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -8399,7 +8413,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8426,7 +8440,7 @@
         <v>81</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>81</v>
@@ -8435,15 +8449,15 @@
         <v>81</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8469,14 +8483,14 @@
         <v>105</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
@@ -8525,7 +8539,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8534,7 +8548,7 @@
         <v>91</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>103</v>
@@ -8552,7 +8566,7 @@
         <v>81</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>81</v>
@@ -8561,15 +8575,15 @@
         <v>81</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8595,16 +8609,16 @@
         <v>111</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -8653,7 +8667,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8680,7 +8694,7 @@
         <v>81</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>81</v>
@@ -8689,15 +8703,15 @@
         <v>81</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8720,13 +8734,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8777,7 +8791,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8792,19 +8806,19 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>81</v>
@@ -8813,15 +8827,15 @@
         <v>81</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8844,13 +8858,13 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8901,7 +8915,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8916,7 +8930,7 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>81</v>
@@ -8928,24 +8942,24 @@
         <v>81</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8968,13 +8982,13 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -9025,7 +9039,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -9049,27 +9063,27 @@
         <v>81</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9092,13 +9106,13 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -9149,7 +9163,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9176,24 +9190,24 @@
         <v>81</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9314,10 +9328,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9440,10 +9454,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9469,13 +9483,13 @@
         <v>213</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9525,7 +9539,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9534,7 +9548,7 @@
         <v>91</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>103</v>
@@ -9566,10 +9580,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9595,13 +9609,13 @@
         <v>105</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9627,13 +9641,13 @@
         <v>81</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>81</v>
@@ -9651,7 +9665,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9692,10 +9706,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9721,13 +9735,13 @@
         <v>149</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9777,7 +9791,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9804,7 +9818,7 @@
         <v>81</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>81</v>
@@ -9818,10 +9832,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9847,13 +9861,13 @@
         <v>213</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9903,7 +9917,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9918,7 +9932,7 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>81</v>
@@ -9944,10 +9958,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9970,13 +9984,13 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -10027,7 +10041,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10054,13 +10068,13 @@
         <v>81</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>81</v>
@@ -10068,10 +10082,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10094,13 +10108,13 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -10151,7 +10165,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10175,10 +10189,10 @@
         <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>81</v>
@@ -10187,15 +10201,15 @@
         <v>81</v>
       </c>
       <c r="AR60" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10316,10 +10330,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10442,10 +10456,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10468,16 +10482,16 @@
         <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10527,7 +10541,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10554,7 +10568,7 @@
         <v>81</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>81</v>
@@ -10568,10 +10582,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10594,13 +10608,13 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10651,7 +10665,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10678,7 +10692,7 @@
         <v>81</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>81</v>
@@ -10692,10 +10706,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10718,13 +10732,13 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10775,7 +10789,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>91</v>
@@ -10790,19 +10804,19 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>81</v>
+        <v>515</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>81</v>
@@ -10816,10 +10830,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10842,16 +10856,16 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10901,7 +10915,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10928,7 +10942,7 @@
         <v>81</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>81</v>
@@ -10942,10 +10956,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11066,10 +11080,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11192,10 +11206,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11320,10 +11334,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11346,17 +11360,17 @@
         <v>92</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>81</v>
@@ -11405,7 +11419,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11432,7 +11446,7 @@
         <v>81</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>81</v>
@@ -11441,15 +11455,15 @@
         <v>81</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11475,14 +11489,14 @@
         <v>213</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>81</v>
@@ -11531,7 +11545,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11546,7 +11560,7 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>81</v>
@@ -11558,7 +11572,7 @@
         <v>81</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>81</v>
@@ -11567,15 +11581,15 @@
         <v>81</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11601,16 +11615,16 @@
         <v>186</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -11638,10 +11652,10 @@
         <v>180</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>81</v>
@@ -11659,7 +11673,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11686,7 +11700,7 @@
         <v>81</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>81</v>
@@ -11695,15 +11709,15 @@
         <v>81</v>
       </c>
       <c r="AR72" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11729,10 +11743,10 @@
         <v>213</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11783,7 +11797,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11798,19 +11812,19 @@
         <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>81</v>
+        <v>556</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>81</v>
@@ -11819,15 +11833,15 @@
         <v>81</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11850,19 +11864,19 @@
         <v>92</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
@@ -11911,7 +11925,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -11938,7 +11952,7 @@
         <v>81</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>81</v>
@@ -11952,10 +11966,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11978,16 +11992,16 @@
         <v>92</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -12016,10 +12030,10 @@
         <v>180</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>81</v>
@@ -12037,7 +12051,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12064,7 +12078,7 @@
         <v>81</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>81</v>
@@ -12073,15 +12087,15 @@
         <v>81</v>
       </c>
       <c r="AR75" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12107,16 +12121,16 @@
         <v>186</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>81</v>
@@ -12144,10 +12158,10 @@
         <v>180</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>81</v>
@@ -12165,7 +12179,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12192,7 +12206,7 @@
         <v>81</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>81</v>
@@ -12201,15 +12215,15 @@
         <v>81</v>
       </c>
       <c r="AR76" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12235,14 +12249,14 @@
         <v>186</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>81</v>
@@ -12270,10 +12284,10 @@
         <v>180</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>81</v>
@@ -12291,7 +12305,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12318,7 +12332,7 @@
         <v>81</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>81</v>
@@ -12327,15 +12341,15 @@
         <v>81</v>
       </c>
       <c r="AR77" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12361,16 +12375,16 @@
         <v>186</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>81</v>
@@ -12398,10 +12412,10 @@
         <v>180</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>81</v>
@@ -12419,7 +12433,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12446,7 +12460,7 @@
         <v>81</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>81</v>
@@ -12455,15 +12469,15 @@
         <v>81</v>
       </c>
       <c r="AR78" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12486,13 +12500,13 @@
         <v>92</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12543,7 +12557,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12579,15 +12593,15 @@
         <v>81</v>
       </c>
       <c r="AR79" t="s" s="2">
-        <v>605</v>
+        <v>609</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12708,10 +12722,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12834,10 +12848,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12863,14 +12877,14 @@
         <v>186</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>81</v>
@@ -12898,10 +12912,10 @@
         <v>180</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>81</v>
@@ -12919,7 +12933,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -12955,15 +12969,15 @@
         <v>81</v>
       </c>
       <c r="AR82" t="s" s="2">
-        <v>615</v>
+        <v>619</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12986,19 +13000,19 @@
         <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>81</v>
@@ -13045,7 +13059,7 @@
         <v>203</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13072,7 +13086,7 @@
         <v>81</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>81</v>
@@ -13081,18 +13095,18 @@
         <v>81</v>
       </c>
       <c r="AR83" t="s" s="2">
-        <v>623</v>
+        <v>627</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>81</v>
@@ -13114,19 +13128,19 @@
         <v>81</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -13175,7 +13189,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13184,10 +13198,10 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>81</v>
@@ -13202,7 +13216,7 @@
         <v>81</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>81</v>
@@ -13211,15 +13225,15 @@
         <v>81</v>
       </c>
       <c r="AR84" t="s" s="2">
-        <v>632</v>
+        <v>636</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13340,10 +13354,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13466,10 +13480,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13492,19 +13506,19 @@
         <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>81</v>
@@ -13553,7 +13567,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13568,19 +13582,19 @@
         <v>103</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>81</v>
@@ -13589,15 +13603,15 @@
         <v>81</v>
       </c>
       <c r="AR87" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13623,20 +13637,20 @@
         <v>111</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q88" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="R88" t="s" s="2">
         <v>81</v>
@@ -13660,10 +13674,10 @@
         <v>167</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>81</v>
@@ -13681,7 +13695,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13708,7 +13722,7 @@
         <v>81</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>81</v>
@@ -13717,15 +13731,15 @@
         <v>81</v>
       </c>
       <c r="AR88" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13751,14 +13765,14 @@
         <v>213</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>81</v>
@@ -13807,7 +13821,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -13822,19 +13836,19 @@
         <v>103</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>81</v>
@@ -13843,15 +13857,15 @@
         <v>81</v>
       </c>
       <c r="AR89" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13877,14 +13891,14 @@
         <v>105</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>81</v>
@@ -13933,7 +13947,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -13942,7 +13956,7 @@
         <v>91</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>103</v>
@@ -13960,7 +13974,7 @@
         <v>81</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>81</v>
@@ -13969,15 +13983,15 @@
         <v>81</v>
       </c>
       <c r="AR90" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14003,16 +14017,16 @@
         <v>111</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>81</v>
@@ -14041,7 +14055,7 @@
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -14059,7 +14073,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -14074,19 +14088,19 @@
         <v>103</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>81</v>
@@ -14095,15 +14109,15 @@
         <v>81</v>
       </c>
       <c r="AR91" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14126,19 +14140,19 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>81</v>
@@ -14187,7 +14201,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14214,7 +14228,7 @@
         <v>81</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>81</v>
@@ -14223,15 +14237,15 @@
         <v>81</v>
       </c>
       <c r="AR92" t="s" s="2">
-        <v>662</v>
+        <v>666</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14254,19 +14268,19 @@
         <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -14315,7 +14329,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14342,7 +14356,7 @@
         <v>81</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>81</v>
@@ -14351,15 +14365,15 @@
         <v>81</v>
       </c>
       <c r="AR93" t="s" s="2">
-        <v>671</v>
+        <v>675</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14382,19 +14396,19 @@
         <v>92</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -14443,7 +14457,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14470,7 +14484,7 @@
         <v>81</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>81</v>
@@ -14484,10 +14498,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14510,17 +14524,17 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -14569,7 +14583,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14596,7 +14610,7 @@
         <v>81</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>81</v>
@@ -14610,10 +14624,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14639,10 +14653,10 @@
         <v>322</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14693,7 +14707,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14720,13 +14734,13 @@
         <v>81</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ96" t="s" s="2">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="AR96" t="s" s="2">
         <v>81</v>
@@ -14734,10 +14748,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14858,10 +14872,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14984,10 +14998,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15112,10 +15126,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15141,10 +15155,10 @@
         <v>278</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -15195,7 +15209,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>91</v>
@@ -15222,7 +15236,7 @@
         <v>81</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>81</v>
@@ -15236,10 +15250,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15265,10 +15279,10 @@
         <v>186</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -15298,28 +15312,28 @@
         <v>180</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="Z101" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF101" t="s" s="2">
         <v>700</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>696</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15346,24 +15360,24 @@
         <v>81</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ101" t="s" s="2">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>702</v>
+        <v>706</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15389,10 +15403,10 @@
         <v>186</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15422,28 +15436,28 @@
         <v>180</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="Z102" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF102" t="s" s="2">
         <v>707</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>703</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15470,13 +15484,13 @@
         <v>81</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>81</v>
@@ -15484,10 +15498,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15510,13 +15524,13 @@
         <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15567,7 +15581,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15594,13 +15608,13 @@
         <v>81</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>81</v>
@@ -15608,14 +15622,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -15634,16 +15648,16 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15693,7 +15707,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -15720,7 +15734,7 @@
         <v>81</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>81</v>
@@ -15734,10 +15748,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15760,16 +15774,16 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15819,7 +15833,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -15846,7 +15860,7 @@
         <v>81</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -845,7 +845,7 @@
   </si>
   <si>
     <t>Medication.DrugProduct,Medication.CMOP
-Medication.DrugProduct.Identifier2,Medication.DrugProduct.ProductName,Medication.DrugProductExtension.FederalSchedule</t>
+Medication.DrugProduct.Identifier2,Medication.DrugProduct.ProductName,Medication.Extension[DrugProductExtension].FederalSchedule</t>
   </si>
   <si>
     <t>./code</t>
@@ -938,7 +938,7 @@
   </si>
   <si>
     <t>Medication.DrugProduct,Medication.CMOP
-Medication.DrugProduct.Description,Medication.DrugProduct.OriginalText,Medication.DrugProduct.Description,Medication.DrugProduct.OriginalText,Medication.ATCCode.Code,Medication.Generic.Description,Medication.Route.Description,Medication.OrderCategory.Description,Medication.OriginalText,Medication.OriginalText</t>
+Medication.ComponentMeds[DrugProduct].Description,Medication.ComponentMeds[DrugProduct].OriginalText,Medication.DrugProduct.Description,Medication.DrugProduct.OriginalText,Medication.ATCCode.Code,Medication.Generic.Description,Medication.Route.Description,Medication.OrderCategory.Description,Medication.OriginalText,Medication.OriginalText</t>
   </si>
   <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file PRESCRIPTION (52) to MedicationDispense</t>
+    <t>This StructureDefinition contains the maps for VistA file PRESCRIPTION (52) to MedicationDispense.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="733">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="726">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1979,29 +1979,6 @@
   </si>
   <si>
     <t>doseQuantity</t>
-  </si>
-  <si>
-    <t>A fixed quantity (no comparator)</t>
-  </si>
-  <si>
-    <t>The comparator is not used on a SimpleQuantity</t>
-  </si>
-  <si>
-    <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
-  </si>
-  <si>
-    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
-  </si>
-  <si>
-    <t>SN (see also Range) or CQ</t>
   </si>
   <si>
     <t>MedicationDispense.dosageInstruction.doseAndRate.dose[x]:doseQuantity.id</t>
@@ -13125,19 +13102,19 @@
         <v>81</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K84" t="s" s="2">
         <v>377</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="O84" t="s" s="2">
         <v>625</v>
@@ -13198,10 +13175,10 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>633</v>
+        <v>81</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>634</v>
+        <v>103</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>81</v>
@@ -13216,7 +13193,7 @@
         <v>81</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>635</v>
+        <v>602</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>81</v>
@@ -13225,15 +13202,15 @@
         <v>81</v>
       </c>
       <c r="AR84" t="s" s="2">
-        <v>636</v>
+        <v>627</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>637</v>
+        <v>630</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13354,10 +13331,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>640</v>
+        <v>633</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13480,10 +13457,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>641</v>
+        <v>634</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>642</v>
+        <v>635</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13582,13 +13559,13 @@
         <v>103</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>643</v>
+        <v>636</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>81</v>
@@ -13608,10 +13585,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>646</v>
+        <v>639</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13736,10 +13713,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>649</v>
+        <v>642</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13836,13 +13813,13 @@
         <v>103</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>81</v>
@@ -13862,10 +13839,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>652</v>
+        <v>645</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13988,10 +13965,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14055,7 +14032,7 @@
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -14088,13 +14065,13 @@
         <v>103</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>657</v>
+        <v>650</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>81</v>
@@ -14114,10 +14091,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>658</v>
+        <v>651</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>658</v>
+        <v>651</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14140,19 +14117,19 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>662</v>
+        <v>655</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>663</v>
+        <v>656</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>81</v>
@@ -14201,7 +14178,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14228,7 +14205,7 @@
         <v>81</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>81</v>
@@ -14237,15 +14214,15 @@
         <v>81</v>
       </c>
       <c r="AR92" t="s" s="2">
-        <v>666</v>
+        <v>659</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14268,19 +14245,19 @@
         <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>668</v>
+        <v>661</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>671</v>
+        <v>664</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>672</v>
+        <v>665</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -14329,7 +14306,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>673</v>
+        <v>666</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14356,7 +14333,7 @@
         <v>81</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>81</v>
@@ -14365,15 +14342,15 @@
         <v>81</v>
       </c>
       <c r="AR93" t="s" s="2">
-        <v>675</v>
+        <v>668</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>676</v>
+        <v>669</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>676</v>
+        <v>669</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14399,16 +14376,16 @@
         <v>377</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>679</v>
+        <v>672</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>680</v>
+        <v>673</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -14457,7 +14434,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14484,7 +14461,7 @@
         <v>81</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>682</v>
+        <v>675</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>81</v>
@@ -14498,10 +14475,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14527,14 +14504,14 @@
         <v>377</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>686</v>
+        <v>679</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -14583,7 +14560,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14610,7 +14587,7 @@
         <v>81</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>682</v>
+        <v>675</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>81</v>
@@ -14624,10 +14601,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14653,10 +14630,10 @@
         <v>322</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>689</v>
+        <v>682</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>690</v>
+        <v>683</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14707,7 +14684,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14734,13 +14711,13 @@
         <v>81</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>691</v>
+        <v>684</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ96" t="s" s="2">
-        <v>692</v>
+        <v>685</v>
       </c>
       <c r="AR96" t="s" s="2">
         <v>81</v>
@@ -14748,10 +14725,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>693</v>
+        <v>686</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>693</v>
+        <v>686</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14872,10 +14849,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14998,10 +14975,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15126,10 +15103,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15155,10 +15132,10 @@
         <v>278</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>697</v>
+        <v>690</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>698</v>
+        <v>691</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -15209,7 +15186,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>91</v>
@@ -15236,7 +15213,7 @@
         <v>81</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>81</v>
@@ -15250,10 +15227,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15279,10 +15256,10 @@
         <v>186</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>702</v>
+        <v>695</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -15312,10 +15289,10 @@
         <v>180</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>81</v>
@@ -15333,7 +15310,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15366,18 +15343,18 @@
         <v>81</v>
       </c>
       <c r="AQ101" t="s" s="2">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>706</v>
+        <v>699</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15403,10 +15380,10 @@
         <v>186</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>708</v>
+        <v>701</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15436,10 +15413,10 @@
         <v>180</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>710</v>
+        <v>703</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>81</v>
@@ -15457,7 +15434,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15484,13 +15461,13 @@
         <v>81</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>712</v>
+        <v>705</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>713</v>
+        <v>706</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>81</v>
@@ -15498,10 +15475,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15524,13 +15501,13 @@
         <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15581,7 +15558,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15608,13 +15585,13 @@
         <v>81</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>718</v>
+        <v>711</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>81</v>
@@ -15622,14 +15599,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>720</v>
+        <v>713</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>720</v>
+        <v>713</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -15648,16 +15625,16 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>723</v>
+        <v>716</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>724</v>
+        <v>717</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>725</v>
+        <v>718</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15707,7 +15684,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>720</v>
+        <v>713</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -15734,7 +15711,7 @@
         <v>81</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>726</v>
+        <v>719</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>81</v>
@@ -15748,10 +15725,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15774,16 +15751,16 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>728</v>
+        <v>721</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>730</v>
+        <v>723</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>731</v>
+        <v>724</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15833,7 +15810,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -15860,7 +15837,7 @@
         <v>81</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>732</v>
+        <v>725</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="727">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -546,10 +546,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-mdo-26-1541:52-31: if not null then #completed {null}</t>
-  </si>
-  <si>
-    <t>1541: fixed value = #completed when PRESCRIPTION - RELEASED DATE/TIME (52-31) case not null</t>
+mdo-26-1541:If (52-31) is not null then fixed value #completed {null}</t>
+  </si>
+  <si>
+    <t>1541: fixed value = #completed when PRESCRIPTION - RELEASED DATE/TIME (52-31) if not null</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -837,7 +837,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>1545: source value from PRESCRIPTION - DRUG &gt; DRUG - PSNDF VA PRODUCT NAME ENTRY (52-6 &gt; 50-22)</t>
+    <t>1545: source value based on PRESCRIPTION - DRUG &gt; DRUG - PSNDF VA PRODUCT NAME ENTRY (52-6 &gt; 50-22)</t>
   </si>
   <si>
     <t>RxOut.RxOutpat.LocalDrugIEN,RxOut.RxOutpat.NationalDrugIEN,RxOut.RxOutpatFill.LocalDrugIEN,RxOut.RxOutpatFill.NationalDrugIEN
@@ -930,7 +930,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1544: source value from PRESCRIPTION - DRUG &gt; DRUG - GENERIC NAME (52-6 &gt; 50-.01)</t>
+    <t>1544: source value based on PRESCRIPTION - DRUG &gt; DRUG - GENERIC NAME (52-6 &gt; 50-.01)</t>
   </si>
   <si>
     <t>RxOut.RxOutpat.LocalDrugIEN,RxOut.RxOutpat.NationalDrugIEN,RxOut.RxOutpatFill.LocalDrugIEN,RxOut.RxOutpatFill.NationalDrugIEN
@@ -963,7 +963,7 @@
     <t>SubstanceAdministration-&gt;subject-&gt;Patient.</t>
   </si>
   <si>
-    <t>820: reference from PRESCRIPTION - PATIENT (52-2)</t>
+    <t>820: reference based on PRESCRIPTION - PATIENT (52-2)</t>
   </si>
   <si>
     <t>RxOut.ActivityLog.PatientIEN,RxOut.ActivityLogOtherComments.PatientIEN,RxOut.RxOutpat.PatientIEN,RxOut.RxOutpatExt.PatientIEN,RxOut.RxOutpatExt.PatientSID,RxOut.RxOutpatFill.PatientIEN,RxOut.RxOutpatMedInstructions.PatientIEN,RxOut.RxOutpatSig.PatientIEN</t>
@@ -1095,7 +1095,7 @@
     <t>The device, practitioner, etc. who performed the action.  It should be assumed that the actor is the dispenser of the medication.</t>
   </si>
   <si>
-    <t>1727: reference from PRESCRIPTION - PHARMACIST (52-23)</t>
+    <t>1727: reference based on PRESCRIPTION - PHARMACIST (52-23)</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1117,7 +1117,7 @@
     <t>The principal physical location where the dispense was performed.</t>
   </si>
   <si>
-    <t>1711: reference from PRESCRIPTION - DIVISION &gt; OUTPATIENT SITE - DEFAULT ERX CLINIC (52-20 &gt; 59-10)</t>
+    <t>1711: reference based on PRESCRIPTION - DIVISION &gt; OUTPATIENT SITE - DEFAULT ERX CLINIC (52-20 &gt; 59-10)</t>
   </si>
   <si>
     <t>Medication.OutpatientSite</t>
@@ -1142,7 +1142,7 @@
     <t>Maps to basedOn in Event logical model.</t>
   </si>
   <si>
-    <t>822: reference from PRESCRIPTION - PLACER ORDER # (52-39.3)</t>
+    <t>822: reference based on PRESCRIPTION - PLACER ORDER # (52-39.3)</t>
   </si>
   <si>
     <t>RxOut.RxOutpat.CPRSOrderEntryNumber</t>
@@ -1245,7 +1245,7 @@
     <t>Quantity.value</t>
   </si>
   <si>
-    <t>823: source value from PRESCRIPTION - QTY (52-7)</t>
+    <t>823: source value based on PRESCRIPTION - QTY (52-7)</t>
   </si>
   <si>
     <t>Medication.OrderQuantity</t>
@@ -1360,7 +1360,7 @@
     <t>The amount of medication expressed as a timing amount.</t>
   </si>
   <si>
-    <t>826: source value from PRESCRIPTION - DAYS SUPPLY (52-8)</t>
+    <t>826: source value based on PRESCRIPTION - DAYS SUPPLY (52-8)</t>
   </si>
   <si>
     <t>Medication.DaysSupply</t>
@@ -1388,7 +1388,7 @@
     <t>The time when the dispensed product was packaged and reviewed.</t>
   </si>
   <si>
-    <t>832: source value from PRESCRIPTION - RELEASED DATE/TIME (52-31)</t>
+    <t>832: source value based on PRESCRIPTION - RELEASED DATE/TIME (52-31)</t>
   </si>
   <si>
     <t>.effectiveTime[xmi:type=IVL_TS].low</t>
@@ -1523,7 +1523,7 @@
     <t>Reference.display</t>
   </si>
   <si>
-    <t>835: source value from PRESCRIPTION - MAIL/WINDOW/PARK (52-11)</t>
+    <t>835: source value based on PRESCRIPTION - MAIL/WINDOW/PARK (52-11)</t>
   </si>
   <si>
     <t>MedicationDispense.receiver</t>
@@ -1626,7 +1626,7 @@
     <t>Annotation.text</t>
   </si>
   <si>
-    <t>1716: source value from PRESCRIPTION - REMARKS (52-12)</t>
+    <t>1716: source value based on PRESCRIPTION - REMARKS (52-12)</t>
   </si>
   <si>
     <t>Medication.Remarks</t>
@@ -1704,7 +1704,7 @@
     <t>Dosage.text</t>
   </si>
   <si>
-    <t>838: source value from PRESCRIPTION - SIG (52-10)</t>
+    <t>838: source value based on PRESCRIPTION - SIG (52-10)</t>
   </si>
   <si>
     <t>RXO-6; RXE-21</t>
@@ -1749,7 +1749,7 @@
     <t>Dosage.patientInstruction</t>
   </si>
   <si>
-    <t>839: source value from PRESCRIPTION - PATIENT INSTRUCTIONS (52-114)</t>
+    <t>839: source value based on PRESCRIPTION - PATIENT INSTRUCTIONS (52-114)</t>
   </si>
   <si>
     <t>RxOut.RxOutpatSig.PatientInstructions</t>
@@ -1999,7 +1999,11 @@
     <t>MedicationDispense.dosageInstruction.doseAndRate.dose[x].value</t>
   </si>
   <si>
-    <t>840: source value from PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - DOSAGE ORDERED (52-113 &gt; 52.0113-.01) case number</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+mdo-26-840:If number then source value from (52-113 &gt; 52.0113-.01) {null}</t>
+  </si>
+  <si>
+    <t>840: source value based on PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - DOSAGE ORDERED (52-113 &gt; 52.0113-.01) if number</t>
   </si>
   <si>
     <t>RxOut.RxOutpatMedInstructions.DoseOrdered</t>
@@ -2020,7 +2024,7 @@
     <t>MedicationDispense.dosageInstruction.doseAndRate.dose[x].unit</t>
   </si>
   <si>
-    <t>842: source value from PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - UNITS (52-113 &gt; 52.0113-2)</t>
+    <t>842: source value based on PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - UNITS (52-113 &gt; 52.0113-2)</t>
   </si>
   <si>
     <t>RxOut.RxOutpatMedInstructions.Unit</t>
@@ -2629,7 +2633,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="147.1640625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="148.19921875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="249.89453125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
@@ -13556,16 +13560,16 @@
         <v>81</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>103</v>
+        <v>636</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>81</v>
@@ -13585,10 +13589,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13713,10 +13717,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13813,13 +13817,13 @@
         <v>103</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>81</v>
@@ -13839,10 +13843,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13965,10 +13969,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14032,7 +14036,7 @@
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -14065,13 +14069,13 @@
         <v>103</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>81</v>
@@ -14091,10 +14095,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14117,19 +14121,19 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>81</v>
@@ -14178,7 +14182,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14205,7 +14209,7 @@
         <v>81</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>81</v>
@@ -14214,15 +14218,15 @@
         <v>81</v>
       </c>
       <c r="AR92" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14245,19 +14249,19 @@
         <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -14306,7 +14310,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14333,7 +14337,7 @@
         <v>81</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>81</v>
@@ -14342,15 +14346,15 @@
         <v>81</v>
       </c>
       <c r="AR93" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14376,16 +14380,16 @@
         <v>377</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -14434,7 +14438,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14461,7 +14465,7 @@
         <v>81</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>81</v>
@@ -14475,10 +14479,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14504,14 +14508,14 @@
         <v>377</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -14560,7 +14564,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14587,7 +14591,7 @@
         <v>81</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>81</v>
@@ -14601,10 +14605,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14630,10 +14634,10 @@
         <v>322</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14684,7 +14688,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14711,13 +14715,13 @@
         <v>81</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ96" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AR96" t="s" s="2">
         <v>81</v>
@@ -14725,10 +14729,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14849,10 +14853,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14975,10 +14979,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15103,10 +15107,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15132,10 +15136,10 @@
         <v>278</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -15186,7 +15190,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>91</v>
@@ -15213,7 +15217,7 @@
         <v>81</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>81</v>
@@ -15227,10 +15231,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15256,10 +15260,10 @@
         <v>186</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -15289,10 +15293,10 @@
         <v>180</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>81</v>
@@ -15310,7 +15314,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15343,18 +15347,18 @@
         <v>81</v>
       </c>
       <c r="AQ101" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15380,10 +15384,10 @@
         <v>186</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15413,10 +15417,10 @@
         <v>180</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>81</v>
@@ -15434,7 +15438,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15461,13 +15465,13 @@
         <v>81</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>81</v>
@@ -15475,10 +15479,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15501,13 +15505,13 @@
         <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15558,7 +15562,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15585,13 +15589,13 @@
         <v>81</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>81</v>
@@ -15599,14 +15603,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -15625,16 +15629,16 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15684,7 +15688,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -15711,7 +15715,7 @@
         <v>81</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>81</v>
@@ -15725,10 +15729,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15751,16 +15755,16 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15810,7 +15814,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -15837,7 +15841,7 @@
         <v>81</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="727">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4228" uniqueCount="728">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2040,6 +2040,9 @@
   </si>
   <si>
     <t>MedicationDispense.dosageInstruction.doseAndRate.dose[x].code</t>
+  </si>
+  <si>
+    <t>see mapping [VF_DoseUnits](ConceptMap-VF-DoseUnits.html)</t>
   </si>
   <si>
     <t>http://va.gov/fhir/ValueSet/DoseUnits</t>
@@ -14034,9 +14037,11 @@
       <c r="X91" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="Y91" s="2"/>
+      <c r="Y91" t="s" s="2">
+        <v>650</v>
+      </c>
       <c r="Z91" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -14069,7 +14074,7 @@
         <v>103</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>645</v>
@@ -14095,10 +14100,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14121,19 +14126,19 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>81</v>
@@ -14182,7 +14187,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14209,7 +14214,7 @@
         <v>81</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>81</v>
@@ -14218,15 +14223,15 @@
         <v>81</v>
       </c>
       <c r="AR92" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14249,19 +14254,19 @@
         <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -14310,7 +14315,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14337,7 +14342,7 @@
         <v>81</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>81</v>
@@ -14346,15 +14351,15 @@
         <v>81</v>
       </c>
       <c r="AR93" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14380,16 +14385,16 @@
         <v>377</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -14438,7 +14443,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14465,7 +14470,7 @@
         <v>81</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>81</v>
@@ -14479,10 +14484,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14508,14 +14513,14 @@
         <v>377</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -14564,7 +14569,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14591,7 +14596,7 @@
         <v>81</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>81</v>
@@ -14605,10 +14610,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14634,10 +14639,10 @@
         <v>322</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14688,7 +14693,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14715,13 +14720,13 @@
         <v>81</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ96" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AR96" t="s" s="2">
         <v>81</v>
@@ -14729,10 +14734,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14853,10 +14858,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14979,10 +14984,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15107,10 +15112,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15136,10 +15141,10 @@
         <v>278</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -15190,7 +15195,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>91</v>
@@ -15217,7 +15222,7 @@
         <v>81</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>81</v>
@@ -15231,10 +15236,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15260,10 +15265,10 @@
         <v>186</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -15293,10 +15298,10 @@
         <v>180</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>81</v>
@@ -15314,7 +15319,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15347,18 +15352,18 @@
         <v>81</v>
       </c>
       <c r="AQ101" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15384,10 +15389,10 @@
         <v>186</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15417,10 +15422,10 @@
         <v>180</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>81</v>
@@ -15438,7 +15443,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15465,13 +15470,13 @@
         <v>81</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>81</v>
@@ -15479,10 +15484,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15505,13 +15510,13 @@
         <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15562,7 +15567,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15589,13 +15594,13 @@
         <v>81</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>81</v>
@@ -15603,14 +15608,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -15629,16 +15634,16 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15688,7 +15693,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -15715,7 +15720,7 @@
         <v>81</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>81</v>
@@ -15729,10 +15734,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15755,16 +15760,16 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15814,7 +15819,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -15841,7 +15846,7 @@
         <v>81</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -546,7 +546,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-mdo-26-1541:If (52-31) is not null then fixed value #completed {null}</t>
+mdo-26-1541:If (52-31) is not null then fixed value #completed {true}</t>
   </si>
   <si>
     <t>1541: fixed value = #completed when PRESCRIPTION - RELEASED DATE/TIME (52-31) if not null</t>
@@ -2000,7 +2000,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-mdo-26-840:If number then source value from (52-113 &gt; 52.0113-.01) {null}</t>
+mdo-26-840:If number then source value from (52-113 &gt; 52.0113-.01) {true}</t>
   </si>
   <si>
     <t>840: source value based on PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - DOSAGE ORDERED (52-113 &gt; 52.0113-.01) if number</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
+++ b/docs/StructureDefinition-MedicationDispenseOriginal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
